--- a/Demographic analysis sites.xlsx
+++ b/Demographic analysis sites.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="622" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1082" uniqueCount="72">
   <si>
     <t>Site</t>
   </si>
@@ -117,6 +117,9 @@
 Cave</t>
   </si>
   <si>
+    <t>Banyan Valley Cave</t>
+  </si>
+  <si>
     <t>Tam Pa Ling</t>
   </si>
   <si>
@@ -169,6 +172,63 @@
   </si>
   <si>
     <t xml:space="preserve">Forestier et al. 2021 </t>
+  </si>
+  <si>
+    <t>Fulongdi</t>
+  </si>
+  <si>
+    <t>Huan et al. 2024</t>
+  </si>
+  <si>
+    <t>Bailiandong</t>
+  </si>
+  <si>
+    <t>Zhou et al. 2019</t>
+  </si>
+  <si>
+    <t>Zhaoguo</t>
+  </si>
+  <si>
+    <t>Wei et al. 2020</t>
+  </si>
+  <si>
+    <t>Tangzigou</t>
+  </si>
+  <si>
+    <t>Zhou et al. 2020</t>
+  </si>
+  <si>
+    <t>Huai Hin</t>
+  </si>
+  <si>
+    <t>Forestier et al. 2013</t>
+  </si>
+  <si>
+    <t>Yahuai</t>
+  </si>
+  <si>
+    <t>Wu et al. 2020</t>
+  </si>
+  <si>
+    <t>Zhongshan</t>
+  </si>
+  <si>
+    <t>Tian et al. 2023</t>
+  </si>
+  <si>
+    <t>Longlin</t>
+  </si>
+  <si>
+    <t>Curnoe et al. 2012</t>
+  </si>
+  <si>
+    <t>Maludong</t>
+  </si>
+  <si>
+    <t>Marwick and Gagan 2011</t>
+  </si>
+  <si>
+    <t>Ban Rai</t>
   </si>
 </sst>
 </file>
@@ -300,8 +360,12 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:F156" displayName="Table1" name="Table1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:F270" displayName="Table1" name="Table1" id="1">
   <tableColumns count="6">
     <tableColumn name="Site" id="1"/>
     <tableColumn name="C14Age" id="2"/>
@@ -1523,13 +1587,13 @@
     </row>
     <row r="51" ht="22.5" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B51" s="3">
-        <v>8300.0</v>
+        <v>3042.0</v>
       </c>
       <c r="C51" s="2">
-        <v>30.0</v>
+        <v>37.0</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>15</v>
@@ -1540,16 +1604,17 @@
       <c r="F51" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="H51" s="5"/>
     </row>
     <row r="52" ht="22.5" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B52" s="3">
-        <v>9800.0</v>
+        <v>2995.0</v>
       </c>
       <c r="C52" s="2">
-        <v>30.0</v>
+        <v>40.0</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>15</v>
@@ -1563,13 +1628,13 @@
     </row>
     <row r="53" ht="22.5" customHeight="1">
       <c r="A53" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B53" s="3">
-        <v>7460.0</v>
+        <v>7397.0</v>
       </c>
       <c r="C53" s="2">
-        <v>30.0</v>
+        <v>320.0</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>15</v>
@@ -1583,13 +1648,13 @@
     </row>
     <row r="54" ht="22.5" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B54" s="3">
-        <v>8180.0</v>
+        <v>7902.0</v>
       </c>
       <c r="C54" s="2">
-        <v>30.0</v>
+        <v>390.0</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>15</v>
@@ -1603,13 +1668,13 @@
     </row>
     <row r="55" ht="22.5" customHeight="1">
       <c r="A55" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B55" s="3">
-        <v>9960.0</v>
+        <v>8547.0</v>
       </c>
       <c r="C55" s="2">
-        <v>30.0</v>
+        <v>200.0</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>15</v>
@@ -1623,13 +1688,13 @@
     </row>
     <row r="56" ht="22.5" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B56" s="3">
-        <v>9140.0</v>
+        <v>7907.0</v>
       </c>
       <c r="C56" s="2">
-        <v>30.0</v>
+        <v>198.0</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>15</v>
@@ -1643,13 +1708,13 @@
     </row>
     <row r="57" ht="22.5" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B57" s="3">
-        <v>10510.0</v>
+        <v>8265.0</v>
       </c>
       <c r="C57" s="2">
-        <v>30.0</v>
+        <v>140.0</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>15</v>
@@ -1663,13 +1728,13 @@
     </row>
     <row r="58" ht="22.5" customHeight="1">
       <c r="A58" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B58" s="3">
-        <v>8100.0</v>
+        <v>8517.0</v>
       </c>
       <c r="C58" s="2">
-        <v>30.0</v>
+        <v>290.0</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>15</v>
@@ -1683,13 +1748,13 @@
     </row>
     <row r="59" ht="22.5" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B59" s="3">
-        <v>11160.0</v>
+        <v>11346.0</v>
       </c>
       <c r="C59" s="2">
-        <v>30.0</v>
+        <v>560.0</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>15</v>
@@ -1703,13 +1768,13 @@
     </row>
     <row r="60" ht="22.5" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B60" s="3">
-        <v>9020.0</v>
+        <v>10096.0</v>
       </c>
       <c r="C60" s="2">
-        <v>30.0</v>
+        <v>310.0</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>15</v>
@@ -1723,19 +1788,19 @@
     </row>
     <row r="61" ht="22.5" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B61" s="3">
-        <v>51400.0</v>
+        <v>9073.0</v>
       </c>
       <c r="C61" s="2">
-        <v>3300.0</v>
+        <v>112.0</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>13</v>
@@ -1743,19 +1808,19 @@
     </row>
     <row r="62" ht="22.5" customHeight="1">
       <c r="A62" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B62" s="3">
-        <v>1750.0</v>
+        <v>9177.0</v>
       </c>
       <c r="C62" s="2">
-        <v>81.0</v>
+        <v>360.0</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>13</v>
@@ -1763,19 +1828,19 @@
     </row>
     <row r="63" ht="22.5" customHeight="1">
       <c r="A63" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B63" s="3">
-        <v>6570.0</v>
+        <v>10896.0</v>
       </c>
       <c r="C63" s="2">
-        <v>125.0</v>
+        <v>580.0</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>13</v>
@@ -1783,19 +1848,19 @@
     </row>
     <row r="64" ht="22.5" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B64" s="3">
-        <v>7740.0</v>
+        <v>9510.0</v>
       </c>
       <c r="C64" s="2">
-        <v>125.0</v>
+        <v>160.0</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F64" s="2" t="s">
         <v>13</v>
@@ -1803,19 +1868,19 @@
     </row>
     <row r="65" ht="22.5" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B65" s="3">
-        <v>6570.0</v>
+        <v>9202.0</v>
       </c>
       <c r="C65" s="2">
-        <v>125.0</v>
+        <v>106.0</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F65" s="2" t="s">
         <v>13</v>
@@ -1823,19 +1888,19 @@
     </row>
     <row r="66" ht="22.5" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B66" s="3">
-        <v>11250.0</v>
+        <v>8300.0</v>
       </c>
       <c r="C66" s="2">
-        <v>200.0</v>
+        <v>30.0</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>13</v>
@@ -1843,19 +1908,19 @@
     </row>
     <row r="67" ht="22.5" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B67" s="3">
-        <v>6230.0</v>
+        <v>9800.0</v>
       </c>
       <c r="C67" s="2">
-        <v>90.0</v>
+        <v>30.0</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>13</v>
@@ -1863,19 +1928,19 @@
     </row>
     <row r="68" ht="22.5" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B68" s="3">
-        <v>13400.0</v>
+        <v>7460.0</v>
       </c>
       <c r="C68" s="2">
-        <v>200.0</v>
+        <v>30.0</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>13</v>
@@ -1883,19 +1948,19 @@
     </row>
     <row r="69" ht="22.5" customHeight="1">
       <c r="A69" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B69" s="3">
-        <v>11625.0</v>
+        <v>8180.0</v>
       </c>
       <c r="C69" s="2">
-        <v>35.0</v>
+        <v>30.0</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>13</v>
@@ -1903,19 +1968,19 @@
     </row>
     <row r="70" ht="22.5" customHeight="1">
       <c r="A70" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B70" s="3">
-        <v>10070.0</v>
+        <v>9960.0</v>
       </c>
       <c r="C70" s="2">
-        <v>40.0</v>
+        <v>30.0</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>13</v>
@@ -1923,19 +1988,19 @@
     </row>
     <row r="71" ht="22.5" customHeight="1">
       <c r="A71" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B71" s="3">
-        <v>13215.0</v>
+        <v>9140.0</v>
       </c>
       <c r="C71" s="2">
-        <v>45.0</v>
+        <v>30.0</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>13</v>
@@ -1943,19 +2008,19 @@
     </row>
     <row r="72" ht="22.5" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B72" s="3">
-        <v>9380.0</v>
+        <v>10510.0</v>
       </c>
       <c r="C72" s="2">
-        <v>40.0</v>
+        <v>30.0</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>13</v>
@@ -1963,19 +2028,19 @@
     </row>
     <row r="73" ht="22.5" customHeight="1">
       <c r="A73" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B73" s="3">
-        <v>9775.0</v>
+        <v>8100.0</v>
       </c>
       <c r="C73" s="2">
-        <v>35.0</v>
+        <v>30.0</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>13</v>
@@ -1983,19 +2048,19 @@
     </row>
     <row r="74" ht="22.5" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B74" s="3">
-        <v>9375.0</v>
+        <v>11160.0</v>
       </c>
       <c r="C74" s="2">
-        <v>45.0</v>
+        <v>30.0</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>13</v>
@@ -2003,39 +2068,40 @@
     </row>
     <row r="75" ht="22.5" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B75" s="3">
-        <v>9505.0</v>
+        <v>9020.0</v>
       </c>
       <c r="C75" s="2">
-        <v>40.0</v>
+        <v>30.0</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="H75" s="5"/>
     </row>
     <row r="76" ht="22.5" customHeight="1">
       <c r="A76" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B76" s="3">
-        <v>9650.0</v>
+        <v>7497.0</v>
       </c>
       <c r="C76" s="2">
-        <v>40.0</v>
+        <v>160.0</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>13</v>
@@ -2043,19 +2109,19 @@
     </row>
     <row r="77" ht="22.5" customHeight="1">
       <c r="A77" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B77" s="3">
-        <v>9730.0</v>
+        <v>5178.0</v>
       </c>
       <c r="C77" s="2">
-        <v>40.0</v>
+        <v>110.0</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>13</v>
@@ -2063,19 +2129,19 @@
     </row>
     <row r="78" ht="22.5" customHeight="1">
       <c r="A78" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B78" s="3">
-        <v>8970.0</v>
+        <v>930.0</v>
       </c>
       <c r="C78" s="2">
-        <v>30.0</v>
+        <v>80.0</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>13</v>
@@ -2083,40 +2149,39 @@
     </row>
     <row r="79" ht="22.5" customHeight="1">
       <c r="A79" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B79" s="3">
-        <v>9240.0</v>
+        <v>5358.0</v>
       </c>
       <c r="C79" s="2">
-        <v>30.0</v>
+        <v>120.0</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I79" s="5"/>
     </row>
     <row r="80" ht="22.5" customHeight="1">
       <c r="A80" s="2" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B80" s="3">
-        <v>9140.0</v>
+        <v>280.0</v>
       </c>
       <c r="C80" s="2">
-        <v>30.0</v>
+        <v>20.0</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>13</v>
@@ -2124,60 +2189,60 @@
     </row>
     <row r="81" ht="22.5" customHeight="1">
       <c r="A81" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B81" s="3">
-        <v>9259.0</v>
+        <v>220.0</v>
       </c>
       <c r="C81" s="2">
-        <v>206.0</v>
+        <v>20.0</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="H81" s="5"/>
     </row>
     <row r="82" ht="22.5" customHeight="1">
       <c r="A82" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B82" s="3">
-        <v>8430.0</v>
+        <v>220.0</v>
       </c>
       <c r="C82" s="2">
-        <v>180.0</v>
+        <v>20.0</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I82" s="5"/>
     </row>
     <row r="83" ht="22.5" customHeight="1">
       <c r="A83" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B83" s="3">
-        <v>9710.0</v>
+        <v>3970.0</v>
       </c>
       <c r="C83" s="2">
-        <v>180.0</v>
+        <v>25.0</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>13</v>
@@ -2185,19 +2250,19 @@
     </row>
     <row r="84" ht="22.5" customHeight="1">
       <c r="A84" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B84" s="3">
-        <v>9990.0</v>
+        <v>7300.0</v>
       </c>
       <c r="C84" s="2">
-        <v>50.0</v>
+        <v>30.0</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>13</v>
@@ -2205,19 +2270,19 @@
     </row>
     <row r="85" ht="22.5" customHeight="1">
       <c r="A85" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B85" s="3">
-        <v>10300.0</v>
+        <v>2850.0</v>
       </c>
       <c r="C85" s="2">
-        <v>200.0</v>
+        <v>25.0</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>13</v>
@@ -2225,19 +2290,19 @@
     </row>
     <row r="86" ht="22.5" customHeight="1">
       <c r="A86" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B86" s="3">
-        <v>10450.0</v>
+        <v>4060.0</v>
       </c>
       <c r="C86" s="2">
-        <v>250.0</v>
+        <v>25.0</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="F86" s="2" t="s">
         <v>13</v>
@@ -2245,19 +2310,19 @@
     </row>
     <row r="87" ht="22.5" customHeight="1">
       <c r="A87" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B87" s="3">
-        <v>12200.0</v>
+        <v>6180.0</v>
       </c>
       <c r="C87" s="2">
-        <v>250.0</v>
+        <v>30.0</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>13</v>
@@ -2265,19 +2330,19 @@
     </row>
     <row r="88" ht="22.5" customHeight="1">
       <c r="A88" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B88" s="3">
-        <v>12310.0</v>
+        <v>5900.0</v>
       </c>
       <c r="C88" s="2">
-        <v>100.0</v>
+        <v>25.0</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>13</v>
@@ -2285,19 +2350,19 @@
     </row>
     <row r="89" ht="22.5" customHeight="1">
       <c r="A89" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B89" s="3">
-        <v>11980.0</v>
+        <v>7540.0</v>
       </c>
       <c r="C89" s="2">
-        <v>200.0</v>
+        <v>30.0</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>13</v>
@@ -2305,19 +2370,19 @@
     </row>
     <row r="90" ht="22.5" customHeight="1">
       <c r="A90" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B90" s="3">
-        <v>14400.0</v>
+        <v>4620.0</v>
       </c>
       <c r="C90" s="2">
-        <v>300.0</v>
+        <v>25.0</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="F90" s="2" t="s">
         <v>13</v>
@@ -2325,19 +2390,19 @@
     </row>
     <row r="91" ht="22.5" customHeight="1">
       <c r="A91" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B91" s="3">
-        <v>12300.0</v>
+        <v>10680.0</v>
       </c>
       <c r="C91" s="2">
-        <v>300.0</v>
+        <v>30.0</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>13</v>
@@ -2345,19 +2410,19 @@
     </row>
     <row r="92" ht="22.5" customHeight="1">
       <c r="A92" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B92" s="3">
-        <v>12370.0</v>
+        <v>9270.0</v>
       </c>
       <c r="C92" s="2">
-        <v>160.0</v>
+        <v>30.0</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>13</v>
@@ -2365,19 +2430,19 @@
     </row>
     <row r="93" ht="22.5" customHeight="1">
       <c r="A93" s="2" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B93" s="3">
-        <v>12580.0</v>
+        <v>51400.0</v>
       </c>
       <c r="C93" s="2">
-        <v>220.0</v>
+        <v>3300.0</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>13</v>
@@ -2385,19 +2450,19 @@
     </row>
     <row r="94" ht="22.5" customHeight="1">
       <c r="A94" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B94" s="3">
-        <v>13190.0</v>
+        <v>1750.0</v>
       </c>
       <c r="C94" s="2">
-        <v>150.0</v>
+        <v>81.0</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>13</v>
@@ -2405,19 +2470,19 @@
     </row>
     <row r="95" ht="22.5" customHeight="1">
       <c r="A95" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B95" s="3">
-        <v>14000.0</v>
+        <v>6570.0</v>
       </c>
       <c r="C95" s="2">
-        <v>300.0</v>
+        <v>125.0</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F95" s="2" t="s">
         <v>13</v>
@@ -2425,19 +2490,19 @@
     </row>
     <row r="96" ht="22.5" customHeight="1">
       <c r="A96" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B96" s="3">
-        <v>11850.0</v>
+        <v>7740.0</v>
       </c>
       <c r="C96" s="2">
-        <v>110.0</v>
+        <v>125.0</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>13</v>
@@ -2445,19 +2510,19 @@
     </row>
     <row r="97" ht="22.5" customHeight="1">
       <c r="A97" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B97" s="3">
-        <v>13700.0</v>
+        <v>6570.0</v>
       </c>
       <c r="C97" s="2">
-        <v>80.0</v>
+        <v>125.0</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>13</v>
@@ -2465,19 +2530,19 @@
     </row>
     <row r="98" ht="22.5" customHeight="1">
       <c r="A98" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B98" s="3">
-        <v>14100.0</v>
+        <v>11250.0</v>
       </c>
       <c r="C98" s="2">
-        <v>300.0</v>
+        <v>200.0</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>13</v>
@@ -2485,19 +2550,19 @@
     </row>
     <row r="99" ht="22.5" customHeight="1">
       <c r="A99" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B99" s="3">
-        <v>15300.0</v>
+        <v>6230.0</v>
       </c>
       <c r="C99" s="2">
-        <v>400.0</v>
+        <v>90.0</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>13</v>
@@ -2505,40 +2570,39 @@
     </row>
     <row r="100" ht="22.5" customHeight="1">
       <c r="A100" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B100" s="3">
-        <v>15200.0</v>
+        <v>13400.0</v>
       </c>
       <c r="C100" s="2">
-        <v>400.0</v>
+        <v>200.0</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I100" s="5"/>
     </row>
     <row r="101" ht="22.5" customHeight="1">
       <c r="A101" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B101" s="3">
-        <v>16180.0</v>
+        <v>11625.0</v>
       </c>
       <c r="C101" s="2">
-        <v>80.0</v>
+        <v>35.0</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F101" s="2" t="s">
         <v>13</v>
@@ -2546,19 +2610,19 @@
     </row>
     <row r="102" ht="22.5" customHeight="1">
       <c r="A102" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B102" s="3">
-        <v>16720.0</v>
+        <v>10070.0</v>
       </c>
       <c r="C102" s="2">
-        <v>300.0</v>
+        <v>40.0</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>13</v>
@@ -2566,19 +2630,19 @@
     </row>
     <row r="103" ht="22.5" customHeight="1">
       <c r="A103" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B103" s="3">
-        <v>14370.0</v>
+        <v>13215.0</v>
       </c>
       <c r="C103" s="2">
-        <v>200.0</v>
+        <v>45.0</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>13</v>
@@ -2586,19 +2650,19 @@
     </row>
     <row r="104" ht="22.5" customHeight="1">
       <c r="A104" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B104" s="3">
-        <v>15600.0</v>
+        <v>9380.0</v>
       </c>
       <c r="C104" s="2">
-        <v>200.0</v>
+        <v>40.0</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>13</v>
@@ -2606,19 +2670,19 @@
     </row>
     <row r="105" ht="22.5" customHeight="1">
       <c r="A105" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B105" s="3">
-        <v>17210.0</v>
+        <v>9775.0</v>
       </c>
       <c r="C105" s="2">
-        <v>180.0</v>
+        <v>35.0</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>13</v>
@@ -2626,19 +2690,19 @@
     </row>
     <row r="106" ht="22.5" customHeight="1">
       <c r="A106" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B106" s="3">
-        <v>17350.0</v>
+        <v>9375.0</v>
       </c>
       <c r="C106" s="2">
-        <v>60.0</v>
+        <v>45.0</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>13</v>
@@ -2646,19 +2710,19 @@
     </row>
     <row r="107" ht="22.5" customHeight="1">
       <c r="A107" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B107" s="3">
-        <v>16100.0</v>
+        <v>9505.0</v>
       </c>
       <c r="C107" s="2">
-        <v>150.0</v>
+        <v>40.0</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>13</v>
@@ -2666,19 +2730,19 @@
     </row>
     <row r="108" ht="22.5" customHeight="1">
       <c r="A108" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B108" s="3">
-        <v>17520.0</v>
+        <v>9650.0</v>
       </c>
       <c r="C108" s="2">
-        <v>120.0</v>
+        <v>40.0</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>13</v>
@@ -2686,19 +2750,19 @@
     </row>
     <row r="109" ht="22.5" customHeight="1">
       <c r="A109" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B109" s="3">
-        <v>17850.0</v>
+        <v>9730.0</v>
       </c>
       <c r="C109" s="2">
-        <v>60.0</v>
+        <v>40.0</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>13</v>
@@ -2706,19 +2770,19 @@
     </row>
     <row r="110" ht="22.5" customHeight="1">
       <c r="A110" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B110" s="3">
+        <v>8970.0</v>
+      </c>
+      <c r="C110" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E110" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="B110" s="3">
-        <v>18040.0</v>
-      </c>
-      <c r="C110" s="2">
-        <v>360.0</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E110" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>13</v>
@@ -2726,39 +2790,40 @@
     </row>
     <row r="111" ht="22.5" customHeight="1">
       <c r="A111" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B111" s="3">
+        <v>9240.0</v>
+      </c>
+      <c r="C111" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E111" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B111" s="3">
-        <v>18000.0</v>
-      </c>
-      <c r="C111" s="2">
-        <v>380.0</v>
-      </c>
-      <c r="D111" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E111" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="F111" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="I111" s="5"/>
     </row>
     <row r="112" ht="22.5" customHeight="1">
       <c r="A112" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B112" s="3">
+        <v>9140.0</v>
+      </c>
+      <c r="C112" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E112" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="B112" s="3">
-        <v>16400.0</v>
-      </c>
-      <c r="C112" s="2">
-        <v>400.0</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E112" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="F112" s="2" t="s">
         <v>13</v>
@@ -2766,13 +2831,13 @@
     </row>
     <row r="113" ht="22.5" customHeight="1">
       <c r="A113" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B113" s="3">
-        <v>16850.0</v>
+        <v>9259.0</v>
       </c>
       <c r="C113" s="2">
-        <v>100.0</v>
+        <v>206.0</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>22</v>
@@ -2786,39 +2851,40 @@
     </row>
     <row r="114" ht="22.5" customHeight="1">
       <c r="A114" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B114" s="3">
-        <v>16990.0</v>
+        <v>8430.0</v>
       </c>
       <c r="C114" s="2">
-        <v>600.0</v>
+        <v>180.0</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="I114" s="5"/>
     </row>
     <row r="115" ht="22.5" customHeight="1">
       <c r="A115" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B115" s="3">
-        <v>17500.0</v>
+        <v>9710.0</v>
       </c>
       <c r="C115" s="2">
-        <v>400.0</v>
+        <v>180.0</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>13</v>
@@ -2826,19 +2892,19 @@
     </row>
     <row r="116" ht="22.5" customHeight="1">
       <c r="A116" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B116" s="3">
-        <v>19200.0</v>
+        <v>9990.0</v>
       </c>
       <c r="C116" s="2">
-        <v>100.0</v>
+        <v>50.0</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F116" s="2" t="s">
         <v>13</v>
@@ -2846,10 +2912,10 @@
     </row>
     <row r="117" ht="22.5" customHeight="1">
       <c r="A117" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B117" s="3">
-        <v>18330.0</v>
+        <v>10300.0</v>
       </c>
       <c r="C117" s="2">
         <v>200.0</v>
@@ -2858,7 +2924,7 @@
         <v>22</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>13</v>
@@ -2866,19 +2932,19 @@
     </row>
     <row r="118" ht="22.5" customHeight="1">
       <c r="A118" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B118" s="3">
-        <v>17700.0</v>
+        <v>10450.0</v>
       </c>
       <c r="C118" s="2">
-        <v>160.0</v>
+        <v>250.0</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>13</v>
@@ -2886,19 +2952,19 @@
     </row>
     <row r="119" ht="22.5" customHeight="1">
       <c r="A119" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B119" s="3">
-        <v>18100.0</v>
+        <v>12200.0</v>
       </c>
       <c r="C119" s="2">
-        <v>800.0</v>
+        <v>250.0</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>13</v>
@@ -2906,19 +2972,19 @@
     </row>
     <row r="120" ht="22.5" customHeight="1">
       <c r="A120" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B120" s="3">
-        <v>18170.0</v>
+        <v>12310.0</v>
       </c>
       <c r="C120" s="2">
-        <v>160.0</v>
+        <v>100.0</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>13</v>
@@ -2926,19 +2992,19 @@
     </row>
     <row r="121" ht="22.5" customHeight="1">
       <c r="A121" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B121" s="3">
-        <v>19560.0</v>
+        <v>11980.0</v>
       </c>
       <c r="C121" s="2">
-        <v>220.0</v>
+        <v>200.0</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F121" s="2" t="s">
         <v>13</v>
@@ -2946,19 +3012,19 @@
     </row>
     <row r="122" ht="22.5" customHeight="1">
       <c r="A122" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B122" s="3">
+        <v>14400.0</v>
+      </c>
+      <c r="C122" s="2">
+        <v>300.0</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E122" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="B122" s="3">
-        <v>11090.0</v>
-      </c>
-      <c r="C122" s="2">
-        <v>185.0</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="F122" s="2" t="s">
         <v>13</v>
@@ -2966,19 +3032,19 @@
     </row>
     <row r="123" ht="22.5" customHeight="1">
       <c r="A123" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B123" s="3">
+        <v>12300.0</v>
+      </c>
+      <c r="C123" s="2">
+        <v>300.0</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E123" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="B123" s="3">
-        <v>9905.0</v>
-      </c>
-      <c r="C123" s="2">
-        <v>150.0</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>13</v>
@@ -2986,19 +3052,19 @@
     </row>
     <row r="124" ht="22.5" customHeight="1">
       <c r="A124" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B124" s="3">
-        <v>15200.0</v>
+        <v>12370.0</v>
       </c>
       <c r="C124" s="2">
-        <v>40.0</v>
+        <v>160.0</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>13</v>
@@ -3006,19 +3072,19 @@
     </row>
     <row r="125" ht="22.5" customHeight="1">
       <c r="A125" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B125" s="3">
-        <v>14940.0</v>
+        <v>12580.0</v>
       </c>
       <c r="C125" s="2">
-        <v>50.0</v>
+        <v>220.0</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>13</v>
@@ -3026,19 +3092,19 @@
     </row>
     <row r="126" ht="22.5" customHeight="1">
       <c r="A126" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B126" s="3">
-        <v>15890.0</v>
+        <v>13190.0</v>
       </c>
       <c r="C126" s="2">
-        <v>50.0</v>
+        <v>150.0</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>13</v>
@@ -3046,19 +3112,19 @@
     </row>
     <row r="127" ht="22.5" customHeight="1">
       <c r="A127" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B127" s="3">
-        <v>16300.0</v>
+        <v>14000.0</v>
       </c>
       <c r="C127" s="2">
-        <v>50.0</v>
+        <v>300.0</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F127" s="2" t="s">
         <v>13</v>
@@ -3066,19 +3132,19 @@
     </row>
     <row r="128" ht="22.5" customHeight="1">
       <c r="A128" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B128" s="3">
-        <v>30820.0</v>
+        <v>11850.0</v>
       </c>
       <c r="C128" s="2">
-        <v>170.0</v>
+        <v>110.0</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>13</v>
@@ -3086,61 +3152,59 @@
     </row>
     <row r="129" ht="22.5" customHeight="1">
       <c r="A129" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B129" s="3">
-        <v>4250.0</v>
+        <v>13700.0</v>
       </c>
       <c r="C129" s="2">
-        <v>150.0</v>
+        <v>80.0</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I129" s="5"/>
     </row>
     <row r="130" ht="22.5" customHeight="1">
       <c r="A130" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B130" s="3">
-        <v>5590.0</v>
+        <v>14100.0</v>
       </c>
       <c r="C130" s="2">
-        <v>70.0</v>
+        <v>300.0</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I130" s="5"/>
     </row>
     <row r="131" ht="22.5" customHeight="1">
       <c r="A131" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B131" s="3">
-        <v>5940.0</v>
+        <v>15300.0</v>
       </c>
       <c r="C131" s="2">
-        <v>140.0</v>
+        <v>400.0</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>13</v>
@@ -3148,39 +3212,40 @@
     </row>
     <row r="132" ht="22.5" customHeight="1">
       <c r="A132" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B132" s="3">
-        <v>6090.0</v>
+        <v>15200.0</v>
       </c>
       <c r="C132" s="2">
-        <v>150.0</v>
+        <v>400.0</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F132" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="I132" s="5"/>
     </row>
     <row r="133" ht="22.5" customHeight="1">
       <c r="A133" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B133" s="3">
-        <v>7060.0</v>
+        <v>16180.0</v>
       </c>
       <c r="C133" s="2">
-        <v>100.0</v>
+        <v>80.0</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>13</v>
@@ -3188,19 +3253,19 @@
     </row>
     <row r="134" ht="22.5" customHeight="1">
       <c r="A134" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B134" s="3">
-        <v>8420.0</v>
+        <v>16720.0</v>
       </c>
       <c r="C134" s="2">
-        <v>90.0</v>
+        <v>300.0</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>13</v>
@@ -3208,19 +3273,19 @@
     </row>
     <row r="135" ht="22.5" customHeight="1">
       <c r="A135" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B135" s="3">
-        <v>9670.0</v>
+        <v>14370.0</v>
       </c>
       <c r="C135" s="2">
-        <v>100.0</v>
+        <v>200.0</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>13</v>
@@ -3228,19 +3293,19 @@
     </row>
     <row r="136" ht="22.5" customHeight="1">
       <c r="A136" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B136" s="3">
-        <v>9770.0</v>
+        <v>15600.0</v>
       </c>
       <c r="C136" s="2">
-        <v>100.0</v>
+        <v>200.0</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>13</v>
@@ -3248,19 +3313,19 @@
     </row>
     <row r="137" ht="22.5" customHeight="1">
       <c r="A137" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B137" s="3">
-        <v>10470.0</v>
+        <v>17210.0</v>
       </c>
       <c r="C137" s="2">
-        <v>80.0</v>
+        <v>180.0</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>13</v>
@@ -3268,19 +3333,19 @@
     </row>
     <row r="138" ht="22.5" customHeight="1">
       <c r="A138" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B138" s="3">
-        <v>11020.0</v>
+        <v>17350.0</v>
       </c>
       <c r="C138" s="2">
-        <v>150.0</v>
+        <v>60.0</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>13</v>
@@ -3288,19 +3353,19 @@
     </row>
     <row r="139" ht="22.5" customHeight="1">
       <c r="A139" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B139" s="3">
-        <v>10530.0</v>
+        <v>16100.0</v>
       </c>
       <c r="C139" s="2">
-        <v>100.0</v>
+        <v>150.0</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F139" s="2" t="s">
         <v>13</v>
@@ -3308,19 +3373,19 @@
     </row>
     <row r="140" ht="22.5" customHeight="1">
       <c r="A140" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B140" s="3">
-        <v>25800.0</v>
+        <v>17520.0</v>
       </c>
       <c r="C140" s="2">
-        <v>600.0</v>
+        <v>120.0</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>13</v>
@@ -3328,19 +3393,19 @@
     </row>
     <row r="141" ht="22.5" customHeight="1">
       <c r="A141" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B141" s="3">
-        <v>9520.0</v>
+        <v>17850.0</v>
       </c>
       <c r="C141" s="2">
-        <v>420.0</v>
+        <v>60.0</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F141" s="2" t="s">
         <v>13</v>
@@ -3348,19 +3413,19 @@
     </row>
     <row r="142" ht="22.5" customHeight="1">
       <c r="A142" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B142" s="3">
-        <v>10590.0</v>
+        <v>18040.0</v>
       </c>
       <c r="C142" s="2">
-        <v>470.0</v>
+        <v>360.0</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>13</v>
@@ -3368,19 +3433,19 @@
     </row>
     <row r="143" ht="22.5" customHeight="1">
       <c r="A143" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B143" s="3">
-        <v>10660.0</v>
+        <v>18000.0</v>
       </c>
       <c r="C143" s="2">
-        <v>480.0</v>
+        <v>380.0</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F143" s="2" t="s">
         <v>13</v>
@@ -3388,19 +3453,19 @@
     </row>
     <row r="144" ht="22.5" customHeight="1">
       <c r="A144" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B144" s="3">
-        <v>10730.0</v>
+        <v>16400.0</v>
       </c>
       <c r="C144" s="2">
-        <v>480.0</v>
+        <v>400.0</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F144" s="2" t="s">
         <v>13</v>
@@ -3408,19 +3473,19 @@
     </row>
     <row r="145" ht="22.5" customHeight="1">
       <c r="A145" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B145" s="3">
-        <v>11270.0</v>
+        <v>16850.0</v>
       </c>
       <c r="C145" s="2">
-        <v>510.0</v>
+        <v>100.0</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>13</v>
@@ -3428,19 +3493,19 @@
     </row>
     <row r="146" ht="22.5" customHeight="1">
       <c r="A146" s="2" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="B146" s="3">
-        <v>12100.0</v>
+        <v>16990.0</v>
       </c>
       <c r="C146" s="2">
-        <v>60.0</v>
+        <v>600.0</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="F146" s="2" t="s">
         <v>13</v>
@@ -3448,19 +3513,19 @@
     </row>
     <row r="147" ht="22.5" customHeight="1">
       <c r="A147" s="2" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="B147" s="3">
-        <v>13640.0</v>
+        <v>17500.0</v>
       </c>
       <c r="C147" s="2">
-        <v>80.0</v>
+        <v>400.0</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="F147" s="2" t="s">
         <v>13</v>
@@ -3468,19 +3533,19 @@
     </row>
     <row r="148" ht="22.5" customHeight="1">
       <c r="A148" s="2" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="B148" s="3">
-        <v>24920.0</v>
+        <v>19200.0</v>
       </c>
       <c r="C148" s="2">
-        <v>200.0</v>
+        <v>100.0</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>13</v>
@@ -3488,19 +3553,19 @@
     </row>
     <row r="149" ht="22.5" customHeight="1">
       <c r="A149" s="2" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="B149" s="3">
-        <v>13599.0</v>
+        <v>18330.0</v>
       </c>
       <c r="C149" s="2">
-        <v>79.0</v>
+        <v>200.0</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>13</v>
@@ -3508,19 +3573,19 @@
     </row>
     <row r="150" ht="22.5" customHeight="1">
       <c r="A150" s="2" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="B150" s="3">
-        <v>22190.0</v>
+        <v>17700.0</v>
       </c>
       <c r="C150" s="2">
         <v>160.0</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>13</v>
@@ -3528,19 +3593,19 @@
     </row>
     <row r="151" ht="22.5" customHeight="1">
       <c r="A151" s="2" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="B151" s="3">
-        <v>16750.0</v>
+        <v>18100.0</v>
       </c>
       <c r="C151" s="2">
-        <v>70.0</v>
+        <v>800.0</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="F151" s="2" t="s">
         <v>13</v>
@@ -3548,19 +3613,19 @@
     </row>
     <row r="152" ht="22.5" customHeight="1">
       <c r="A152" s="2" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="B152" s="3">
-        <v>15360.0</v>
+        <v>18170.0</v>
       </c>
       <c r="C152" s="2">
-        <v>70.0</v>
+        <v>160.0</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>13</v>
@@ -3568,19 +3633,19 @@
     </row>
     <row r="153" ht="22.5" customHeight="1">
       <c r="A153" s="2" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="B153" s="3">
-        <v>19880.0</v>
+        <v>19560.0</v>
       </c>
       <c r="C153" s="2">
-        <v>90.0</v>
+        <v>220.0</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="F153" s="2" t="s">
         <v>13</v>
@@ -3588,19 +3653,19 @@
     </row>
     <row r="154" ht="22.5" customHeight="1">
       <c r="A154" s="2" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="B154" s="3">
-        <v>27620.0</v>
+        <v>11090.0</v>
       </c>
       <c r="C154" s="2">
-        <v>170.0</v>
+        <v>185.0</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>13</v>
@@ -3608,31 +3673,2340 @@
     </row>
     <row r="155" ht="22.5" customHeight="1">
       <c r="A155" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B155" s="3">
+        <v>9905.0</v>
+      </c>
+      <c r="C155" s="2">
+        <v>150.0</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F155" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="156" ht="22.5" customHeight="1">
+      <c r="A156" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B156" s="3">
+        <v>15200.0</v>
+      </c>
+      <c r="C156" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="157" ht="22.5" customHeight="1">
+      <c r="A157" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B157" s="3">
+        <v>14940.0</v>
+      </c>
+      <c r="C157" s="2">
+        <v>50.0</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="158" ht="22.5" customHeight="1">
+      <c r="A158" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B158" s="3">
+        <v>15890.0</v>
+      </c>
+      <c r="C158" s="2">
+        <v>50.0</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="159" ht="22.5" customHeight="1">
+      <c r="A159" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B159" s="3">
+        <v>16300.0</v>
+      </c>
+      <c r="C159" s="2">
+        <v>50.0</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="160" ht="22.5" customHeight="1">
+      <c r="A160" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B160" s="3">
+        <v>30820.0</v>
+      </c>
+      <c r="C160" s="2">
+        <v>170.0</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="161" ht="22.5" customHeight="1">
+      <c r="A161" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B161" s="3">
+        <v>4250.0</v>
+      </c>
+      <c r="C161" s="2">
+        <v>150.0</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I161" s="5"/>
+    </row>
+    <row r="162" ht="22.5" customHeight="1">
+      <c r="A162" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B162" s="3">
+        <v>5590.0</v>
+      </c>
+      <c r="C162" s="2">
+        <v>70.0</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I162" s="5"/>
+    </row>
+    <row r="163" ht="22.5" customHeight="1">
+      <c r="A163" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B163" s="3">
+        <v>5940.0</v>
+      </c>
+      <c r="C163" s="2">
+        <v>140.0</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="164" ht="22.5" customHeight="1">
+      <c r="A164" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B164" s="3">
+        <v>6090.0</v>
+      </c>
+      <c r="C164" s="2">
+        <v>150.0</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F164" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="165" ht="22.5" customHeight="1">
+      <c r="A165" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B165" s="3">
+        <v>7060.0</v>
+      </c>
+      <c r="C165" s="2">
+        <v>100.0</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="166" ht="22.5" customHeight="1">
+      <c r="A166" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B166" s="3">
+        <v>8420.0</v>
+      </c>
+      <c r="C166" s="2">
+        <v>90.0</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="167" ht="22.5" customHeight="1">
+      <c r="A167" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B167" s="3">
+        <v>9670.0</v>
+      </c>
+      <c r="C167" s="2">
+        <v>100.0</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="168" ht="22.5" customHeight="1">
+      <c r="A168" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B168" s="3">
+        <v>9770.0</v>
+      </c>
+      <c r="C168" s="2">
+        <v>100.0</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="169" ht="22.5" customHeight="1">
+      <c r="A169" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B169" s="3">
+        <v>10470.0</v>
+      </c>
+      <c r="C169" s="2">
+        <v>80.0</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="170" ht="22.5" customHeight="1">
+      <c r="A170" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B170" s="3">
+        <v>11020.0</v>
+      </c>
+      <c r="C170" s="2">
+        <v>150.0</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F170" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="171" ht="22.5" customHeight="1">
+      <c r="A171" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B171" s="3">
+        <v>10530.0</v>
+      </c>
+      <c r="C171" s="2">
+        <v>100.0</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F171" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="172" ht="22.5" customHeight="1">
+      <c r="A172" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B172" s="3">
+        <v>25800.0</v>
+      </c>
+      <c r="C172" s="2">
+        <v>600.0</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="173" ht="22.5" customHeight="1">
+      <c r="A173" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B173" s="3">
+        <v>9520.0</v>
+      </c>
+      <c r="C173" s="2">
+        <v>420.0</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F173" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="174" ht="22.5" customHeight="1">
+      <c r="A174" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B174" s="3">
+        <v>10590.0</v>
+      </c>
+      <c r="C174" s="2">
+        <v>470.0</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F174" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="175" ht="22.5" customHeight="1">
+      <c r="A175" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B175" s="3">
+        <v>10660.0</v>
+      </c>
+      <c r="C175" s="2">
+        <v>480.0</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F175" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="176" ht="22.5" customHeight="1">
+      <c r="A176" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B176" s="3">
+        <v>10730.0</v>
+      </c>
+      <c r="C176" s="2">
+        <v>480.0</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F176" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="177" ht="22.5" customHeight="1">
+      <c r="A177" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B177" s="3">
+        <v>11270.0</v>
+      </c>
+      <c r="C177" s="2">
+        <v>510.0</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F177" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="178" ht="22.5" customHeight="1">
+      <c r="A178" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B155" s="3">
+      <c r="B178" s="3">
+        <v>12100.0</v>
+      </c>
+      <c r="C178" s="2">
+        <v>60.0</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F178" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="179" ht="22.5" customHeight="1">
+      <c r="A179" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B179" s="3">
+        <v>13640.0</v>
+      </c>
+      <c r="C179" s="2">
+        <v>80.0</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F179" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="180" ht="22.5" customHeight="1">
+      <c r="A180" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B180" s="3">
+        <v>24920.0</v>
+      </c>
+      <c r="C180" s="2">
+        <v>200.0</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F180" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="181" ht="22.5" customHeight="1">
+      <c r="A181" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B181" s="3">
+        <v>13599.0</v>
+      </c>
+      <c r="C181" s="2">
+        <v>79.0</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F181" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="182" ht="22.5" customHeight="1">
+      <c r="A182" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B182" s="3">
+        <v>22190.0</v>
+      </c>
+      <c r="C182" s="2">
+        <v>160.0</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F182" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="183" ht="22.5" customHeight="1">
+      <c r="A183" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B183" s="3">
+        <v>16750.0</v>
+      </c>
+      <c r="C183" s="2">
+        <v>70.0</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F183" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="184" ht="22.5" customHeight="1">
+      <c r="A184" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B184" s="3">
+        <v>15360.0</v>
+      </c>
+      <c r="C184" s="2">
+        <v>70.0</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F184" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="185" ht="22.5" customHeight="1">
+      <c r="A185" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B185" s="3">
+        <v>19880.0</v>
+      </c>
+      <c r="C185" s="2">
+        <v>90.0</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F185" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="186" ht="22.5" customHeight="1">
+      <c r="A186" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B186" s="3">
+        <v>27620.0</v>
+      </c>
+      <c r="C186" s="2">
+        <v>170.0</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F186" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="187" ht="22.5" customHeight="1">
+      <c r="A187" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B187" s="3">
         <v>26580.0</v>
       </c>
-      <c r="C155" s="2">
+      <c r="C187" s="2">
         <v>250.0</v>
       </c>
-      <c r="D155" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E155" s="2" t="s">
+      <c r="D187" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E187" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="F155" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="156" ht="22.5" customHeight="1">
-      <c r="A156" s="2"/>
-      <c r="B156" s="3"/>
-      <c r="C156" s="2"/>
-      <c r="D156" s="2"/>
-      <c r="E156" s="2"/>
-      <c r="F156" s="2"/>
+      <c r="F187" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H187" s="5"/>
+    </row>
+    <row r="188" ht="22.5" customHeight="1">
+      <c r="A188" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B188" s="3">
+        <v>12140.0</v>
+      </c>
+      <c r="C188" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F188" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="189" ht="22.5" customHeight="1">
+      <c r="A189" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B189" s="3">
+        <v>13030.0</v>
+      </c>
+      <c r="C189" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F189" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="190" ht="22.5" customHeight="1">
+      <c r="A190" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B190" s="3">
+        <v>12980.0</v>
+      </c>
+      <c r="C190" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F190" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="191" ht="22.5" customHeight="1">
+      <c r="A191" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B191" s="3">
+        <v>12900.0</v>
+      </c>
+      <c r="C191" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F191" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="192" ht="22.5" customHeight="1">
+      <c r="A192" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B192" s="3">
+        <v>13420.0</v>
+      </c>
+      <c r="C192" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F192" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="193" ht="22.5" customHeight="1">
+      <c r="A193" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B193" s="3">
+        <v>13530.0</v>
+      </c>
+      <c r="C193" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F193" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="194" ht="22.5" customHeight="1">
+      <c r="A194" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B194" s="3">
+        <v>13910.0</v>
+      </c>
+      <c r="C194" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F194" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H194" s="5"/>
+    </row>
+    <row r="195" ht="22.5" customHeight="1">
+      <c r="A195" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B195" s="3">
+        <v>13990.0</v>
+      </c>
+      <c r="C195" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F195" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="196" ht="22.5" customHeight="1">
+      <c r="A196" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B196" s="3">
+        <v>6880.0</v>
+      </c>
+      <c r="C196" s="2">
+        <v>125.0</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F196" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="197" ht="22.5" customHeight="1">
+      <c r="A197" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B197" s="3">
+        <v>9250.0</v>
+      </c>
+      <c r="C197" s="2">
+        <v>90.0</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F197" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="198" ht="22.5" customHeight="1">
+      <c r="A198" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B198" s="3">
+        <v>10840.0</v>
+      </c>
+      <c r="C198" s="2">
+        <v>580.0</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E198" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F198" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="199" ht="22.5" customHeight="1">
+      <c r="A199" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B199" s="3">
+        <v>13905.0</v>
+      </c>
+      <c r="C199" s="2">
+        <v>250.0</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E199" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F199" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="200" ht="22.5" customHeight="1">
+      <c r="A200" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B200" s="3">
+        <v>14240.0</v>
+      </c>
+      <c r="C200" s="2">
+        <v>230.0</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F200" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="201" ht="22.5" customHeight="1">
+      <c r="A201" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B201" s="3">
+        <v>11670.0</v>
+      </c>
+      <c r="C201" s="2">
+        <v>150.0</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F201" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="202" ht="22.5" customHeight="1">
+      <c r="A202" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B202" s="3">
+        <v>19090.0</v>
+      </c>
+      <c r="C202" s="2">
+        <v>200.0</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F202" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="203" ht="22.5" customHeight="1">
+      <c r="A203" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B203" s="3">
+        <v>20240.0</v>
+      </c>
+      <c r="C203" s="2">
+        <v>660.0</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F203" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="204" ht="22.5" customHeight="1">
+      <c r="A204" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B204" s="3">
+        <v>10020.0</v>
+      </c>
+      <c r="C204" s="2">
+        <v>290.0</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F204" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="205" ht="22.5" customHeight="1">
+      <c r="A205" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B205" s="3">
+        <v>17680.0</v>
+      </c>
+      <c r="C205" s="2">
+        <v>300.0</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F205" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="206" ht="22.5" customHeight="1">
+      <c r="A206" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B206" s="3">
+        <v>12420.0</v>
+      </c>
+      <c r="C206" s="2">
+        <v>180.0</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F206" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="207" ht="22.5" customHeight="1">
+      <c r="A207" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B207" s="3">
+        <v>19145.0</v>
+      </c>
+      <c r="C207" s="2">
+        <v>180.0</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F207" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="208" ht="22.5" customHeight="1">
+      <c r="A208" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B208" s="3">
+        <v>17930.0</v>
+      </c>
+      <c r="C208" s="2">
+        <v>410.0</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F208" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="209" ht="22.5" customHeight="1">
+      <c r="A209" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B209" s="3">
+        <v>20960.0</v>
+      </c>
+      <c r="C209" s="2">
+        <v>150.0</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F209" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="210" ht="22.5" customHeight="1">
+      <c r="A210" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B210" s="3">
+        <v>25920.0</v>
+      </c>
+      <c r="C210" s="2">
+        <v>625.0</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F210" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="211" ht="22.5" customHeight="1">
+      <c r="A211" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B211" s="3">
+        <v>9500.0</v>
+      </c>
+      <c r="C211" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F211" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H211" s="5"/>
+    </row>
+    <row r="212" ht="22.5" customHeight="1">
+      <c r="A212" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B212" s="3">
+        <v>9230.0</v>
+      </c>
+      <c r="C212" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F212" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H212" s="5"/>
+    </row>
+    <row r="213" ht="22.5" customHeight="1">
+      <c r="A213" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B213" s="3">
+        <v>9080.0</v>
+      </c>
+      <c r="C213" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F213" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H213" s="5"/>
+    </row>
+    <row r="214" ht="22.5" customHeight="1">
+      <c r="A214" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B214" s="3">
+        <v>9190.0</v>
+      </c>
+      <c r="C214" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F214" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H214" s="5"/>
+    </row>
+    <row r="215" ht="22.5" customHeight="1">
+      <c r="A215" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B215" s="3">
+        <v>10350.0</v>
+      </c>
+      <c r="C215" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F215" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H215" s="5"/>
+    </row>
+    <row r="216" ht="22.5" customHeight="1">
+      <c r="A216" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B216" s="3">
+        <v>14090.0</v>
+      </c>
+      <c r="C216" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F216" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H216" s="5"/>
+    </row>
+    <row r="217" ht="22.5" customHeight="1">
+      <c r="A217" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B217" s="3">
+        <v>19530.0</v>
+      </c>
+      <c r="C217" s="2">
+        <v>60.0</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E217" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F217" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H217" s="5"/>
+    </row>
+    <row r="218" ht="22.5" customHeight="1">
+      <c r="A218" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B218" s="3">
+        <v>33430.0</v>
+      </c>
+      <c r="C218" s="2">
+        <v>220.0</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F218" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H218" s="5"/>
+    </row>
+    <row r="219" ht="22.5" customHeight="1">
+      <c r="A219" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B219" s="3">
+        <v>36000.0</v>
+      </c>
+      <c r="C219" s="2">
+        <v>2000.0</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F219" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H219" s="5"/>
+    </row>
+    <row r="220" ht="22.5" customHeight="1">
+      <c r="A220" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B220" s="3">
+        <v>13170.0</v>
+      </c>
+      <c r="C220" s="2">
+        <v>590.0</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F220" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="221" ht="22.5" customHeight="1">
+      <c r="A221" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B221" s="3">
+        <v>8750.0</v>
+      </c>
+      <c r="C221" s="2">
+        <v>60.0</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F221" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="222" ht="22.5" customHeight="1">
+      <c r="A222" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B222" s="3">
+        <v>8800.0</v>
+      </c>
+      <c r="C222" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F222" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="223" ht="22.5" customHeight="1">
+      <c r="A223" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B223" s="3">
+        <v>7350.0</v>
+      </c>
+      <c r="C223" s="2">
+        <v>60.0</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F223" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="224" ht="22.5" customHeight="1">
+      <c r="A224" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B224" s="3">
+        <v>8745.0</v>
+      </c>
+      <c r="C224" s="2">
+        <v>60.0</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F224" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="225" ht="22.5" customHeight="1">
+      <c r="A225" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B225" s="3">
+        <v>9000.0</v>
+      </c>
+      <c r="C225" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F225" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="226" ht="22.5" customHeight="1">
+      <c r="A226" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B226" s="3">
+        <v>3700.0</v>
+      </c>
+      <c r="C226" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F226" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H226" s="5"/>
+    </row>
+    <row r="227" ht="22.5" customHeight="1">
+      <c r="A227" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B227" s="3">
+        <v>1205.0</v>
+      </c>
+      <c r="C227" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E227" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F227" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="228" ht="22.5" customHeight="1">
+      <c r="A228" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B228" s="3">
+        <v>13340.0</v>
+      </c>
+      <c r="C228" s="2">
+        <v>50.0</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F228" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="229" ht="22.5" customHeight="1">
+      <c r="A229" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B229" s="3">
+        <v>13500.0</v>
+      </c>
+      <c r="C229" s="2">
+        <v>50.0</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E229" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F229" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="230" ht="22.5" customHeight="1">
+      <c r="A230" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B230" s="3">
+        <v>13445.0</v>
+      </c>
+      <c r="C230" s="2">
+        <v>50.0</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F230" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="231" ht="22.5" customHeight="1">
+      <c r="A231" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B231" s="3">
+        <v>20310.0</v>
+      </c>
+      <c r="C231" s="2">
+        <v>70.0</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F231" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="232" ht="22.5" customHeight="1">
+      <c r="A232" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B232" s="3">
+        <v>20470.0</v>
+      </c>
+      <c r="C232" s="2">
+        <v>70.0</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F232" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="233" ht="22.5" customHeight="1">
+      <c r="A233" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B233" s="3">
+        <v>21100.0</v>
+      </c>
+      <c r="C233" s="2">
+        <v>100.0</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E233" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F233" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="234" ht="22.5" customHeight="1">
+      <c r="A234" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B234" s="3">
+        <v>32050.0</v>
+      </c>
+      <c r="C234" s="2">
+        <v>190.0</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F234" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="235" ht="22.5" customHeight="1">
+      <c r="A235" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B235" s="3">
+        <v>7810.0</v>
+      </c>
+      <c r="C235" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E235" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F235" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="236" ht="22.5" customHeight="1">
+      <c r="A236" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B236" s="3">
+        <v>7735.0</v>
+      </c>
+      <c r="C236" s="2">
+        <v>35.0</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E236" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F236" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H236" s="5"/>
+    </row>
+    <row r="237" ht="22.5" customHeight="1">
+      <c r="A237" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B237" s="3">
+        <v>8010.0</v>
+      </c>
+      <c r="C237" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E237" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F237" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="238" ht="22.5" customHeight="1">
+      <c r="A238" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B238" s="3">
+        <v>8970.0</v>
+      </c>
+      <c r="C238" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F238" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="239" ht="22.5" customHeight="1">
+      <c r="A239" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B239" s="3">
+        <v>8015.0</v>
+      </c>
+      <c r="C239" s="2">
+        <v>45.0</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E239" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F239" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="240" ht="22.5" customHeight="1">
+      <c r="A240" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B240" s="3">
+        <v>9220.0</v>
+      </c>
+      <c r="C240" s="2">
+        <v>30.0</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F240" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="241" ht="22.5" customHeight="1">
+      <c r="A241" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B241" s="3">
+        <v>10780.0</v>
+      </c>
+      <c r="C241" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E241" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F241" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="242" ht="22.5" customHeight="1">
+      <c r="A242" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B242" s="3">
+        <v>9980.0</v>
+      </c>
+      <c r="C242" s="2">
+        <v>60.0</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E242" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F242" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="243" ht="22.5" customHeight="1">
+      <c r="A243" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B243" s="3">
+        <v>11280.0</v>
+      </c>
+      <c r="C243" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E243" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F243" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="244" ht="22.5" customHeight="1">
+      <c r="A244" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B244" s="3">
+        <v>11020.0</v>
+      </c>
+      <c r="C244" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F244" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="245" ht="22.5" customHeight="1">
+      <c r="A245" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B245" s="3">
+        <v>12335.0</v>
+      </c>
+      <c r="C245" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F245" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="246" ht="22.5" customHeight="1">
+      <c r="A246" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B246" s="3">
+        <v>10014.0</v>
+      </c>
+      <c r="C246" s="2">
+        <v>64.0</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F246" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="247" ht="22.5" customHeight="1">
+      <c r="A247" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B247" s="3">
+        <v>11425.0</v>
+      </c>
+      <c r="C247" s="2">
+        <v>50.0</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E247" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F247" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="248" ht="22.5" customHeight="1">
+      <c r="A248" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B248" s="3">
+        <v>11527.0</v>
+      </c>
+      <c r="C248" s="2">
+        <v>51.0</v>
+      </c>
+      <c r="D248" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E248" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F248" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H248" s="5"/>
+    </row>
+    <row r="249" ht="22.5" customHeight="1">
+      <c r="A249" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B249" s="3">
+        <v>11675.0</v>
+      </c>
+      <c r="C249" s="2">
+        <v>52.0</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F249" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="250" ht="22.5" customHeight="1">
+      <c r="A250" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B250" s="3">
+        <v>11874.0</v>
+      </c>
+      <c r="C250" s="2">
+        <v>49.0</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F250" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="251" ht="22.5" customHeight="1">
+      <c r="A251" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B251" s="3">
+        <v>11749.0</v>
+      </c>
+      <c r="C251" s="2">
+        <v>49.0</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E251" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F251" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="252" ht="22.5" customHeight="1">
+      <c r="A252" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B252" s="3">
+        <v>12037.0</v>
+      </c>
+      <c r="C252" s="2">
+        <v>54.0</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E252" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F252" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="253" ht="22.5" customHeight="1">
+      <c r="A253" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B253" s="3">
+        <v>11982.0</v>
+      </c>
+      <c r="C253" s="2">
+        <v>78.0</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E253" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F253" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="254" ht="22.5" customHeight="1">
+      <c r="A254" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B254" s="3">
+        <v>12020.0</v>
+      </c>
+      <c r="C254" s="2">
+        <v>54.0</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E254" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F254" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="255" ht="22.5" customHeight="1">
+      <c r="A255" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B255" s="3">
+        <v>12137.0</v>
+      </c>
+      <c r="C255" s="2">
+        <v>51.0</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E255" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F255" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="256" ht="22.5" customHeight="1">
+      <c r="A256" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B256" s="3">
+        <v>12430.0</v>
+      </c>
+      <c r="C256" s="2">
+        <v>57.0</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E256" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F256" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="257" ht="22.5" customHeight="1">
+      <c r="A257" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B257" s="3">
+        <v>12304.0</v>
+      </c>
+      <c r="C257" s="2">
+        <v>59.0</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E257" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F257" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="258" ht="22.5" customHeight="1">
+      <c r="A258" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B258" s="3">
+        <v>13490.0</v>
+      </c>
+      <c r="C258" s="2">
+        <v>65.0</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E258" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F258" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="259" ht="22.5" customHeight="1">
+      <c r="A259" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B259" s="3">
+        <v>13683.0</v>
+      </c>
+      <c r="C259" s="2">
+        <v>62.0</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E259" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F259" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="260" ht="22.5" customHeight="1">
+      <c r="A260" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B260" s="3">
+        <v>14699.0</v>
+      </c>
+      <c r="C260" s="2">
+        <v>65.0</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E260" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F260" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="261" ht="22.5" customHeight="1">
+      <c r="A261" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B261" s="3">
+        <v>20000.0</v>
+      </c>
+      <c r="C261" s="2">
+        <v>117.0</v>
+      </c>
+      <c r="D261" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E261" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F261" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="262" ht="22.5" customHeight="1">
+      <c r="A262" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B262" s="3">
+        <v>29318.0</v>
+      </c>
+      <c r="C262" s="2">
+        <v>366.0</v>
+      </c>
+      <c r="D262" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E262" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F262" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H262" s="5"/>
+    </row>
+    <row r="263" ht="22.5" customHeight="1">
+      <c r="A263" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B263" s="3">
+        <v>34029.0</v>
+      </c>
+      <c r="C263" s="2">
+        <v>598.0</v>
+      </c>
+      <c r="D263" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E263" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F263" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="264" ht="22.5" customHeight="1">
+      <c r="A264" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B264" s="3">
+        <v>7040.0</v>
+      </c>
+      <c r="C264" s="2">
+        <v>60.0</v>
+      </c>
+      <c r="D264" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E264" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F264" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="265" ht="22.5" customHeight="1">
+      <c r="A265" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B265" s="3">
+        <v>6600.0</v>
+      </c>
+      <c r="C265" s="2">
+        <v>70.0</v>
+      </c>
+      <c r="D265" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E265" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F265" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="266" ht="22.5" customHeight="1">
+      <c r="A266" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B266" s="3">
+        <v>6850.0</v>
+      </c>
+      <c r="C266" s="2">
+        <v>70.0</v>
+      </c>
+      <c r="D266" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E266" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F266" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="267" ht="22.5" customHeight="1">
+      <c r="A267" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B267" s="3">
+        <v>7950.0</v>
+      </c>
+      <c r="C267" s="2">
+        <v>70.0</v>
+      </c>
+      <c r="D267" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E267" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F267" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="268" ht="22.5" customHeight="1">
+      <c r="A268" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B268" s="3">
+        <v>7250.0</v>
+      </c>
+      <c r="C268" s="2">
+        <v>40.0</v>
+      </c>
+      <c r="D268" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E268" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F268" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="269" ht="22.5" customHeight="1">
+      <c r="A269" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B269" s="3">
+        <v>8850.0</v>
+      </c>
+      <c r="C269" s="2">
+        <v>50.0</v>
+      </c>
+      <c r="D269" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E269" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F269" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="270" ht="22.5" customHeight="1">
+      <c r="A270" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B270" s="3">
+        <v>8190.0</v>
+      </c>
+      <c r="C270" s="2">
+        <v>50.0</v>
+      </c>
+      <c r="D270" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E270" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F270" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/Demographic analysis sites.xlsx
+++ b/Demographic analysis sites.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1190" uniqueCount="132">
   <si>
     <t>Site</t>
   </si>
@@ -253,6 +253,12 @@
     <t>Citation</t>
   </si>
   <si>
+    <t>Abbreviation</t>
+  </si>
+  <si>
+    <t>Condition</t>
+  </si>
+  <si>
     <t>Younger Dryas</t>
   </si>
   <si>
@@ -262,12 +268,24 @@
     <t>Rasmussen et al. 2006</t>
   </si>
   <si>
+    <t>YD</t>
+  </si>
+  <si>
+    <t>cooler</t>
+  </si>
+  <si>
     <t>Bølling–Allerød Interstadial</t>
   </si>
   <si>
     <t>Warmer period, GI-1</t>
   </si>
   <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>warmer</t>
+  </si>
+  <si>
     <t>Oldest Dryas</t>
   </si>
   <si>
@@ -277,6 +295,9 @@
     <t>Shakun and Carlson 2010</t>
   </si>
   <si>
+    <t>OD</t>
+  </si>
+  <si>
     <t>Last Glacial Maximum</t>
   </si>
   <si>
@@ -286,6 +307,9 @@
     <t>Clark et al. 2009</t>
   </si>
   <si>
+    <t>LGM</t>
+  </si>
+  <si>
     <t>Heinrich event 1</t>
   </si>
   <si>
@@ -295,16 +319,31 @@
     <t>Hemming 2004</t>
   </si>
   <si>
+    <t>H1</t>
+  </si>
+  <si>
     <t>Heinrich event 2</t>
   </si>
   <si>
+    <t>H2</t>
+  </si>
+  <si>
     <t>Heinrich event 3</t>
   </si>
   <si>
+    <t>H3</t>
+  </si>
+  <si>
     <t>Heinrich event 4</t>
   </si>
   <si>
+    <t>H4</t>
+  </si>
+  <si>
     <t>Heinrich event 5</t>
+  </si>
+  <si>
+    <t>H5</t>
   </si>
   <si>
     <t>MIS 3</t>
@@ -409,7 +448,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -439,6 +478,12 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -545,13 +590,15 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:E1001" displayName="Table2" name="Table2" id="2">
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:G1001" displayName="Table2" name="Table2" id="2">
+  <tableColumns count="7">
     <tableColumn name="Climate event" id="1"/>
     <tableColumn name="Start year" id="2"/>
     <tableColumn name="End year" id="3"/>
     <tableColumn name="Comment" id="4"/>
     <tableColumn name="Citation" id="5"/>
+    <tableColumn name="Abbreviation" id="6"/>
+    <tableColumn name="Condition" id="7"/>
   </tableColumns>
   <tableStyleInfo name="climate_events-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
@@ -7773,10 +7820,16 @@
       <c r="E1" s="8" t="s">
         <v>78</v>
       </c>
+      <c r="F1" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B2" s="9">
         <v>12900.0</v>
@@ -7785,15 +7838,21 @@
         <v>11700.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B3" s="9">
         <v>14700.0</v>
@@ -7802,15 +7861,21 @@
         <v>12900.0</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>81</v>
+      <c r="F3" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B4" s="9">
         <v>18000.0</v>
@@ -7819,15 +7884,21 @@
         <v>14700.0</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>85</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B5" s="9">
         <v>26500.0</v>
@@ -7836,15 +7907,21 @@
         <v>19000.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>89</v>
+        <v>96</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="B6" s="3">
         <v>16800.0</v>
@@ -7853,15 +7930,19 @@
         <v>16800.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>92</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="G6" s="10"/>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="B7" s="3">
         <v>24000.0</v>
@@ -7870,12 +7951,16 @@
         <v>24000.0</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>92</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="G7" s="10"/>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="B8" s="3">
         <v>31000.0</v>
@@ -7884,12 +7969,16 @@
         <v>31000.0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>92</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="G8" s="10"/>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="B9" s="3">
         <v>38000.0</v>
@@ -7898,12 +7987,16 @@
         <v>38000.0</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>92</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="G9" s="10"/>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="B10" s="3">
         <v>45000.0</v>
@@ -7912,12 +8005,16 @@
         <v>45000.0</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>92</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G10" s="10"/>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="B11" s="3">
         <v>57000.0</v>
@@ -7926,15 +8023,19 @@
         <v>29000.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>99</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="G11" s="10"/>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="B12" s="3">
         <v>29000.0</v>
@@ -7943,15 +8044,21 @@
         <v>11700.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>99</v>
+        <v>112</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="B13" s="3">
         <v>11170.0</v>
@@ -7960,15 +8067,19 @@
         <v>0.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>99</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="G13" s="10"/>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="B14" s="3">
         <v>8400.0</v>
@@ -7977,15 +8088,21 @@
         <v>8000.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>105</v>
+        <v>118</v>
+      </c>
+      <c r="F14" s="5">
+        <v>8.2</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="B15" s="3">
         <v>23340.0</v>
@@ -7994,15 +8111,21 @@
         <v>23240.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>108</v>
+        <v>121</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="B16" s="3">
         <v>27780.0</v>
@@ -8011,15 +8134,21 @@
         <v>27480.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>108</v>
+        <v>121</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="G16" s="5" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="B17" s="3">
         <v>28900.0</v>
@@ -8028,15 +8157,21 @@
         <v>28600.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>108</v>
+        <v>121</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="B18" s="3">
         <v>32500.0</v>
@@ -8045,15 +8180,21 @@
         <v>32000.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>108</v>
+        <v>121</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="B19" s="3">
         <v>33740.0</v>
@@ -8062,15 +8203,21 @@
         <v>33440.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>108</v>
+        <v>121</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="B20" s="3">
         <v>35480.0</v>
@@ -8079,15 +8226,21 @@
         <v>34780.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>108</v>
+        <v>121</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="G20" s="5" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="B21" s="3">
         <v>38220.0</v>
@@ -8096,15 +8249,21 @@
         <v>36620.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>108</v>
+        <v>121</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="B22" s="3">
         <v>40160.0</v>
@@ -8113,15 +8272,21 @@
         <v>39860.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>108</v>
+        <v>121</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="B23" s="3">
         <v>41460.0</v>
@@ -8130,15 +8295,21 @@
         <v>40760.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>108</v>
+        <v>121</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="B24" s="3">
         <v>43340.0</v>
@@ -8147,15 +8318,21 @@
         <v>42340.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>108</v>
+        <v>121</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="B25" s="3">
         <v>46860.0</v>
@@ -8164,988 +8341,3920 @@
         <v>44260.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="26" ht="22.5" customHeight="1"/>
-    <row r="27" ht="22.5" customHeight="1"/>
-    <row r="28" ht="22.5" customHeight="1"/>
-    <row r="29" ht="22.5" customHeight="1"/>
-    <row r="30" ht="22.5" customHeight="1"/>
-    <row r="31" ht="22.5" customHeight="1"/>
-    <row r="32" ht="22.5" customHeight="1"/>
-    <row r="33" ht="22.5" customHeight="1"/>
-    <row r="34" ht="22.5" customHeight="1"/>
-    <row r="35" ht="22.5" customHeight="1"/>
-    <row r="36" ht="22.5" customHeight="1"/>
-    <row r="37" ht="22.5" customHeight="1"/>
-    <row r="38" ht="22.5" customHeight="1"/>
-    <row r="39" ht="22.5" customHeight="1"/>
-    <row r="40" ht="22.5" customHeight="1"/>
-    <row r="41" ht="22.5" customHeight="1"/>
-    <row r="42" ht="22.5" customHeight="1"/>
-    <row r="43" ht="22.5" customHeight="1"/>
-    <row r="44" ht="22.5" customHeight="1"/>
-    <row r="45" ht="22.5" customHeight="1"/>
-    <row r="46" ht="22.5" customHeight="1"/>
-    <row r="47" ht="22.5" customHeight="1"/>
-    <row r="48" ht="22.5" customHeight="1"/>
-    <row r="49" ht="22.5" customHeight="1"/>
-    <row r="50" ht="22.5" customHeight="1"/>
-    <row r="51" ht="22.5" customHeight="1"/>
-    <row r="52" ht="22.5" customHeight="1"/>
-    <row r="53" ht="22.5" customHeight="1"/>
-    <row r="54" ht="22.5" customHeight="1"/>
-    <row r="55" ht="22.5" customHeight="1"/>
-    <row r="56" ht="22.5" customHeight="1"/>
-    <row r="57" ht="22.5" customHeight="1"/>
-    <row r="58" ht="22.5" customHeight="1"/>
-    <row r="59" ht="22.5" customHeight="1"/>
-    <row r="60" ht="22.5" customHeight="1"/>
-    <row r="61" ht="22.5" customHeight="1"/>
-    <row r="62" ht="22.5" customHeight="1"/>
-    <row r="63" ht="22.5" customHeight="1"/>
-    <row r="64" ht="22.5" customHeight="1"/>
-    <row r="65" ht="22.5" customHeight="1"/>
-    <row r="66" ht="22.5" customHeight="1"/>
-    <row r="67" ht="22.5" customHeight="1"/>
-    <row r="68" ht="22.5" customHeight="1"/>
-    <row r="69" ht="22.5" customHeight="1"/>
-    <row r="70" ht="22.5" customHeight="1"/>
-    <row r="71" ht="22.5" customHeight="1"/>
-    <row r="72" ht="22.5" customHeight="1"/>
-    <row r="73" ht="22.5" customHeight="1"/>
-    <row r="74" ht="22.5" customHeight="1"/>
-    <row r="75" ht="22.5" customHeight="1"/>
-    <row r="76" ht="22.5" customHeight="1"/>
-    <row r="77" ht="22.5" customHeight="1"/>
-    <row r="78" ht="22.5" customHeight="1"/>
-    <row r="79" ht="22.5" customHeight="1"/>
-    <row r="80" ht="22.5" customHeight="1"/>
-    <row r="81" ht="22.5" customHeight="1"/>
-    <row r="82" ht="22.5" customHeight="1"/>
-    <row r="83" ht="22.5" customHeight="1"/>
-    <row r="84" ht="22.5" customHeight="1"/>
-    <row r="85" ht="22.5" customHeight="1"/>
-    <row r="86" ht="22.5" customHeight="1"/>
-    <row r="87" ht="22.5" customHeight="1"/>
-    <row r="88" ht="22.5" customHeight="1"/>
-    <row r="89" ht="22.5" customHeight="1"/>
-    <row r="90" ht="22.5" customHeight="1"/>
-    <row r="91" ht="22.5" customHeight="1"/>
-    <row r="92" ht="22.5" customHeight="1"/>
-    <row r="93" ht="22.5" customHeight="1"/>
-    <row r="94" ht="22.5" customHeight="1"/>
-    <row r="95" ht="22.5" customHeight="1"/>
-    <row r="96" ht="22.5" customHeight="1"/>
-    <row r="97" ht="22.5" customHeight="1"/>
-    <row r="98" ht="22.5" customHeight="1"/>
-    <row r="99" ht="22.5" customHeight="1"/>
-    <row r="100" ht="22.5" customHeight="1"/>
-    <row r="101" ht="22.5" customHeight="1"/>
-    <row r="102" ht="22.5" customHeight="1"/>
-    <row r="103" ht="22.5" customHeight="1"/>
-    <row r="104" ht="22.5" customHeight="1"/>
-    <row r="105" ht="22.5" customHeight="1"/>
-    <row r="106" ht="22.5" customHeight="1"/>
-    <row r="107" ht="22.5" customHeight="1"/>
-    <row r="108" ht="22.5" customHeight="1"/>
-    <row r="109" ht="22.5" customHeight="1"/>
-    <row r="110" ht="22.5" customHeight="1"/>
-    <row r="111" ht="22.5" customHeight="1"/>
-    <row r="112" ht="22.5" customHeight="1"/>
-    <row r="113" ht="22.5" customHeight="1"/>
-    <row r="114" ht="22.5" customHeight="1"/>
-    <row r="115" ht="22.5" customHeight="1"/>
-    <row r="116" ht="22.5" customHeight="1"/>
-    <row r="117" ht="22.5" customHeight="1"/>
-    <row r="118" ht="22.5" customHeight="1"/>
-    <row r="119" ht="22.5" customHeight="1"/>
-    <row r="120" ht="22.5" customHeight="1"/>
-    <row r="121" ht="22.5" customHeight="1"/>
-    <row r="122" ht="22.5" customHeight="1"/>
-    <row r="123" ht="22.5" customHeight="1"/>
-    <row r="124" ht="22.5" customHeight="1"/>
-    <row r="125" ht="22.5" customHeight="1"/>
-    <row r="126" ht="22.5" customHeight="1"/>
-    <row r="127" ht="22.5" customHeight="1"/>
-    <row r="128" ht="22.5" customHeight="1"/>
-    <row r="129" ht="22.5" customHeight="1"/>
-    <row r="130" ht="22.5" customHeight="1"/>
-    <row r="131" ht="22.5" customHeight="1"/>
-    <row r="132" ht="22.5" customHeight="1"/>
-    <row r="133" ht="22.5" customHeight="1"/>
-    <row r="134" ht="22.5" customHeight="1"/>
-    <row r="135" ht="22.5" customHeight="1"/>
-    <row r="136" ht="22.5" customHeight="1"/>
-    <row r="137" ht="22.5" customHeight="1"/>
-    <row r="138" ht="22.5" customHeight="1"/>
-    <row r="139" ht="22.5" customHeight="1"/>
-    <row r="140" ht="22.5" customHeight="1"/>
-    <row r="141" ht="22.5" customHeight="1"/>
-    <row r="142" ht="22.5" customHeight="1"/>
-    <row r="143" ht="22.5" customHeight="1"/>
-    <row r="144" ht="22.5" customHeight="1"/>
-    <row r="145" ht="22.5" customHeight="1"/>
-    <row r="146" ht="22.5" customHeight="1"/>
-    <row r="147" ht="22.5" customHeight="1"/>
-    <row r="148" ht="22.5" customHeight="1"/>
-    <row r="149" ht="22.5" customHeight="1"/>
-    <row r="150" ht="22.5" customHeight="1"/>
-    <row r="151" ht="22.5" customHeight="1"/>
-    <row r="152" ht="22.5" customHeight="1"/>
-    <row r="153" ht="22.5" customHeight="1"/>
-    <row r="154" ht="22.5" customHeight="1"/>
-    <row r="155" ht="22.5" customHeight="1"/>
-    <row r="156" ht="22.5" customHeight="1"/>
-    <row r="157" ht="22.5" customHeight="1"/>
-    <row r="158" ht="22.5" customHeight="1"/>
-    <row r="159" ht="22.5" customHeight="1"/>
-    <row r="160" ht="22.5" customHeight="1"/>
-    <row r="161" ht="22.5" customHeight="1"/>
-    <row r="162" ht="22.5" customHeight="1"/>
-    <row r="163" ht="22.5" customHeight="1"/>
-    <row r="164" ht="22.5" customHeight="1"/>
-    <row r="165" ht="22.5" customHeight="1"/>
-    <row r="166" ht="22.5" customHeight="1"/>
-    <row r="167" ht="22.5" customHeight="1"/>
-    <row r="168" ht="22.5" customHeight="1"/>
-    <row r="169" ht="22.5" customHeight="1"/>
-    <row r="170" ht="22.5" customHeight="1"/>
-    <row r="171" ht="22.5" customHeight="1"/>
-    <row r="172" ht="22.5" customHeight="1"/>
-    <row r="173" ht="22.5" customHeight="1"/>
-    <row r="174" ht="22.5" customHeight="1"/>
-    <row r="175" ht="22.5" customHeight="1"/>
-    <row r="176" ht="22.5" customHeight="1"/>
-    <row r="177" ht="22.5" customHeight="1"/>
-    <row r="178" ht="22.5" customHeight="1"/>
-    <row r="179" ht="22.5" customHeight="1"/>
-    <row r="180" ht="22.5" customHeight="1"/>
-    <row r="181" ht="22.5" customHeight="1"/>
-    <row r="182" ht="22.5" customHeight="1"/>
-    <row r="183" ht="22.5" customHeight="1"/>
-    <row r="184" ht="22.5" customHeight="1"/>
-    <row r="185" ht="22.5" customHeight="1"/>
-    <row r="186" ht="22.5" customHeight="1"/>
-    <row r="187" ht="22.5" customHeight="1"/>
-    <row r="188" ht="22.5" customHeight="1"/>
-    <row r="189" ht="22.5" customHeight="1"/>
-    <row r="190" ht="22.5" customHeight="1"/>
-    <row r="191" ht="22.5" customHeight="1"/>
-    <row r="192" ht="22.5" customHeight="1"/>
-    <row r="193" ht="22.5" customHeight="1"/>
-    <row r="194" ht="22.5" customHeight="1"/>
-    <row r="195" ht="22.5" customHeight="1"/>
-    <row r="196" ht="22.5" customHeight="1"/>
-    <row r="197" ht="22.5" customHeight="1"/>
-    <row r="198" ht="22.5" customHeight="1"/>
-    <row r="199" ht="22.5" customHeight="1"/>
-    <row r="200" ht="22.5" customHeight="1"/>
-    <row r="201" ht="22.5" customHeight="1"/>
-    <row r="202" ht="22.5" customHeight="1"/>
-    <row r="203" ht="22.5" customHeight="1"/>
-    <row r="204" ht="22.5" customHeight="1"/>
-    <row r="205" ht="22.5" customHeight="1"/>
-    <row r="206" ht="22.5" customHeight="1"/>
-    <row r="207" ht="22.5" customHeight="1"/>
-    <row r="208" ht="22.5" customHeight="1"/>
-    <row r="209" ht="22.5" customHeight="1"/>
-    <row r="210" ht="22.5" customHeight="1"/>
-    <row r="211" ht="22.5" customHeight="1"/>
-    <row r="212" ht="22.5" customHeight="1"/>
-    <row r="213" ht="22.5" customHeight="1"/>
-    <row r="214" ht="22.5" customHeight="1"/>
-    <row r="215" ht="22.5" customHeight="1"/>
-    <row r="216" ht="22.5" customHeight="1"/>
-    <row r="217" ht="22.5" customHeight="1"/>
-    <row r="218" ht="22.5" customHeight="1"/>
-    <row r="219" ht="22.5" customHeight="1"/>
-    <row r="220" ht="22.5" customHeight="1"/>
-    <row r="221" ht="22.5" customHeight="1"/>
-    <row r="222" ht="22.5" customHeight="1"/>
-    <row r="223" ht="22.5" customHeight="1"/>
-    <row r="224" ht="22.5" customHeight="1"/>
-    <row r="225" ht="22.5" customHeight="1"/>
-    <row r="226" ht="22.5" customHeight="1"/>
-    <row r="227" ht="22.5" customHeight="1"/>
-    <row r="228" ht="22.5" customHeight="1"/>
-    <row r="229" ht="22.5" customHeight="1"/>
-    <row r="230" ht="22.5" customHeight="1"/>
-    <row r="231" ht="22.5" customHeight="1"/>
-    <row r="232" ht="22.5" customHeight="1"/>
-    <row r="233" ht="22.5" customHeight="1"/>
-    <row r="234" ht="22.5" customHeight="1"/>
-    <row r="235" ht="22.5" customHeight="1"/>
-    <row r="236" ht="22.5" customHeight="1"/>
-    <row r="237" ht="22.5" customHeight="1"/>
-    <row r="238" ht="22.5" customHeight="1"/>
-    <row r="239" ht="22.5" customHeight="1"/>
-    <row r="240" ht="22.5" customHeight="1"/>
-    <row r="241" ht="22.5" customHeight="1"/>
-    <row r="242" ht="22.5" customHeight="1"/>
-    <row r="243" ht="22.5" customHeight="1"/>
-    <row r="244" ht="22.5" customHeight="1"/>
-    <row r="245" ht="22.5" customHeight="1"/>
-    <row r="246" ht="22.5" customHeight="1"/>
-    <row r="247" ht="22.5" customHeight="1"/>
-    <row r="248" ht="22.5" customHeight="1"/>
-    <row r="249" ht="22.5" customHeight="1"/>
-    <row r="250" ht="22.5" customHeight="1"/>
-    <row r="251" ht="22.5" customHeight="1"/>
-    <row r="252" ht="22.5" customHeight="1"/>
-    <row r="253" ht="22.5" customHeight="1"/>
-    <row r="254" ht="22.5" customHeight="1"/>
-    <row r="255" ht="22.5" customHeight="1"/>
-    <row r="256" ht="22.5" customHeight="1"/>
-    <row r="257" ht="22.5" customHeight="1"/>
-    <row r="258" ht="22.5" customHeight="1"/>
-    <row r="259" ht="22.5" customHeight="1"/>
-    <row r="260" ht="22.5" customHeight="1"/>
-    <row r="261" ht="22.5" customHeight="1"/>
-    <row r="262" ht="22.5" customHeight="1"/>
-    <row r="263" ht="22.5" customHeight="1"/>
-    <row r="264" ht="22.5" customHeight="1"/>
-    <row r="265" ht="22.5" customHeight="1"/>
-    <row r="266" ht="22.5" customHeight="1"/>
-    <row r="267" ht="22.5" customHeight="1"/>
-    <row r="268" ht="22.5" customHeight="1"/>
-    <row r="269" ht="22.5" customHeight="1"/>
-    <row r="270" ht="22.5" customHeight="1"/>
-    <row r="271" ht="22.5" customHeight="1"/>
-    <row r="272" ht="22.5" customHeight="1"/>
-    <row r="273" ht="22.5" customHeight="1"/>
-    <row r="274" ht="22.5" customHeight="1"/>
-    <row r="275" ht="22.5" customHeight="1"/>
-    <row r="276" ht="22.5" customHeight="1"/>
-    <row r="277" ht="22.5" customHeight="1"/>
-    <row r="278" ht="22.5" customHeight="1"/>
-    <row r="279" ht="22.5" customHeight="1"/>
-    <row r="280" ht="22.5" customHeight="1"/>
-    <row r="281" ht="22.5" customHeight="1"/>
-    <row r="282" ht="22.5" customHeight="1"/>
-    <row r="283" ht="22.5" customHeight="1"/>
-    <row r="284" ht="22.5" customHeight="1"/>
-    <row r="285" ht="22.5" customHeight="1"/>
-    <row r="286" ht="22.5" customHeight="1"/>
-    <row r="287" ht="22.5" customHeight="1"/>
-    <row r="288" ht="22.5" customHeight="1"/>
-    <row r="289" ht="22.5" customHeight="1"/>
-    <row r="290" ht="22.5" customHeight="1"/>
-    <row r="291" ht="22.5" customHeight="1"/>
-    <row r="292" ht="22.5" customHeight="1"/>
-    <row r="293" ht="22.5" customHeight="1"/>
-    <row r="294" ht="22.5" customHeight="1"/>
-    <row r="295" ht="22.5" customHeight="1"/>
-    <row r="296" ht="22.5" customHeight="1"/>
-    <row r="297" ht="22.5" customHeight="1"/>
-    <row r="298" ht="22.5" customHeight="1"/>
-    <row r="299" ht="22.5" customHeight="1"/>
-    <row r="300" ht="22.5" customHeight="1"/>
-    <row r="301" ht="22.5" customHeight="1"/>
-    <row r="302" ht="22.5" customHeight="1"/>
-    <row r="303" ht="22.5" customHeight="1"/>
-    <row r="304" ht="22.5" customHeight="1"/>
-    <row r="305" ht="22.5" customHeight="1"/>
-    <row r="306" ht="22.5" customHeight="1"/>
-    <row r="307" ht="22.5" customHeight="1"/>
-    <row r="308" ht="22.5" customHeight="1"/>
-    <row r="309" ht="22.5" customHeight="1"/>
-    <row r="310" ht="22.5" customHeight="1"/>
-    <row r="311" ht="22.5" customHeight="1"/>
-    <row r="312" ht="22.5" customHeight="1"/>
-    <row r="313" ht="22.5" customHeight="1"/>
-    <row r="314" ht="22.5" customHeight="1"/>
-    <row r="315" ht="22.5" customHeight="1"/>
-    <row r="316" ht="22.5" customHeight="1"/>
-    <row r="317" ht="22.5" customHeight="1"/>
-    <row r="318" ht="22.5" customHeight="1"/>
-    <row r="319" ht="22.5" customHeight="1"/>
-    <row r="320" ht="22.5" customHeight="1"/>
-    <row r="321" ht="22.5" customHeight="1"/>
-    <row r="322" ht="22.5" customHeight="1"/>
-    <row r="323" ht="22.5" customHeight="1"/>
-    <row r="324" ht="22.5" customHeight="1"/>
-    <row r="325" ht="22.5" customHeight="1"/>
-    <row r="326" ht="22.5" customHeight="1"/>
-    <row r="327" ht="22.5" customHeight="1"/>
-    <row r="328" ht="22.5" customHeight="1"/>
-    <row r="329" ht="22.5" customHeight="1"/>
-    <row r="330" ht="22.5" customHeight="1"/>
-    <row r="331" ht="22.5" customHeight="1"/>
-    <row r="332" ht="22.5" customHeight="1"/>
-    <row r="333" ht="22.5" customHeight="1"/>
-    <row r="334" ht="22.5" customHeight="1"/>
-    <row r="335" ht="22.5" customHeight="1"/>
-    <row r="336" ht="22.5" customHeight="1"/>
-    <row r="337" ht="22.5" customHeight="1"/>
-    <row r="338" ht="22.5" customHeight="1"/>
-    <row r="339" ht="22.5" customHeight="1"/>
-    <row r="340" ht="22.5" customHeight="1"/>
-    <row r="341" ht="22.5" customHeight="1"/>
-    <row r="342" ht="22.5" customHeight="1"/>
-    <row r="343" ht="22.5" customHeight="1"/>
-    <row r="344" ht="22.5" customHeight="1"/>
-    <row r="345" ht="22.5" customHeight="1"/>
-    <row r="346" ht="22.5" customHeight="1"/>
-    <row r="347" ht="22.5" customHeight="1"/>
-    <row r="348" ht="22.5" customHeight="1"/>
-    <row r="349" ht="22.5" customHeight="1"/>
-    <row r="350" ht="22.5" customHeight="1"/>
-    <row r="351" ht="22.5" customHeight="1"/>
-    <row r="352" ht="22.5" customHeight="1"/>
-    <row r="353" ht="22.5" customHeight="1"/>
-    <row r="354" ht="22.5" customHeight="1"/>
-    <row r="355" ht="22.5" customHeight="1"/>
-    <row r="356" ht="22.5" customHeight="1"/>
-    <row r="357" ht="22.5" customHeight="1"/>
-    <row r="358" ht="22.5" customHeight="1"/>
-    <row r="359" ht="22.5" customHeight="1"/>
-    <row r="360" ht="22.5" customHeight="1"/>
-    <row r="361" ht="22.5" customHeight="1"/>
-    <row r="362" ht="22.5" customHeight="1"/>
-    <row r="363" ht="22.5" customHeight="1"/>
-    <row r="364" ht="22.5" customHeight="1"/>
-    <row r="365" ht="22.5" customHeight="1"/>
-    <row r="366" ht="22.5" customHeight="1"/>
-    <row r="367" ht="22.5" customHeight="1"/>
-    <row r="368" ht="22.5" customHeight="1"/>
-    <row r="369" ht="22.5" customHeight="1"/>
-    <row r="370" ht="22.5" customHeight="1"/>
-    <row r="371" ht="22.5" customHeight="1"/>
-    <row r="372" ht="22.5" customHeight="1"/>
-    <row r="373" ht="22.5" customHeight="1"/>
-    <row r="374" ht="22.5" customHeight="1"/>
-    <row r="375" ht="22.5" customHeight="1"/>
-    <row r="376" ht="22.5" customHeight="1"/>
-    <row r="377" ht="22.5" customHeight="1"/>
-    <row r="378" ht="22.5" customHeight="1"/>
-    <row r="379" ht="22.5" customHeight="1"/>
-    <row r="380" ht="22.5" customHeight="1"/>
-    <row r="381" ht="22.5" customHeight="1"/>
-    <row r="382" ht="22.5" customHeight="1"/>
-    <row r="383" ht="22.5" customHeight="1"/>
-    <row r="384" ht="22.5" customHeight="1"/>
-    <row r="385" ht="22.5" customHeight="1"/>
-    <row r="386" ht="22.5" customHeight="1"/>
-    <row r="387" ht="22.5" customHeight="1"/>
-    <row r="388" ht="22.5" customHeight="1"/>
-    <row r="389" ht="22.5" customHeight="1"/>
-    <row r="390" ht="22.5" customHeight="1"/>
-    <row r="391" ht="22.5" customHeight="1"/>
-    <row r="392" ht="22.5" customHeight="1"/>
-    <row r="393" ht="22.5" customHeight="1"/>
-    <row r="394" ht="22.5" customHeight="1"/>
-    <row r="395" ht="22.5" customHeight="1"/>
-    <row r="396" ht="22.5" customHeight="1"/>
-    <row r="397" ht="22.5" customHeight="1"/>
-    <row r="398" ht="22.5" customHeight="1"/>
-    <row r="399" ht="22.5" customHeight="1"/>
-    <row r="400" ht="22.5" customHeight="1"/>
-    <row r="401" ht="22.5" customHeight="1"/>
-    <row r="402" ht="22.5" customHeight="1"/>
-    <row r="403" ht="22.5" customHeight="1"/>
-    <row r="404" ht="22.5" customHeight="1"/>
-    <row r="405" ht="22.5" customHeight="1"/>
-    <row r="406" ht="22.5" customHeight="1"/>
-    <row r="407" ht="22.5" customHeight="1"/>
-    <row r="408" ht="22.5" customHeight="1"/>
-    <row r="409" ht="22.5" customHeight="1"/>
-    <row r="410" ht="22.5" customHeight="1"/>
-    <row r="411" ht="22.5" customHeight="1"/>
-    <row r="412" ht="22.5" customHeight="1"/>
-    <row r="413" ht="22.5" customHeight="1"/>
-    <row r="414" ht="22.5" customHeight="1"/>
-    <row r="415" ht="22.5" customHeight="1"/>
-    <row r="416" ht="22.5" customHeight="1"/>
-    <row r="417" ht="22.5" customHeight="1"/>
-    <row r="418" ht="22.5" customHeight="1"/>
-    <row r="419" ht="22.5" customHeight="1"/>
-    <row r="420" ht="22.5" customHeight="1"/>
-    <row r="421" ht="22.5" customHeight="1"/>
-    <row r="422" ht="22.5" customHeight="1"/>
-    <row r="423" ht="22.5" customHeight="1"/>
-    <row r="424" ht="22.5" customHeight="1"/>
-    <row r="425" ht="22.5" customHeight="1"/>
-    <row r="426" ht="22.5" customHeight="1"/>
-    <row r="427" ht="22.5" customHeight="1"/>
-    <row r="428" ht="22.5" customHeight="1"/>
-    <row r="429" ht="22.5" customHeight="1"/>
-    <row r="430" ht="22.5" customHeight="1"/>
-    <row r="431" ht="22.5" customHeight="1"/>
-    <row r="432" ht="22.5" customHeight="1"/>
-    <row r="433" ht="22.5" customHeight="1"/>
-    <row r="434" ht="22.5" customHeight="1"/>
-    <row r="435" ht="22.5" customHeight="1"/>
-    <row r="436" ht="22.5" customHeight="1"/>
-    <row r="437" ht="22.5" customHeight="1"/>
-    <row r="438" ht="22.5" customHeight="1"/>
-    <row r="439" ht="22.5" customHeight="1"/>
-    <row r="440" ht="22.5" customHeight="1"/>
-    <row r="441" ht="22.5" customHeight="1"/>
-    <row r="442" ht="22.5" customHeight="1"/>
-    <row r="443" ht="22.5" customHeight="1"/>
-    <row r="444" ht="22.5" customHeight="1"/>
-    <row r="445" ht="22.5" customHeight="1"/>
-    <row r="446" ht="22.5" customHeight="1"/>
-    <row r="447" ht="22.5" customHeight="1"/>
-    <row r="448" ht="22.5" customHeight="1"/>
-    <row r="449" ht="22.5" customHeight="1"/>
-    <row r="450" ht="22.5" customHeight="1"/>
-    <row r="451" ht="22.5" customHeight="1"/>
-    <row r="452" ht="22.5" customHeight="1"/>
-    <row r="453" ht="22.5" customHeight="1"/>
-    <row r="454" ht="22.5" customHeight="1"/>
-    <row r="455" ht="22.5" customHeight="1"/>
-    <row r="456" ht="22.5" customHeight="1"/>
-    <row r="457" ht="22.5" customHeight="1"/>
-    <row r="458" ht="22.5" customHeight="1"/>
-    <row r="459" ht="22.5" customHeight="1"/>
-    <row r="460" ht="22.5" customHeight="1"/>
-    <row r="461" ht="22.5" customHeight="1"/>
-    <row r="462" ht="22.5" customHeight="1"/>
-    <row r="463" ht="22.5" customHeight="1"/>
-    <row r="464" ht="22.5" customHeight="1"/>
-    <row r="465" ht="22.5" customHeight="1"/>
-    <row r="466" ht="22.5" customHeight="1"/>
-    <row r="467" ht="22.5" customHeight="1"/>
-    <row r="468" ht="22.5" customHeight="1"/>
-    <row r="469" ht="22.5" customHeight="1"/>
-    <row r="470" ht="22.5" customHeight="1"/>
-    <row r="471" ht="22.5" customHeight="1"/>
-    <row r="472" ht="22.5" customHeight="1"/>
-    <row r="473" ht="22.5" customHeight="1"/>
-    <row r="474" ht="22.5" customHeight="1"/>
-    <row r="475" ht="22.5" customHeight="1"/>
-    <row r="476" ht="22.5" customHeight="1"/>
-    <row r="477" ht="22.5" customHeight="1"/>
-    <row r="478" ht="22.5" customHeight="1"/>
-    <row r="479" ht="22.5" customHeight="1"/>
-    <row r="480" ht="22.5" customHeight="1"/>
-    <row r="481" ht="22.5" customHeight="1"/>
-    <row r="482" ht="22.5" customHeight="1"/>
-    <row r="483" ht="22.5" customHeight="1"/>
-    <row r="484" ht="22.5" customHeight="1"/>
-    <row r="485" ht="22.5" customHeight="1"/>
-    <row r="486" ht="22.5" customHeight="1"/>
-    <row r="487" ht="22.5" customHeight="1"/>
-    <row r="488" ht="22.5" customHeight="1"/>
-    <row r="489" ht="22.5" customHeight="1"/>
-    <row r="490" ht="22.5" customHeight="1"/>
-    <row r="491" ht="22.5" customHeight="1"/>
-    <row r="492" ht="22.5" customHeight="1"/>
-    <row r="493" ht="22.5" customHeight="1"/>
-    <row r="494" ht="22.5" customHeight="1"/>
-    <row r="495" ht="22.5" customHeight="1"/>
-    <row r="496" ht="22.5" customHeight="1"/>
-    <row r="497" ht="22.5" customHeight="1"/>
-    <row r="498" ht="22.5" customHeight="1"/>
-    <row r="499" ht="22.5" customHeight="1"/>
-    <row r="500" ht="22.5" customHeight="1"/>
-    <row r="501" ht="22.5" customHeight="1"/>
-    <row r="502" ht="22.5" customHeight="1"/>
-    <row r="503" ht="22.5" customHeight="1"/>
-    <row r="504" ht="22.5" customHeight="1"/>
-    <row r="505" ht="22.5" customHeight="1"/>
-    <row r="506" ht="22.5" customHeight="1"/>
-    <row r="507" ht="22.5" customHeight="1"/>
-    <row r="508" ht="22.5" customHeight="1"/>
-    <row r="509" ht="22.5" customHeight="1"/>
-    <row r="510" ht="22.5" customHeight="1"/>
-    <row r="511" ht="22.5" customHeight="1"/>
-    <row r="512" ht="22.5" customHeight="1"/>
-    <row r="513" ht="22.5" customHeight="1"/>
-    <row r="514" ht="22.5" customHeight="1"/>
-    <row r="515" ht="22.5" customHeight="1"/>
-    <row r="516" ht="22.5" customHeight="1"/>
-    <row r="517" ht="22.5" customHeight="1"/>
-    <row r="518" ht="22.5" customHeight="1"/>
-    <row r="519" ht="22.5" customHeight="1"/>
-    <row r="520" ht="22.5" customHeight="1"/>
-    <row r="521" ht="22.5" customHeight="1"/>
-    <row r="522" ht="22.5" customHeight="1"/>
-    <row r="523" ht="22.5" customHeight="1"/>
-    <row r="524" ht="22.5" customHeight="1"/>
-    <row r="525" ht="22.5" customHeight="1"/>
-    <row r="526" ht="22.5" customHeight="1"/>
-    <row r="527" ht="22.5" customHeight="1"/>
-    <row r="528" ht="22.5" customHeight="1"/>
-    <row r="529" ht="22.5" customHeight="1"/>
-    <row r="530" ht="22.5" customHeight="1"/>
-    <row r="531" ht="22.5" customHeight="1"/>
-    <row r="532" ht="22.5" customHeight="1"/>
-    <row r="533" ht="22.5" customHeight="1"/>
-    <row r="534" ht="22.5" customHeight="1"/>
-    <row r="535" ht="22.5" customHeight="1"/>
-    <row r="536" ht="22.5" customHeight="1"/>
-    <row r="537" ht="22.5" customHeight="1"/>
-    <row r="538" ht="22.5" customHeight="1"/>
-    <row r="539" ht="22.5" customHeight="1"/>
-    <row r="540" ht="22.5" customHeight="1"/>
-    <row r="541" ht="22.5" customHeight="1"/>
-    <row r="542" ht="22.5" customHeight="1"/>
-    <row r="543" ht="22.5" customHeight="1"/>
-    <row r="544" ht="22.5" customHeight="1"/>
-    <row r="545" ht="22.5" customHeight="1"/>
-    <row r="546" ht="22.5" customHeight="1"/>
-    <row r="547" ht="22.5" customHeight="1"/>
-    <row r="548" ht="22.5" customHeight="1"/>
-    <row r="549" ht="22.5" customHeight="1"/>
-    <row r="550" ht="22.5" customHeight="1"/>
-    <row r="551" ht="22.5" customHeight="1"/>
-    <row r="552" ht="22.5" customHeight="1"/>
-    <row r="553" ht="22.5" customHeight="1"/>
-    <row r="554" ht="22.5" customHeight="1"/>
-    <row r="555" ht="22.5" customHeight="1"/>
-    <row r="556" ht="22.5" customHeight="1"/>
-    <row r="557" ht="22.5" customHeight="1"/>
-    <row r="558" ht="22.5" customHeight="1"/>
-    <row r="559" ht="22.5" customHeight="1"/>
-    <row r="560" ht="22.5" customHeight="1"/>
-    <row r="561" ht="22.5" customHeight="1"/>
-    <row r="562" ht="22.5" customHeight="1"/>
-    <row r="563" ht="22.5" customHeight="1"/>
-    <row r="564" ht="22.5" customHeight="1"/>
-    <row r="565" ht="22.5" customHeight="1"/>
-    <row r="566" ht="22.5" customHeight="1"/>
-    <row r="567" ht="22.5" customHeight="1"/>
-    <row r="568" ht="22.5" customHeight="1"/>
-    <row r="569" ht="22.5" customHeight="1"/>
-    <row r="570" ht="22.5" customHeight="1"/>
-    <row r="571" ht="22.5" customHeight="1"/>
-    <row r="572" ht="22.5" customHeight="1"/>
-    <row r="573" ht="22.5" customHeight="1"/>
-    <row r="574" ht="22.5" customHeight="1"/>
-    <row r="575" ht="22.5" customHeight="1"/>
-    <row r="576" ht="22.5" customHeight="1"/>
-    <row r="577" ht="22.5" customHeight="1"/>
-    <row r="578" ht="22.5" customHeight="1"/>
-    <row r="579" ht="22.5" customHeight="1"/>
-    <row r="580" ht="22.5" customHeight="1"/>
-    <row r="581" ht="22.5" customHeight="1"/>
-    <row r="582" ht="22.5" customHeight="1"/>
-    <row r="583" ht="22.5" customHeight="1"/>
-    <row r="584" ht="22.5" customHeight="1"/>
-    <row r="585" ht="22.5" customHeight="1"/>
-    <row r="586" ht="22.5" customHeight="1"/>
-    <row r="587" ht="22.5" customHeight="1"/>
-    <row r="588" ht="22.5" customHeight="1"/>
-    <row r="589" ht="22.5" customHeight="1"/>
-    <row r="590" ht="22.5" customHeight="1"/>
-    <row r="591" ht="22.5" customHeight="1"/>
-    <row r="592" ht="22.5" customHeight="1"/>
-    <row r="593" ht="22.5" customHeight="1"/>
-    <row r="594" ht="22.5" customHeight="1"/>
-    <row r="595" ht="22.5" customHeight="1"/>
-    <row r="596" ht="22.5" customHeight="1"/>
-    <row r="597" ht="22.5" customHeight="1"/>
-    <row r="598" ht="22.5" customHeight="1"/>
-    <row r="599" ht="22.5" customHeight="1"/>
-    <row r="600" ht="22.5" customHeight="1"/>
-    <row r="601" ht="22.5" customHeight="1"/>
-    <row r="602" ht="22.5" customHeight="1"/>
-    <row r="603" ht="22.5" customHeight="1"/>
-    <row r="604" ht="22.5" customHeight="1"/>
-    <row r="605" ht="22.5" customHeight="1"/>
-    <row r="606" ht="22.5" customHeight="1"/>
-    <row r="607" ht="22.5" customHeight="1"/>
-    <row r="608" ht="22.5" customHeight="1"/>
-    <row r="609" ht="22.5" customHeight="1"/>
-    <row r="610" ht="22.5" customHeight="1"/>
-    <row r="611" ht="22.5" customHeight="1"/>
-    <row r="612" ht="22.5" customHeight="1"/>
-    <row r="613" ht="22.5" customHeight="1"/>
-    <row r="614" ht="22.5" customHeight="1"/>
-    <row r="615" ht="22.5" customHeight="1"/>
-    <row r="616" ht="22.5" customHeight="1"/>
-    <row r="617" ht="22.5" customHeight="1"/>
-    <row r="618" ht="22.5" customHeight="1"/>
-    <row r="619" ht="22.5" customHeight="1"/>
-    <row r="620" ht="22.5" customHeight="1"/>
-    <row r="621" ht="22.5" customHeight="1"/>
-    <row r="622" ht="22.5" customHeight="1"/>
-    <row r="623" ht="22.5" customHeight="1"/>
-    <row r="624" ht="22.5" customHeight="1"/>
-    <row r="625" ht="22.5" customHeight="1"/>
-    <row r="626" ht="22.5" customHeight="1"/>
-    <row r="627" ht="22.5" customHeight="1"/>
-    <row r="628" ht="22.5" customHeight="1"/>
-    <row r="629" ht="22.5" customHeight="1"/>
-    <row r="630" ht="22.5" customHeight="1"/>
-    <row r="631" ht="22.5" customHeight="1"/>
-    <row r="632" ht="22.5" customHeight="1"/>
-    <row r="633" ht="22.5" customHeight="1"/>
-    <row r="634" ht="22.5" customHeight="1"/>
-    <row r="635" ht="22.5" customHeight="1"/>
-    <row r="636" ht="22.5" customHeight="1"/>
-    <row r="637" ht="22.5" customHeight="1"/>
-    <row r="638" ht="22.5" customHeight="1"/>
-    <row r="639" ht="22.5" customHeight="1"/>
-    <row r="640" ht="22.5" customHeight="1"/>
-    <row r="641" ht="22.5" customHeight="1"/>
-    <row r="642" ht="22.5" customHeight="1"/>
-    <row r="643" ht="22.5" customHeight="1"/>
-    <row r="644" ht="22.5" customHeight="1"/>
-    <row r="645" ht="22.5" customHeight="1"/>
-    <row r="646" ht="22.5" customHeight="1"/>
-    <row r="647" ht="22.5" customHeight="1"/>
-    <row r="648" ht="22.5" customHeight="1"/>
-    <row r="649" ht="22.5" customHeight="1"/>
-    <row r="650" ht="22.5" customHeight="1"/>
-    <row r="651" ht="22.5" customHeight="1"/>
-    <row r="652" ht="22.5" customHeight="1"/>
-    <row r="653" ht="22.5" customHeight="1"/>
-    <row r="654" ht="22.5" customHeight="1"/>
-    <row r="655" ht="22.5" customHeight="1"/>
-    <row r="656" ht="22.5" customHeight="1"/>
-    <row r="657" ht="22.5" customHeight="1"/>
-    <row r="658" ht="22.5" customHeight="1"/>
-    <row r="659" ht="22.5" customHeight="1"/>
-    <row r="660" ht="22.5" customHeight="1"/>
-    <row r="661" ht="22.5" customHeight="1"/>
-    <row r="662" ht="22.5" customHeight="1"/>
-    <row r="663" ht="22.5" customHeight="1"/>
-    <row r="664" ht="22.5" customHeight="1"/>
-    <row r="665" ht="22.5" customHeight="1"/>
-    <row r="666" ht="22.5" customHeight="1"/>
-    <row r="667" ht="22.5" customHeight="1"/>
-    <row r="668" ht="22.5" customHeight="1"/>
-    <row r="669" ht="22.5" customHeight="1"/>
-    <row r="670" ht="22.5" customHeight="1"/>
-    <row r="671" ht="22.5" customHeight="1"/>
-    <row r="672" ht="22.5" customHeight="1"/>
-    <row r="673" ht="22.5" customHeight="1"/>
-    <row r="674" ht="22.5" customHeight="1"/>
-    <row r="675" ht="22.5" customHeight="1"/>
-    <row r="676" ht="22.5" customHeight="1"/>
-    <row r="677" ht="22.5" customHeight="1"/>
-    <row r="678" ht="22.5" customHeight="1"/>
-    <row r="679" ht="22.5" customHeight="1"/>
-    <row r="680" ht="22.5" customHeight="1"/>
-    <row r="681" ht="22.5" customHeight="1"/>
-    <row r="682" ht="22.5" customHeight="1"/>
-    <row r="683" ht="22.5" customHeight="1"/>
-    <row r="684" ht="22.5" customHeight="1"/>
-    <row r="685" ht="22.5" customHeight="1"/>
-    <row r="686" ht="22.5" customHeight="1"/>
-    <row r="687" ht="22.5" customHeight="1"/>
-    <row r="688" ht="22.5" customHeight="1"/>
-    <row r="689" ht="22.5" customHeight="1"/>
-    <row r="690" ht="22.5" customHeight="1"/>
-    <row r="691" ht="22.5" customHeight="1"/>
-    <row r="692" ht="22.5" customHeight="1"/>
-    <row r="693" ht="22.5" customHeight="1"/>
-    <row r="694" ht="22.5" customHeight="1"/>
-    <row r="695" ht="22.5" customHeight="1"/>
-    <row r="696" ht="22.5" customHeight="1"/>
-    <row r="697" ht="22.5" customHeight="1"/>
-    <row r="698" ht="22.5" customHeight="1"/>
-    <row r="699" ht="22.5" customHeight="1"/>
-    <row r="700" ht="22.5" customHeight="1"/>
-    <row r="701" ht="22.5" customHeight="1"/>
-    <row r="702" ht="22.5" customHeight="1"/>
-    <row r="703" ht="22.5" customHeight="1"/>
-    <row r="704" ht="22.5" customHeight="1"/>
-    <row r="705" ht="22.5" customHeight="1"/>
-    <row r="706" ht="22.5" customHeight="1"/>
-    <row r="707" ht="22.5" customHeight="1"/>
-    <row r="708" ht="22.5" customHeight="1"/>
-    <row r="709" ht="22.5" customHeight="1"/>
-    <row r="710" ht="22.5" customHeight="1"/>
-    <row r="711" ht="22.5" customHeight="1"/>
-    <row r="712" ht="22.5" customHeight="1"/>
-    <row r="713" ht="22.5" customHeight="1"/>
-    <row r="714" ht="22.5" customHeight="1"/>
-    <row r="715" ht="22.5" customHeight="1"/>
-    <row r="716" ht="22.5" customHeight="1"/>
-    <row r="717" ht="22.5" customHeight="1"/>
-    <row r="718" ht="22.5" customHeight="1"/>
-    <row r="719" ht="22.5" customHeight="1"/>
-    <row r="720" ht="22.5" customHeight="1"/>
-    <row r="721" ht="22.5" customHeight="1"/>
-    <row r="722" ht="22.5" customHeight="1"/>
-    <row r="723" ht="22.5" customHeight="1"/>
-    <row r="724" ht="22.5" customHeight="1"/>
-    <row r="725" ht="22.5" customHeight="1"/>
-    <row r="726" ht="22.5" customHeight="1"/>
-    <row r="727" ht="22.5" customHeight="1"/>
-    <row r="728" ht="22.5" customHeight="1"/>
-    <row r="729" ht="22.5" customHeight="1"/>
-    <row r="730" ht="22.5" customHeight="1"/>
-    <row r="731" ht="22.5" customHeight="1"/>
-    <row r="732" ht="22.5" customHeight="1"/>
-    <row r="733" ht="22.5" customHeight="1"/>
-    <row r="734" ht="22.5" customHeight="1"/>
-    <row r="735" ht="22.5" customHeight="1"/>
-    <row r="736" ht="22.5" customHeight="1"/>
-    <row r="737" ht="22.5" customHeight="1"/>
-    <row r="738" ht="22.5" customHeight="1"/>
-    <row r="739" ht="22.5" customHeight="1"/>
-    <row r="740" ht="22.5" customHeight="1"/>
-    <row r="741" ht="22.5" customHeight="1"/>
-    <row r="742" ht="22.5" customHeight="1"/>
-    <row r="743" ht="22.5" customHeight="1"/>
-    <row r="744" ht="22.5" customHeight="1"/>
-    <row r="745" ht="22.5" customHeight="1"/>
-    <row r="746" ht="22.5" customHeight="1"/>
-    <row r="747" ht="22.5" customHeight="1"/>
-    <row r="748" ht="22.5" customHeight="1"/>
-    <row r="749" ht="22.5" customHeight="1"/>
-    <row r="750" ht="22.5" customHeight="1"/>
-    <row r="751" ht="22.5" customHeight="1"/>
-    <row r="752" ht="22.5" customHeight="1"/>
-    <row r="753" ht="22.5" customHeight="1"/>
-    <row r="754" ht="22.5" customHeight="1"/>
-    <row r="755" ht="22.5" customHeight="1"/>
-    <row r="756" ht="22.5" customHeight="1"/>
-    <row r="757" ht="22.5" customHeight="1"/>
-    <row r="758" ht="22.5" customHeight="1"/>
-    <row r="759" ht="22.5" customHeight="1"/>
-    <row r="760" ht="22.5" customHeight="1"/>
-    <row r="761" ht="22.5" customHeight="1"/>
-    <row r="762" ht="22.5" customHeight="1"/>
-    <row r="763" ht="22.5" customHeight="1"/>
-    <row r="764" ht="22.5" customHeight="1"/>
-    <row r="765" ht="22.5" customHeight="1"/>
-    <row r="766" ht="22.5" customHeight="1"/>
-    <row r="767" ht="22.5" customHeight="1"/>
-    <row r="768" ht="22.5" customHeight="1"/>
-    <row r="769" ht="22.5" customHeight="1"/>
-    <row r="770" ht="22.5" customHeight="1"/>
-    <row r="771" ht="22.5" customHeight="1"/>
-    <row r="772" ht="22.5" customHeight="1"/>
-    <row r="773" ht="22.5" customHeight="1"/>
-    <row r="774" ht="22.5" customHeight="1"/>
-    <row r="775" ht="22.5" customHeight="1"/>
-    <row r="776" ht="22.5" customHeight="1"/>
-    <row r="777" ht="22.5" customHeight="1"/>
-    <row r="778" ht="22.5" customHeight="1"/>
-    <row r="779" ht="22.5" customHeight="1"/>
-    <row r="780" ht="22.5" customHeight="1"/>
-    <row r="781" ht="22.5" customHeight="1"/>
-    <row r="782" ht="22.5" customHeight="1"/>
-    <row r="783" ht="22.5" customHeight="1"/>
-    <row r="784" ht="22.5" customHeight="1"/>
-    <row r="785" ht="22.5" customHeight="1"/>
-    <row r="786" ht="22.5" customHeight="1"/>
-    <row r="787" ht="22.5" customHeight="1"/>
-    <row r="788" ht="22.5" customHeight="1"/>
-    <row r="789" ht="22.5" customHeight="1"/>
-    <row r="790" ht="22.5" customHeight="1"/>
-    <row r="791" ht="22.5" customHeight="1"/>
-    <row r="792" ht="22.5" customHeight="1"/>
-    <row r="793" ht="22.5" customHeight="1"/>
-    <row r="794" ht="22.5" customHeight="1"/>
-    <row r="795" ht="22.5" customHeight="1"/>
-    <row r="796" ht="22.5" customHeight="1"/>
-    <row r="797" ht="22.5" customHeight="1"/>
-    <row r="798" ht="22.5" customHeight="1"/>
-    <row r="799" ht="22.5" customHeight="1"/>
-    <row r="800" ht="22.5" customHeight="1"/>
-    <row r="801" ht="22.5" customHeight="1"/>
-    <row r="802" ht="22.5" customHeight="1"/>
-    <row r="803" ht="22.5" customHeight="1"/>
-    <row r="804" ht="22.5" customHeight="1"/>
-    <row r="805" ht="22.5" customHeight="1"/>
-    <row r="806" ht="22.5" customHeight="1"/>
-    <row r="807" ht="22.5" customHeight="1"/>
-    <row r="808" ht="22.5" customHeight="1"/>
-    <row r="809" ht="22.5" customHeight="1"/>
-    <row r="810" ht="22.5" customHeight="1"/>
-    <row r="811" ht="22.5" customHeight="1"/>
-    <row r="812" ht="22.5" customHeight="1"/>
-    <row r="813" ht="22.5" customHeight="1"/>
-    <row r="814" ht="22.5" customHeight="1"/>
-    <row r="815" ht="22.5" customHeight="1"/>
-    <row r="816" ht="22.5" customHeight="1"/>
-    <row r="817" ht="22.5" customHeight="1"/>
-    <row r="818" ht="22.5" customHeight="1"/>
-    <row r="819" ht="22.5" customHeight="1"/>
-    <row r="820" ht="22.5" customHeight="1"/>
-    <row r="821" ht="22.5" customHeight="1"/>
-    <row r="822" ht="22.5" customHeight="1"/>
-    <row r="823" ht="22.5" customHeight="1"/>
-    <row r="824" ht="22.5" customHeight="1"/>
-    <row r="825" ht="22.5" customHeight="1"/>
-    <row r="826" ht="22.5" customHeight="1"/>
-    <row r="827" ht="22.5" customHeight="1"/>
-    <row r="828" ht="22.5" customHeight="1"/>
-    <row r="829" ht="22.5" customHeight="1"/>
-    <row r="830" ht="22.5" customHeight="1"/>
-    <row r="831" ht="22.5" customHeight="1"/>
-    <row r="832" ht="22.5" customHeight="1"/>
-    <row r="833" ht="22.5" customHeight="1"/>
-    <row r="834" ht="22.5" customHeight="1"/>
-    <row r="835" ht="22.5" customHeight="1"/>
-    <row r="836" ht="22.5" customHeight="1"/>
-    <row r="837" ht="22.5" customHeight="1"/>
-    <row r="838" ht="22.5" customHeight="1"/>
-    <row r="839" ht="22.5" customHeight="1"/>
-    <row r="840" ht="22.5" customHeight="1"/>
-    <row r="841" ht="22.5" customHeight="1"/>
-    <row r="842" ht="22.5" customHeight="1"/>
-    <row r="843" ht="22.5" customHeight="1"/>
-    <row r="844" ht="22.5" customHeight="1"/>
-    <row r="845" ht="22.5" customHeight="1"/>
-    <row r="846" ht="22.5" customHeight="1"/>
-    <row r="847" ht="22.5" customHeight="1"/>
-    <row r="848" ht="22.5" customHeight="1"/>
-    <row r="849" ht="22.5" customHeight="1"/>
-    <row r="850" ht="22.5" customHeight="1"/>
-    <row r="851" ht="22.5" customHeight="1"/>
-    <row r="852" ht="22.5" customHeight="1"/>
-    <row r="853" ht="22.5" customHeight="1"/>
-    <row r="854" ht="22.5" customHeight="1"/>
-    <row r="855" ht="22.5" customHeight="1"/>
-    <row r="856" ht="22.5" customHeight="1"/>
-    <row r="857" ht="22.5" customHeight="1"/>
-    <row r="858" ht="22.5" customHeight="1"/>
-    <row r="859" ht="22.5" customHeight="1"/>
-    <row r="860" ht="22.5" customHeight="1"/>
-    <row r="861" ht="22.5" customHeight="1"/>
-    <row r="862" ht="22.5" customHeight="1"/>
-    <row r="863" ht="22.5" customHeight="1"/>
-    <row r="864" ht="22.5" customHeight="1"/>
-    <row r="865" ht="22.5" customHeight="1"/>
-    <row r="866" ht="22.5" customHeight="1"/>
-    <row r="867" ht="22.5" customHeight="1"/>
-    <row r="868" ht="22.5" customHeight="1"/>
-    <row r="869" ht="22.5" customHeight="1"/>
-    <row r="870" ht="22.5" customHeight="1"/>
-    <row r="871" ht="22.5" customHeight="1"/>
-    <row r="872" ht="22.5" customHeight="1"/>
-    <row r="873" ht="22.5" customHeight="1"/>
-    <row r="874" ht="22.5" customHeight="1"/>
-    <row r="875" ht="22.5" customHeight="1"/>
-    <row r="876" ht="22.5" customHeight="1"/>
-    <row r="877" ht="22.5" customHeight="1"/>
-    <row r="878" ht="22.5" customHeight="1"/>
-    <row r="879" ht="22.5" customHeight="1"/>
-    <row r="880" ht="22.5" customHeight="1"/>
-    <row r="881" ht="22.5" customHeight="1"/>
-    <row r="882" ht="22.5" customHeight="1"/>
-    <row r="883" ht="22.5" customHeight="1"/>
-    <row r="884" ht="22.5" customHeight="1"/>
-    <row r="885" ht="22.5" customHeight="1"/>
-    <row r="886" ht="22.5" customHeight="1"/>
-    <row r="887" ht="22.5" customHeight="1"/>
-    <row r="888" ht="22.5" customHeight="1"/>
-    <row r="889" ht="22.5" customHeight="1"/>
-    <row r="890" ht="22.5" customHeight="1"/>
-    <row r="891" ht="22.5" customHeight="1"/>
-    <row r="892" ht="22.5" customHeight="1"/>
-    <row r="893" ht="22.5" customHeight="1"/>
-    <row r="894" ht="22.5" customHeight="1"/>
-    <row r="895" ht="22.5" customHeight="1"/>
-    <row r="896" ht="22.5" customHeight="1"/>
-    <row r="897" ht="22.5" customHeight="1"/>
-    <row r="898" ht="22.5" customHeight="1"/>
-    <row r="899" ht="22.5" customHeight="1"/>
-    <row r="900" ht="22.5" customHeight="1"/>
-    <row r="901" ht="22.5" customHeight="1"/>
-    <row r="902" ht="22.5" customHeight="1"/>
-    <row r="903" ht="22.5" customHeight="1"/>
-    <row r="904" ht="22.5" customHeight="1"/>
-    <row r="905" ht="22.5" customHeight="1"/>
-    <row r="906" ht="22.5" customHeight="1"/>
-    <row r="907" ht="22.5" customHeight="1"/>
-    <row r="908" ht="22.5" customHeight="1"/>
-    <row r="909" ht="22.5" customHeight="1"/>
-    <row r="910" ht="22.5" customHeight="1"/>
-    <row r="911" ht="22.5" customHeight="1"/>
-    <row r="912" ht="22.5" customHeight="1"/>
-    <row r="913" ht="22.5" customHeight="1"/>
-    <row r="914" ht="22.5" customHeight="1"/>
-    <row r="915" ht="22.5" customHeight="1"/>
-    <row r="916" ht="22.5" customHeight="1"/>
-    <row r="917" ht="22.5" customHeight="1"/>
-    <row r="918" ht="22.5" customHeight="1"/>
-    <row r="919" ht="22.5" customHeight="1"/>
-    <row r="920" ht="22.5" customHeight="1"/>
-    <row r="921" ht="22.5" customHeight="1"/>
-    <row r="922" ht="22.5" customHeight="1"/>
-    <row r="923" ht="22.5" customHeight="1"/>
-    <row r="924" ht="22.5" customHeight="1"/>
-    <row r="925" ht="22.5" customHeight="1"/>
-    <row r="926" ht="22.5" customHeight="1"/>
-    <row r="927" ht="22.5" customHeight="1"/>
-    <row r="928" ht="22.5" customHeight="1"/>
-    <row r="929" ht="22.5" customHeight="1"/>
-    <row r="930" ht="22.5" customHeight="1"/>
-    <row r="931" ht="22.5" customHeight="1"/>
-    <row r="932" ht="22.5" customHeight="1"/>
-    <row r="933" ht="22.5" customHeight="1"/>
-    <row r="934" ht="22.5" customHeight="1"/>
-    <row r="935" ht="22.5" customHeight="1"/>
-    <row r="936" ht="22.5" customHeight="1"/>
-    <row r="937" ht="22.5" customHeight="1"/>
-    <row r="938" ht="22.5" customHeight="1"/>
-    <row r="939" ht="22.5" customHeight="1"/>
-    <row r="940" ht="22.5" customHeight="1"/>
-    <row r="941" ht="22.5" customHeight="1"/>
-    <row r="942" ht="22.5" customHeight="1"/>
-    <row r="943" ht="22.5" customHeight="1"/>
-    <row r="944" ht="22.5" customHeight="1"/>
-    <row r="945" ht="22.5" customHeight="1"/>
-    <row r="946" ht="22.5" customHeight="1"/>
-    <row r="947" ht="22.5" customHeight="1"/>
-    <row r="948" ht="22.5" customHeight="1"/>
-    <row r="949" ht="22.5" customHeight="1"/>
-    <row r="950" ht="22.5" customHeight="1"/>
-    <row r="951" ht="22.5" customHeight="1"/>
-    <row r="952" ht="22.5" customHeight="1"/>
-    <row r="953" ht="22.5" customHeight="1"/>
-    <row r="954" ht="22.5" customHeight="1"/>
-    <row r="955" ht="22.5" customHeight="1"/>
-    <row r="956" ht="22.5" customHeight="1"/>
-    <row r="957" ht="22.5" customHeight="1"/>
-    <row r="958" ht="22.5" customHeight="1"/>
-    <row r="959" ht="22.5" customHeight="1"/>
-    <row r="960" ht="22.5" customHeight="1"/>
-    <row r="961" ht="22.5" customHeight="1"/>
-    <row r="962" ht="22.5" customHeight="1"/>
-    <row r="963" ht="22.5" customHeight="1"/>
-    <row r="964" ht="22.5" customHeight="1"/>
-    <row r="965" ht="22.5" customHeight="1"/>
-    <row r="966" ht="22.5" customHeight="1"/>
-    <row r="967" ht="22.5" customHeight="1"/>
-    <row r="968" ht="22.5" customHeight="1"/>
-    <row r="969" ht="22.5" customHeight="1"/>
-    <row r="970" ht="22.5" customHeight="1"/>
-    <row r="971" ht="22.5" customHeight="1"/>
-    <row r="972" ht="22.5" customHeight="1"/>
-    <row r="973" ht="22.5" customHeight="1"/>
-    <row r="974" ht="22.5" customHeight="1"/>
-    <row r="975" ht="22.5" customHeight="1"/>
-    <row r="976" ht="22.5" customHeight="1"/>
-    <row r="977" ht="22.5" customHeight="1"/>
-    <row r="978" ht="22.5" customHeight="1"/>
-    <row r="979" ht="22.5" customHeight="1"/>
-    <row r="980" ht="22.5" customHeight="1"/>
-    <row r="981" ht="22.5" customHeight="1"/>
-    <row r="982" ht="22.5" customHeight="1"/>
-    <row r="983" ht="22.5" customHeight="1"/>
-    <row r="984" ht="22.5" customHeight="1"/>
-    <row r="985" ht="22.5" customHeight="1"/>
-    <row r="986" ht="22.5" customHeight="1"/>
-    <row r="987" ht="22.5" customHeight="1"/>
-    <row r="988" ht="22.5" customHeight="1"/>
-    <row r="989" ht="22.5" customHeight="1"/>
-    <row r="990" ht="22.5" customHeight="1"/>
-    <row r="991" ht="22.5" customHeight="1"/>
-    <row r="992" ht="22.5" customHeight="1"/>
-    <row r="993" ht="22.5" customHeight="1"/>
-    <row r="994" ht="22.5" customHeight="1"/>
-    <row r="995" ht="22.5" customHeight="1"/>
-    <row r="996" ht="22.5" customHeight="1"/>
-    <row r="997" ht="22.5" customHeight="1"/>
-    <row r="998" ht="22.5" customHeight="1"/>
-    <row r="999" ht="22.5" customHeight="1"/>
-    <row r="1000" ht="22.5" customHeight="1"/>
-    <row r="1001" ht="22.5" customHeight="1"/>
+        <v>121</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="G25" s="10"/>
+    </row>
+    <row r="26" ht="22.5" customHeight="1">
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+    </row>
+    <row r="27" ht="22.5" customHeight="1">
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+    </row>
+    <row r="28" ht="22.5" customHeight="1">
+      <c r="F28" s="11"/>
+      <c r="G28" s="11"/>
+    </row>
+    <row r="29" ht="22.5" customHeight="1">
+      <c r="F29" s="11"/>
+      <c r="G29" s="11"/>
+    </row>
+    <row r="30" ht="22.5" customHeight="1">
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+    </row>
+    <row r="31" ht="22.5" customHeight="1">
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+    </row>
+    <row r="32" ht="22.5" customHeight="1">
+      <c r="F32" s="11"/>
+      <c r="G32" s="11"/>
+    </row>
+    <row r="33" ht="22.5" customHeight="1">
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+    </row>
+    <row r="34" ht="22.5" customHeight="1">
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+    </row>
+    <row r="35" ht="22.5" customHeight="1">
+      <c r="F35" s="11"/>
+      <c r="G35" s="11"/>
+    </row>
+    <row r="36" ht="22.5" customHeight="1">
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+    </row>
+    <row r="37" ht="22.5" customHeight="1">
+      <c r="F37" s="11"/>
+      <c r="G37" s="11"/>
+    </row>
+    <row r="38" ht="22.5" customHeight="1">
+      <c r="F38" s="11"/>
+      <c r="G38" s="11"/>
+    </row>
+    <row r="39" ht="22.5" customHeight="1">
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+    </row>
+    <row r="40" ht="22.5" customHeight="1">
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+    </row>
+    <row r="41" ht="22.5" customHeight="1">
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+    </row>
+    <row r="42" ht="22.5" customHeight="1">
+      <c r="F42" s="11"/>
+      <c r="G42" s="11"/>
+    </row>
+    <row r="43" ht="22.5" customHeight="1">
+      <c r="F43" s="11"/>
+      <c r="G43" s="11"/>
+    </row>
+    <row r="44" ht="22.5" customHeight="1">
+      <c r="F44" s="11"/>
+      <c r="G44" s="11"/>
+    </row>
+    <row r="45" ht="22.5" customHeight="1">
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+    </row>
+    <row r="46" ht="22.5" customHeight="1">
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+    </row>
+    <row r="47" ht="22.5" customHeight="1">
+      <c r="F47" s="11"/>
+      <c r="G47" s="11"/>
+    </row>
+    <row r="48" ht="22.5" customHeight="1">
+      <c r="F48" s="11"/>
+      <c r="G48" s="11"/>
+    </row>
+    <row r="49" ht="22.5" customHeight="1">
+      <c r="F49" s="11"/>
+      <c r="G49" s="11"/>
+    </row>
+    <row r="50" ht="22.5" customHeight="1">
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+    </row>
+    <row r="51" ht="22.5" customHeight="1">
+      <c r="F51" s="11"/>
+      <c r="G51" s="11"/>
+    </row>
+    <row r="52" ht="22.5" customHeight="1">
+      <c r="F52" s="11"/>
+      <c r="G52" s="11"/>
+    </row>
+    <row r="53" ht="22.5" customHeight="1">
+      <c r="F53" s="11"/>
+      <c r="G53" s="11"/>
+    </row>
+    <row r="54" ht="22.5" customHeight="1">
+      <c r="F54" s="11"/>
+      <c r="G54" s="11"/>
+    </row>
+    <row r="55" ht="22.5" customHeight="1">
+      <c r="F55" s="11"/>
+      <c r="G55" s="11"/>
+    </row>
+    <row r="56" ht="22.5" customHeight="1">
+      <c r="F56" s="11"/>
+      <c r="G56" s="11"/>
+    </row>
+    <row r="57" ht="22.5" customHeight="1">
+      <c r="F57" s="11"/>
+      <c r="G57" s="11"/>
+    </row>
+    <row r="58" ht="22.5" customHeight="1">
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+    </row>
+    <row r="59" ht="22.5" customHeight="1">
+      <c r="F59" s="11"/>
+      <c r="G59" s="11"/>
+    </row>
+    <row r="60" ht="22.5" customHeight="1">
+      <c r="F60" s="11"/>
+      <c r="G60" s="11"/>
+    </row>
+    <row r="61" ht="22.5" customHeight="1">
+      <c r="F61" s="11"/>
+      <c r="G61" s="11"/>
+    </row>
+    <row r="62" ht="22.5" customHeight="1">
+      <c r="F62" s="11"/>
+      <c r="G62" s="11"/>
+    </row>
+    <row r="63" ht="22.5" customHeight="1">
+      <c r="F63" s="11"/>
+      <c r="G63" s="11"/>
+    </row>
+    <row r="64" ht="22.5" customHeight="1">
+      <c r="F64" s="11"/>
+      <c r="G64" s="11"/>
+    </row>
+    <row r="65" ht="22.5" customHeight="1">
+      <c r="F65" s="11"/>
+      <c r="G65" s="11"/>
+    </row>
+    <row r="66" ht="22.5" customHeight="1">
+      <c r="F66" s="11"/>
+      <c r="G66" s="11"/>
+    </row>
+    <row r="67" ht="22.5" customHeight="1">
+      <c r="F67" s="11"/>
+      <c r="G67" s="11"/>
+    </row>
+    <row r="68" ht="22.5" customHeight="1">
+      <c r="F68" s="11"/>
+      <c r="G68" s="11"/>
+    </row>
+    <row r="69" ht="22.5" customHeight="1">
+      <c r="F69" s="11"/>
+      <c r="G69" s="11"/>
+    </row>
+    <row r="70" ht="22.5" customHeight="1">
+      <c r="F70" s="11"/>
+      <c r="G70" s="11"/>
+    </row>
+    <row r="71" ht="22.5" customHeight="1">
+      <c r="F71" s="11"/>
+      <c r="G71" s="11"/>
+    </row>
+    <row r="72" ht="22.5" customHeight="1">
+      <c r="F72" s="11"/>
+      <c r="G72" s="11"/>
+    </row>
+    <row r="73" ht="22.5" customHeight="1">
+      <c r="F73" s="11"/>
+      <c r="G73" s="11"/>
+    </row>
+    <row r="74" ht="22.5" customHeight="1">
+      <c r="F74" s="11"/>
+      <c r="G74" s="11"/>
+    </row>
+    <row r="75" ht="22.5" customHeight="1">
+      <c r="F75" s="11"/>
+      <c r="G75" s="11"/>
+    </row>
+    <row r="76" ht="22.5" customHeight="1">
+      <c r="F76" s="11"/>
+      <c r="G76" s="11"/>
+    </row>
+    <row r="77" ht="22.5" customHeight="1">
+      <c r="F77" s="11"/>
+      <c r="G77" s="11"/>
+    </row>
+    <row r="78" ht="22.5" customHeight="1">
+      <c r="F78" s="11"/>
+      <c r="G78" s="11"/>
+    </row>
+    <row r="79" ht="22.5" customHeight="1">
+      <c r="F79" s="11"/>
+      <c r="G79" s="11"/>
+    </row>
+    <row r="80" ht="22.5" customHeight="1">
+      <c r="F80" s="11"/>
+      <c r="G80" s="11"/>
+    </row>
+    <row r="81" ht="22.5" customHeight="1">
+      <c r="F81" s="11"/>
+      <c r="G81" s="11"/>
+    </row>
+    <row r="82" ht="22.5" customHeight="1">
+      <c r="F82" s="11"/>
+      <c r="G82" s="11"/>
+    </row>
+    <row r="83" ht="22.5" customHeight="1">
+      <c r="F83" s="11"/>
+      <c r="G83" s="11"/>
+    </row>
+    <row r="84" ht="22.5" customHeight="1">
+      <c r="F84" s="11"/>
+      <c r="G84" s="11"/>
+    </row>
+    <row r="85" ht="22.5" customHeight="1">
+      <c r="F85" s="11"/>
+      <c r="G85" s="11"/>
+    </row>
+    <row r="86" ht="22.5" customHeight="1">
+      <c r="F86" s="11"/>
+      <c r="G86" s="11"/>
+    </row>
+    <row r="87" ht="22.5" customHeight="1">
+      <c r="F87" s="11"/>
+      <c r="G87" s="11"/>
+    </row>
+    <row r="88" ht="22.5" customHeight="1">
+      <c r="F88" s="11"/>
+      <c r="G88" s="11"/>
+    </row>
+    <row r="89" ht="22.5" customHeight="1">
+      <c r="F89" s="11"/>
+      <c r="G89" s="11"/>
+    </row>
+    <row r="90" ht="22.5" customHeight="1">
+      <c r="F90" s="11"/>
+      <c r="G90" s="11"/>
+    </row>
+    <row r="91" ht="22.5" customHeight="1">
+      <c r="F91" s="11"/>
+      <c r="G91" s="11"/>
+    </row>
+    <row r="92" ht="22.5" customHeight="1">
+      <c r="F92" s="11"/>
+      <c r="G92" s="11"/>
+    </row>
+    <row r="93" ht="22.5" customHeight="1">
+      <c r="F93" s="11"/>
+      <c r="G93" s="11"/>
+    </row>
+    <row r="94" ht="22.5" customHeight="1">
+      <c r="F94" s="11"/>
+      <c r="G94" s="11"/>
+    </row>
+    <row r="95" ht="22.5" customHeight="1">
+      <c r="F95" s="11"/>
+      <c r="G95" s="11"/>
+    </row>
+    <row r="96" ht="22.5" customHeight="1">
+      <c r="F96" s="11"/>
+      <c r="G96" s="11"/>
+    </row>
+    <row r="97" ht="22.5" customHeight="1">
+      <c r="F97" s="11"/>
+      <c r="G97" s="11"/>
+    </row>
+    <row r="98" ht="22.5" customHeight="1">
+      <c r="F98" s="11"/>
+      <c r="G98" s="11"/>
+    </row>
+    <row r="99" ht="22.5" customHeight="1">
+      <c r="F99" s="11"/>
+      <c r="G99" s="11"/>
+    </row>
+    <row r="100" ht="22.5" customHeight="1">
+      <c r="F100" s="11"/>
+      <c r="G100" s="11"/>
+    </row>
+    <row r="101" ht="22.5" customHeight="1">
+      <c r="F101" s="11"/>
+      <c r="G101" s="11"/>
+    </row>
+    <row r="102" ht="22.5" customHeight="1">
+      <c r="F102" s="11"/>
+      <c r="G102" s="11"/>
+    </row>
+    <row r="103" ht="22.5" customHeight="1">
+      <c r="F103" s="11"/>
+      <c r="G103" s="11"/>
+    </row>
+    <row r="104" ht="22.5" customHeight="1">
+      <c r="F104" s="11"/>
+      <c r="G104" s="11"/>
+    </row>
+    <row r="105" ht="22.5" customHeight="1">
+      <c r="F105" s="11"/>
+      <c r="G105" s="11"/>
+    </row>
+    <row r="106" ht="22.5" customHeight="1">
+      <c r="F106" s="11"/>
+      <c r="G106" s="11"/>
+    </row>
+    <row r="107" ht="22.5" customHeight="1">
+      <c r="F107" s="11"/>
+      <c r="G107" s="11"/>
+    </row>
+    <row r="108" ht="22.5" customHeight="1">
+      <c r="F108" s="11"/>
+      <c r="G108" s="11"/>
+    </row>
+    <row r="109" ht="22.5" customHeight="1">
+      <c r="F109" s="11"/>
+      <c r="G109" s="11"/>
+    </row>
+    <row r="110" ht="22.5" customHeight="1">
+      <c r="F110" s="11"/>
+      <c r="G110" s="11"/>
+    </row>
+    <row r="111" ht="22.5" customHeight="1">
+      <c r="F111" s="11"/>
+      <c r="G111" s="11"/>
+    </row>
+    <row r="112" ht="22.5" customHeight="1">
+      <c r="F112" s="11"/>
+      <c r="G112" s="11"/>
+    </row>
+    <row r="113" ht="22.5" customHeight="1">
+      <c r="F113" s="11"/>
+      <c r="G113" s="11"/>
+    </row>
+    <row r="114" ht="22.5" customHeight="1">
+      <c r="F114" s="11"/>
+      <c r="G114" s="11"/>
+    </row>
+    <row r="115" ht="22.5" customHeight="1">
+      <c r="F115" s="11"/>
+      <c r="G115" s="11"/>
+    </row>
+    <row r="116" ht="22.5" customHeight="1">
+      <c r="F116" s="11"/>
+      <c r="G116" s="11"/>
+    </row>
+    <row r="117" ht="22.5" customHeight="1">
+      <c r="F117" s="11"/>
+      <c r="G117" s="11"/>
+    </row>
+    <row r="118" ht="22.5" customHeight="1">
+      <c r="F118" s="11"/>
+      <c r="G118" s="11"/>
+    </row>
+    <row r="119" ht="22.5" customHeight="1">
+      <c r="F119" s="11"/>
+      <c r="G119" s="11"/>
+    </row>
+    <row r="120" ht="22.5" customHeight="1">
+      <c r="F120" s="11"/>
+      <c r="G120" s="11"/>
+    </row>
+    <row r="121" ht="22.5" customHeight="1">
+      <c r="F121" s="11"/>
+      <c r="G121" s="11"/>
+    </row>
+    <row r="122" ht="22.5" customHeight="1">
+      <c r="F122" s="11"/>
+      <c r="G122" s="11"/>
+    </row>
+    <row r="123" ht="22.5" customHeight="1">
+      <c r="F123" s="11"/>
+      <c r="G123" s="11"/>
+    </row>
+    <row r="124" ht="22.5" customHeight="1">
+      <c r="F124" s="11"/>
+      <c r="G124" s="11"/>
+    </row>
+    <row r="125" ht="22.5" customHeight="1">
+      <c r="F125" s="11"/>
+      <c r="G125" s="11"/>
+    </row>
+    <row r="126" ht="22.5" customHeight="1">
+      <c r="F126" s="11"/>
+      <c r="G126" s="11"/>
+    </row>
+    <row r="127" ht="22.5" customHeight="1">
+      <c r="F127" s="11"/>
+      <c r="G127" s="11"/>
+    </row>
+    <row r="128" ht="22.5" customHeight="1">
+      <c r="F128" s="11"/>
+      <c r="G128" s="11"/>
+    </row>
+    <row r="129" ht="22.5" customHeight="1">
+      <c r="F129" s="11"/>
+      <c r="G129" s="11"/>
+    </row>
+    <row r="130" ht="22.5" customHeight="1">
+      <c r="F130" s="11"/>
+      <c r="G130" s="11"/>
+    </row>
+    <row r="131" ht="22.5" customHeight="1">
+      <c r="F131" s="11"/>
+      <c r="G131" s="11"/>
+    </row>
+    <row r="132" ht="22.5" customHeight="1">
+      <c r="F132" s="11"/>
+      <c r="G132" s="11"/>
+    </row>
+    <row r="133" ht="22.5" customHeight="1">
+      <c r="F133" s="11"/>
+      <c r="G133" s="11"/>
+    </row>
+    <row r="134" ht="22.5" customHeight="1">
+      <c r="F134" s="11"/>
+      <c r="G134" s="11"/>
+    </row>
+    <row r="135" ht="22.5" customHeight="1">
+      <c r="F135" s="11"/>
+      <c r="G135" s="11"/>
+    </row>
+    <row r="136" ht="22.5" customHeight="1">
+      <c r="F136" s="11"/>
+      <c r="G136" s="11"/>
+    </row>
+    <row r="137" ht="22.5" customHeight="1">
+      <c r="F137" s="11"/>
+      <c r="G137" s="11"/>
+    </row>
+    <row r="138" ht="22.5" customHeight="1">
+      <c r="F138" s="11"/>
+      <c r="G138" s="11"/>
+    </row>
+    <row r="139" ht="22.5" customHeight="1">
+      <c r="F139" s="11"/>
+      <c r="G139" s="11"/>
+    </row>
+    <row r="140" ht="22.5" customHeight="1">
+      <c r="F140" s="11"/>
+      <c r="G140" s="11"/>
+    </row>
+    <row r="141" ht="22.5" customHeight="1">
+      <c r="F141" s="11"/>
+      <c r="G141" s="11"/>
+    </row>
+    <row r="142" ht="22.5" customHeight="1">
+      <c r="F142" s="11"/>
+      <c r="G142" s="11"/>
+    </row>
+    <row r="143" ht="22.5" customHeight="1">
+      <c r="F143" s="11"/>
+      <c r="G143" s="11"/>
+    </row>
+    <row r="144" ht="22.5" customHeight="1">
+      <c r="F144" s="11"/>
+      <c r="G144" s="11"/>
+    </row>
+    <row r="145" ht="22.5" customHeight="1">
+      <c r="F145" s="11"/>
+      <c r="G145" s="11"/>
+    </row>
+    <row r="146" ht="22.5" customHeight="1">
+      <c r="F146" s="11"/>
+      <c r="G146" s="11"/>
+    </row>
+    <row r="147" ht="22.5" customHeight="1">
+      <c r="F147" s="11"/>
+      <c r="G147" s="11"/>
+    </row>
+    <row r="148" ht="22.5" customHeight="1">
+      <c r="F148" s="11"/>
+      <c r="G148" s="11"/>
+    </row>
+    <row r="149" ht="22.5" customHeight="1">
+      <c r="F149" s="11"/>
+      <c r="G149" s="11"/>
+    </row>
+    <row r="150" ht="22.5" customHeight="1">
+      <c r="F150" s="11"/>
+      <c r="G150" s="11"/>
+    </row>
+    <row r="151" ht="22.5" customHeight="1">
+      <c r="F151" s="11"/>
+      <c r="G151" s="11"/>
+    </row>
+    <row r="152" ht="22.5" customHeight="1">
+      <c r="F152" s="11"/>
+      <c r="G152" s="11"/>
+    </row>
+    <row r="153" ht="22.5" customHeight="1">
+      <c r="F153" s="11"/>
+      <c r="G153" s="11"/>
+    </row>
+    <row r="154" ht="22.5" customHeight="1">
+      <c r="F154" s="11"/>
+      <c r="G154" s="11"/>
+    </row>
+    <row r="155" ht="22.5" customHeight="1">
+      <c r="F155" s="11"/>
+      <c r="G155" s="11"/>
+    </row>
+    <row r="156" ht="22.5" customHeight="1">
+      <c r="F156" s="11"/>
+      <c r="G156" s="11"/>
+    </row>
+    <row r="157" ht="22.5" customHeight="1">
+      <c r="F157" s="11"/>
+      <c r="G157" s="11"/>
+    </row>
+    <row r="158" ht="22.5" customHeight="1">
+      <c r="F158" s="11"/>
+      <c r="G158" s="11"/>
+    </row>
+    <row r="159" ht="22.5" customHeight="1">
+      <c r="F159" s="11"/>
+      <c r="G159" s="11"/>
+    </row>
+    <row r="160" ht="22.5" customHeight="1">
+      <c r="F160" s="11"/>
+      <c r="G160" s="11"/>
+    </row>
+    <row r="161" ht="22.5" customHeight="1">
+      <c r="F161" s="11"/>
+      <c r="G161" s="11"/>
+    </row>
+    <row r="162" ht="22.5" customHeight="1">
+      <c r="F162" s="11"/>
+      <c r="G162" s="11"/>
+    </row>
+    <row r="163" ht="22.5" customHeight="1">
+      <c r="F163" s="11"/>
+      <c r="G163" s="11"/>
+    </row>
+    <row r="164" ht="22.5" customHeight="1">
+      <c r="F164" s="11"/>
+      <c r="G164" s="11"/>
+    </row>
+    <row r="165" ht="22.5" customHeight="1">
+      <c r="F165" s="11"/>
+      <c r="G165" s="11"/>
+    </row>
+    <row r="166" ht="22.5" customHeight="1">
+      <c r="F166" s="11"/>
+      <c r="G166" s="11"/>
+    </row>
+    <row r="167" ht="22.5" customHeight="1">
+      <c r="F167" s="11"/>
+      <c r="G167" s="11"/>
+    </row>
+    <row r="168" ht="22.5" customHeight="1">
+      <c r="F168" s="11"/>
+      <c r="G168" s="11"/>
+    </row>
+    <row r="169" ht="22.5" customHeight="1">
+      <c r="F169" s="11"/>
+      <c r="G169" s="11"/>
+    </row>
+    <row r="170" ht="22.5" customHeight="1">
+      <c r="F170" s="11"/>
+      <c r="G170" s="11"/>
+    </row>
+    <row r="171" ht="22.5" customHeight="1">
+      <c r="F171" s="11"/>
+      <c r="G171" s="11"/>
+    </row>
+    <row r="172" ht="22.5" customHeight="1">
+      <c r="F172" s="11"/>
+      <c r="G172" s="11"/>
+    </row>
+    <row r="173" ht="22.5" customHeight="1">
+      <c r="F173" s="11"/>
+      <c r="G173" s="11"/>
+    </row>
+    <row r="174" ht="22.5" customHeight="1">
+      <c r="F174" s="11"/>
+      <c r="G174" s="11"/>
+    </row>
+    <row r="175" ht="22.5" customHeight="1">
+      <c r="F175" s="11"/>
+      <c r="G175" s="11"/>
+    </row>
+    <row r="176" ht="22.5" customHeight="1">
+      <c r="F176" s="11"/>
+      <c r="G176" s="11"/>
+    </row>
+    <row r="177" ht="22.5" customHeight="1">
+      <c r="F177" s="11"/>
+      <c r="G177" s="11"/>
+    </row>
+    <row r="178" ht="22.5" customHeight="1">
+      <c r="F178" s="11"/>
+      <c r="G178" s="11"/>
+    </row>
+    <row r="179" ht="22.5" customHeight="1">
+      <c r="F179" s="11"/>
+      <c r="G179" s="11"/>
+    </row>
+    <row r="180" ht="22.5" customHeight="1">
+      <c r="F180" s="11"/>
+      <c r="G180" s="11"/>
+    </row>
+    <row r="181" ht="22.5" customHeight="1">
+      <c r="F181" s="11"/>
+      <c r="G181" s="11"/>
+    </row>
+    <row r="182" ht="22.5" customHeight="1">
+      <c r="F182" s="11"/>
+      <c r="G182" s="11"/>
+    </row>
+    <row r="183" ht="22.5" customHeight="1">
+      <c r="F183" s="11"/>
+      <c r="G183" s="11"/>
+    </row>
+    <row r="184" ht="22.5" customHeight="1">
+      <c r="F184" s="11"/>
+      <c r="G184" s="11"/>
+    </row>
+    <row r="185" ht="22.5" customHeight="1">
+      <c r="F185" s="11"/>
+      <c r="G185" s="11"/>
+    </row>
+    <row r="186" ht="22.5" customHeight="1">
+      <c r="F186" s="11"/>
+      <c r="G186" s="11"/>
+    </row>
+    <row r="187" ht="22.5" customHeight="1">
+      <c r="F187" s="11"/>
+      <c r="G187" s="11"/>
+    </row>
+    <row r="188" ht="22.5" customHeight="1">
+      <c r="F188" s="11"/>
+      <c r="G188" s="11"/>
+    </row>
+    <row r="189" ht="22.5" customHeight="1">
+      <c r="F189" s="11"/>
+      <c r="G189" s="11"/>
+    </row>
+    <row r="190" ht="22.5" customHeight="1">
+      <c r="F190" s="11"/>
+      <c r="G190" s="11"/>
+    </row>
+    <row r="191" ht="22.5" customHeight="1">
+      <c r="F191" s="11"/>
+      <c r="G191" s="11"/>
+    </row>
+    <row r="192" ht="22.5" customHeight="1">
+      <c r="F192" s="11"/>
+      <c r="G192" s="11"/>
+    </row>
+    <row r="193" ht="22.5" customHeight="1">
+      <c r="F193" s="11"/>
+      <c r="G193" s="11"/>
+    </row>
+    <row r="194" ht="22.5" customHeight="1">
+      <c r="F194" s="11"/>
+      <c r="G194" s="11"/>
+    </row>
+    <row r="195" ht="22.5" customHeight="1">
+      <c r="F195" s="11"/>
+      <c r="G195" s="11"/>
+    </row>
+    <row r="196" ht="22.5" customHeight="1">
+      <c r="F196" s="11"/>
+      <c r="G196" s="11"/>
+    </row>
+    <row r="197" ht="22.5" customHeight="1">
+      <c r="F197" s="11"/>
+      <c r="G197" s="11"/>
+    </row>
+    <row r="198" ht="22.5" customHeight="1">
+      <c r="F198" s="11"/>
+      <c r="G198" s="11"/>
+    </row>
+    <row r="199" ht="22.5" customHeight="1">
+      <c r="F199" s="11"/>
+      <c r="G199" s="11"/>
+    </row>
+    <row r="200" ht="22.5" customHeight="1">
+      <c r="F200" s="11"/>
+      <c r="G200" s="11"/>
+    </row>
+    <row r="201" ht="22.5" customHeight="1">
+      <c r="F201" s="11"/>
+      <c r="G201" s="11"/>
+    </row>
+    <row r="202" ht="22.5" customHeight="1">
+      <c r="F202" s="11"/>
+      <c r="G202" s="11"/>
+    </row>
+    <row r="203" ht="22.5" customHeight="1">
+      <c r="F203" s="11"/>
+      <c r="G203" s="11"/>
+    </row>
+    <row r="204" ht="22.5" customHeight="1">
+      <c r="F204" s="11"/>
+      <c r="G204" s="11"/>
+    </row>
+    <row r="205" ht="22.5" customHeight="1">
+      <c r="F205" s="11"/>
+      <c r="G205" s="11"/>
+    </row>
+    <row r="206" ht="22.5" customHeight="1">
+      <c r="F206" s="11"/>
+      <c r="G206" s="11"/>
+    </row>
+    <row r="207" ht="22.5" customHeight="1">
+      <c r="F207" s="11"/>
+      <c r="G207" s="11"/>
+    </row>
+    <row r="208" ht="22.5" customHeight="1">
+      <c r="F208" s="11"/>
+      <c r="G208" s="11"/>
+    </row>
+    <row r="209" ht="22.5" customHeight="1">
+      <c r="F209" s="11"/>
+      <c r="G209" s="11"/>
+    </row>
+    <row r="210" ht="22.5" customHeight="1">
+      <c r="F210" s="11"/>
+      <c r="G210" s="11"/>
+    </row>
+    <row r="211" ht="22.5" customHeight="1">
+      <c r="F211" s="11"/>
+      <c r="G211" s="11"/>
+    </row>
+    <row r="212" ht="22.5" customHeight="1">
+      <c r="F212" s="11"/>
+      <c r="G212" s="11"/>
+    </row>
+    <row r="213" ht="22.5" customHeight="1">
+      <c r="F213" s="11"/>
+      <c r="G213" s="11"/>
+    </row>
+    <row r="214" ht="22.5" customHeight="1">
+      <c r="F214" s="11"/>
+      <c r="G214" s="11"/>
+    </row>
+    <row r="215" ht="22.5" customHeight="1">
+      <c r="F215" s="11"/>
+      <c r="G215" s="11"/>
+    </row>
+    <row r="216" ht="22.5" customHeight="1">
+      <c r="F216" s="11"/>
+      <c r="G216" s="11"/>
+    </row>
+    <row r="217" ht="22.5" customHeight="1">
+      <c r="F217" s="11"/>
+      <c r="G217" s="11"/>
+    </row>
+    <row r="218" ht="22.5" customHeight="1">
+      <c r="F218" s="11"/>
+      <c r="G218" s="11"/>
+    </row>
+    <row r="219" ht="22.5" customHeight="1">
+      <c r="F219" s="11"/>
+      <c r="G219" s="11"/>
+    </row>
+    <row r="220" ht="22.5" customHeight="1">
+      <c r="F220" s="11"/>
+      <c r="G220" s="11"/>
+    </row>
+    <row r="221" ht="22.5" customHeight="1">
+      <c r="F221" s="11"/>
+      <c r="G221" s="11"/>
+    </row>
+    <row r="222" ht="22.5" customHeight="1">
+      <c r="F222" s="11"/>
+      <c r="G222" s="11"/>
+    </row>
+    <row r="223" ht="22.5" customHeight="1">
+      <c r="F223" s="11"/>
+      <c r="G223" s="11"/>
+    </row>
+    <row r="224" ht="22.5" customHeight="1">
+      <c r="F224" s="11"/>
+      <c r="G224" s="11"/>
+    </row>
+    <row r="225" ht="22.5" customHeight="1">
+      <c r="F225" s="11"/>
+      <c r="G225" s="11"/>
+    </row>
+    <row r="226" ht="22.5" customHeight="1">
+      <c r="F226" s="11"/>
+      <c r="G226" s="11"/>
+    </row>
+    <row r="227" ht="22.5" customHeight="1">
+      <c r="F227" s="11"/>
+      <c r="G227" s="11"/>
+    </row>
+    <row r="228" ht="22.5" customHeight="1">
+      <c r="F228" s="11"/>
+      <c r="G228" s="11"/>
+    </row>
+    <row r="229" ht="22.5" customHeight="1">
+      <c r="F229" s="11"/>
+      <c r="G229" s="11"/>
+    </row>
+    <row r="230" ht="22.5" customHeight="1">
+      <c r="F230" s="11"/>
+      <c r="G230" s="11"/>
+    </row>
+    <row r="231" ht="22.5" customHeight="1">
+      <c r="F231" s="11"/>
+      <c r="G231" s="11"/>
+    </row>
+    <row r="232" ht="22.5" customHeight="1">
+      <c r="F232" s="11"/>
+      <c r="G232" s="11"/>
+    </row>
+    <row r="233" ht="22.5" customHeight="1">
+      <c r="F233" s="11"/>
+      <c r="G233" s="11"/>
+    </row>
+    <row r="234" ht="22.5" customHeight="1">
+      <c r="F234" s="11"/>
+      <c r="G234" s="11"/>
+    </row>
+    <row r="235" ht="22.5" customHeight="1">
+      <c r="F235" s="11"/>
+      <c r="G235" s="11"/>
+    </row>
+    <row r="236" ht="22.5" customHeight="1">
+      <c r="F236" s="11"/>
+      <c r="G236" s="11"/>
+    </row>
+    <row r="237" ht="22.5" customHeight="1">
+      <c r="F237" s="11"/>
+      <c r="G237" s="11"/>
+    </row>
+    <row r="238" ht="22.5" customHeight="1">
+      <c r="F238" s="11"/>
+      <c r="G238" s="11"/>
+    </row>
+    <row r="239" ht="22.5" customHeight="1">
+      <c r="F239" s="11"/>
+      <c r="G239" s="11"/>
+    </row>
+    <row r="240" ht="22.5" customHeight="1">
+      <c r="F240" s="11"/>
+      <c r="G240" s="11"/>
+    </row>
+    <row r="241" ht="22.5" customHeight="1">
+      <c r="F241" s="11"/>
+      <c r="G241" s="11"/>
+    </row>
+    <row r="242" ht="22.5" customHeight="1">
+      <c r="F242" s="11"/>
+      <c r="G242" s="11"/>
+    </row>
+    <row r="243" ht="22.5" customHeight="1">
+      <c r="F243" s="11"/>
+      <c r="G243" s="11"/>
+    </row>
+    <row r="244" ht="22.5" customHeight="1">
+      <c r="F244" s="11"/>
+      <c r="G244" s="11"/>
+    </row>
+    <row r="245" ht="22.5" customHeight="1">
+      <c r="F245" s="11"/>
+      <c r="G245" s="11"/>
+    </row>
+    <row r="246" ht="22.5" customHeight="1">
+      <c r="F246" s="11"/>
+      <c r="G246" s="11"/>
+    </row>
+    <row r="247" ht="22.5" customHeight="1">
+      <c r="F247" s="11"/>
+      <c r="G247" s="11"/>
+    </row>
+    <row r="248" ht="22.5" customHeight="1">
+      <c r="F248" s="11"/>
+      <c r="G248" s="11"/>
+    </row>
+    <row r="249" ht="22.5" customHeight="1">
+      <c r="F249" s="11"/>
+      <c r="G249" s="11"/>
+    </row>
+    <row r="250" ht="22.5" customHeight="1">
+      <c r="F250" s="11"/>
+      <c r="G250" s="11"/>
+    </row>
+    <row r="251" ht="22.5" customHeight="1">
+      <c r="F251" s="11"/>
+      <c r="G251" s="11"/>
+    </row>
+    <row r="252" ht="22.5" customHeight="1">
+      <c r="F252" s="11"/>
+      <c r="G252" s="11"/>
+    </row>
+    <row r="253" ht="22.5" customHeight="1">
+      <c r="F253" s="11"/>
+      <c r="G253" s="11"/>
+    </row>
+    <row r="254" ht="22.5" customHeight="1">
+      <c r="F254" s="11"/>
+      <c r="G254" s="11"/>
+    </row>
+    <row r="255" ht="22.5" customHeight="1">
+      <c r="F255" s="11"/>
+      <c r="G255" s="11"/>
+    </row>
+    <row r="256" ht="22.5" customHeight="1">
+      <c r="F256" s="11"/>
+      <c r="G256" s="11"/>
+    </row>
+    <row r="257" ht="22.5" customHeight="1">
+      <c r="F257" s="11"/>
+      <c r="G257" s="11"/>
+    </row>
+    <row r="258" ht="22.5" customHeight="1">
+      <c r="F258" s="11"/>
+      <c r="G258" s="11"/>
+    </row>
+    <row r="259" ht="22.5" customHeight="1">
+      <c r="F259" s="11"/>
+      <c r="G259" s="11"/>
+    </row>
+    <row r="260" ht="22.5" customHeight="1">
+      <c r="F260" s="11"/>
+      <c r="G260" s="11"/>
+    </row>
+    <row r="261" ht="22.5" customHeight="1">
+      <c r="F261" s="11"/>
+      <c r="G261" s="11"/>
+    </row>
+    <row r="262" ht="22.5" customHeight="1">
+      <c r="F262" s="11"/>
+      <c r="G262" s="11"/>
+    </row>
+    <row r="263" ht="22.5" customHeight="1">
+      <c r="F263" s="11"/>
+      <c r="G263" s="11"/>
+    </row>
+    <row r="264" ht="22.5" customHeight="1">
+      <c r="F264" s="11"/>
+      <c r="G264" s="11"/>
+    </row>
+    <row r="265" ht="22.5" customHeight="1">
+      <c r="F265" s="11"/>
+      <c r="G265" s="11"/>
+    </row>
+    <row r="266" ht="22.5" customHeight="1">
+      <c r="F266" s="11"/>
+      <c r="G266" s="11"/>
+    </row>
+    <row r="267" ht="22.5" customHeight="1">
+      <c r="F267" s="11"/>
+      <c r="G267" s="11"/>
+    </row>
+    <row r="268" ht="22.5" customHeight="1">
+      <c r="F268" s="11"/>
+      <c r="G268" s="11"/>
+    </row>
+    <row r="269" ht="22.5" customHeight="1">
+      <c r="F269" s="11"/>
+      <c r="G269" s="11"/>
+    </row>
+    <row r="270" ht="22.5" customHeight="1">
+      <c r="F270" s="11"/>
+      <c r="G270" s="11"/>
+    </row>
+    <row r="271" ht="22.5" customHeight="1">
+      <c r="F271" s="11"/>
+      <c r="G271" s="11"/>
+    </row>
+    <row r="272" ht="22.5" customHeight="1">
+      <c r="F272" s="11"/>
+      <c r="G272" s="11"/>
+    </row>
+    <row r="273" ht="22.5" customHeight="1">
+      <c r="F273" s="11"/>
+      <c r="G273" s="11"/>
+    </row>
+    <row r="274" ht="22.5" customHeight="1">
+      <c r="F274" s="11"/>
+      <c r="G274" s="11"/>
+    </row>
+    <row r="275" ht="22.5" customHeight="1">
+      <c r="F275" s="11"/>
+      <c r="G275" s="11"/>
+    </row>
+    <row r="276" ht="22.5" customHeight="1">
+      <c r="F276" s="11"/>
+      <c r="G276" s="11"/>
+    </row>
+    <row r="277" ht="22.5" customHeight="1">
+      <c r="F277" s="11"/>
+      <c r="G277" s="11"/>
+    </row>
+    <row r="278" ht="22.5" customHeight="1">
+      <c r="F278" s="11"/>
+      <c r="G278" s="11"/>
+    </row>
+    <row r="279" ht="22.5" customHeight="1">
+      <c r="F279" s="11"/>
+      <c r="G279" s="11"/>
+    </row>
+    <row r="280" ht="22.5" customHeight="1">
+      <c r="F280" s="11"/>
+      <c r="G280" s="11"/>
+    </row>
+    <row r="281" ht="22.5" customHeight="1">
+      <c r="F281" s="11"/>
+      <c r="G281" s="11"/>
+    </row>
+    <row r="282" ht="22.5" customHeight="1">
+      <c r="F282" s="11"/>
+      <c r="G282" s="11"/>
+    </row>
+    <row r="283" ht="22.5" customHeight="1">
+      <c r="F283" s="11"/>
+      <c r="G283" s="11"/>
+    </row>
+    <row r="284" ht="22.5" customHeight="1">
+      <c r="F284" s="11"/>
+      <c r="G284" s="11"/>
+    </row>
+    <row r="285" ht="22.5" customHeight="1">
+      <c r="F285" s="11"/>
+      <c r="G285" s="11"/>
+    </row>
+    <row r="286" ht="22.5" customHeight="1">
+      <c r="F286" s="11"/>
+      <c r="G286" s="11"/>
+    </row>
+    <row r="287" ht="22.5" customHeight="1">
+      <c r="F287" s="11"/>
+      <c r="G287" s="11"/>
+    </row>
+    <row r="288" ht="22.5" customHeight="1">
+      <c r="F288" s="11"/>
+      <c r="G288" s="11"/>
+    </row>
+    <row r="289" ht="22.5" customHeight="1">
+      <c r="F289" s="11"/>
+      <c r="G289" s="11"/>
+    </row>
+    <row r="290" ht="22.5" customHeight="1">
+      <c r="F290" s="11"/>
+      <c r="G290" s="11"/>
+    </row>
+    <row r="291" ht="22.5" customHeight="1">
+      <c r="F291" s="11"/>
+      <c r="G291" s="11"/>
+    </row>
+    <row r="292" ht="22.5" customHeight="1">
+      <c r="F292" s="11"/>
+      <c r="G292" s="11"/>
+    </row>
+    <row r="293" ht="22.5" customHeight="1">
+      <c r="F293" s="11"/>
+      <c r="G293" s="11"/>
+    </row>
+    <row r="294" ht="22.5" customHeight="1">
+      <c r="F294" s="11"/>
+      <c r="G294" s="11"/>
+    </row>
+    <row r="295" ht="22.5" customHeight="1">
+      <c r="F295" s="11"/>
+      <c r="G295" s="11"/>
+    </row>
+    <row r="296" ht="22.5" customHeight="1">
+      <c r="F296" s="11"/>
+      <c r="G296" s="11"/>
+    </row>
+    <row r="297" ht="22.5" customHeight="1">
+      <c r="F297" s="11"/>
+      <c r="G297" s="11"/>
+    </row>
+    <row r="298" ht="22.5" customHeight="1">
+      <c r="F298" s="11"/>
+      <c r="G298" s="11"/>
+    </row>
+    <row r="299" ht="22.5" customHeight="1">
+      <c r="F299" s="11"/>
+      <c r="G299" s="11"/>
+    </row>
+    <row r="300" ht="22.5" customHeight="1">
+      <c r="F300" s="11"/>
+      <c r="G300" s="11"/>
+    </row>
+    <row r="301" ht="22.5" customHeight="1">
+      <c r="F301" s="11"/>
+      <c r="G301" s="11"/>
+    </row>
+    <row r="302" ht="22.5" customHeight="1">
+      <c r="F302" s="11"/>
+      <c r="G302" s="11"/>
+    </row>
+    <row r="303" ht="22.5" customHeight="1">
+      <c r="F303" s="11"/>
+      <c r="G303" s="11"/>
+    </row>
+    <row r="304" ht="22.5" customHeight="1">
+      <c r="F304" s="11"/>
+      <c r="G304" s="11"/>
+    </row>
+    <row r="305" ht="22.5" customHeight="1">
+      <c r="F305" s="11"/>
+      <c r="G305" s="11"/>
+    </row>
+    <row r="306" ht="22.5" customHeight="1">
+      <c r="F306" s="11"/>
+      <c r="G306" s="11"/>
+    </row>
+    <row r="307" ht="22.5" customHeight="1">
+      <c r="F307" s="11"/>
+      <c r="G307" s="11"/>
+    </row>
+    <row r="308" ht="22.5" customHeight="1">
+      <c r="F308" s="11"/>
+      <c r="G308" s="11"/>
+    </row>
+    <row r="309" ht="22.5" customHeight="1">
+      <c r="F309" s="11"/>
+      <c r="G309" s="11"/>
+    </row>
+    <row r="310" ht="22.5" customHeight="1">
+      <c r="F310" s="11"/>
+      <c r="G310" s="11"/>
+    </row>
+    <row r="311" ht="22.5" customHeight="1">
+      <c r="F311" s="11"/>
+      <c r="G311" s="11"/>
+    </row>
+    <row r="312" ht="22.5" customHeight="1">
+      <c r="F312" s="11"/>
+      <c r="G312" s="11"/>
+    </row>
+    <row r="313" ht="22.5" customHeight="1">
+      <c r="F313" s="11"/>
+      <c r="G313" s="11"/>
+    </row>
+    <row r="314" ht="22.5" customHeight="1">
+      <c r="F314" s="11"/>
+      <c r="G314" s="11"/>
+    </row>
+    <row r="315" ht="22.5" customHeight="1">
+      <c r="F315" s="11"/>
+      <c r="G315" s="11"/>
+    </row>
+    <row r="316" ht="22.5" customHeight="1">
+      <c r="F316" s="11"/>
+      <c r="G316" s="11"/>
+    </row>
+    <row r="317" ht="22.5" customHeight="1">
+      <c r="F317" s="11"/>
+      <c r="G317" s="11"/>
+    </row>
+    <row r="318" ht="22.5" customHeight="1">
+      <c r="F318" s="11"/>
+      <c r="G318" s="11"/>
+    </row>
+    <row r="319" ht="22.5" customHeight="1">
+      <c r="F319" s="11"/>
+      <c r="G319" s="11"/>
+    </row>
+    <row r="320" ht="22.5" customHeight="1">
+      <c r="F320" s="11"/>
+      <c r="G320" s="11"/>
+    </row>
+    <row r="321" ht="22.5" customHeight="1">
+      <c r="F321" s="11"/>
+      <c r="G321" s="11"/>
+    </row>
+    <row r="322" ht="22.5" customHeight="1">
+      <c r="F322" s="11"/>
+      <c r="G322" s="11"/>
+    </row>
+    <row r="323" ht="22.5" customHeight="1">
+      <c r="F323" s="11"/>
+      <c r="G323" s="11"/>
+    </row>
+    <row r="324" ht="22.5" customHeight="1">
+      <c r="F324" s="11"/>
+      <c r="G324" s="11"/>
+    </row>
+    <row r="325" ht="22.5" customHeight="1">
+      <c r="F325" s="11"/>
+      <c r="G325" s="11"/>
+    </row>
+    <row r="326" ht="22.5" customHeight="1">
+      <c r="F326" s="11"/>
+      <c r="G326" s="11"/>
+    </row>
+    <row r="327" ht="22.5" customHeight="1">
+      <c r="F327" s="11"/>
+      <c r="G327" s="11"/>
+    </row>
+    <row r="328" ht="22.5" customHeight="1">
+      <c r="F328" s="11"/>
+      <c r="G328" s="11"/>
+    </row>
+    <row r="329" ht="22.5" customHeight="1">
+      <c r="F329" s="11"/>
+      <c r="G329" s="11"/>
+    </row>
+    <row r="330" ht="22.5" customHeight="1">
+      <c r="F330" s="11"/>
+      <c r="G330" s="11"/>
+    </row>
+    <row r="331" ht="22.5" customHeight="1">
+      <c r="F331" s="11"/>
+      <c r="G331" s="11"/>
+    </row>
+    <row r="332" ht="22.5" customHeight="1">
+      <c r="F332" s="11"/>
+      <c r="G332" s="11"/>
+    </row>
+    <row r="333" ht="22.5" customHeight="1">
+      <c r="F333" s="11"/>
+      <c r="G333" s="11"/>
+    </row>
+    <row r="334" ht="22.5" customHeight="1">
+      <c r="F334" s="11"/>
+      <c r="G334" s="11"/>
+    </row>
+    <row r="335" ht="22.5" customHeight="1">
+      <c r="F335" s="11"/>
+      <c r="G335" s="11"/>
+    </row>
+    <row r="336" ht="22.5" customHeight="1">
+      <c r="F336" s="11"/>
+      <c r="G336" s="11"/>
+    </row>
+    <row r="337" ht="22.5" customHeight="1">
+      <c r="F337" s="11"/>
+      <c r="G337" s="11"/>
+    </row>
+    <row r="338" ht="22.5" customHeight="1">
+      <c r="F338" s="11"/>
+      <c r="G338" s="11"/>
+    </row>
+    <row r="339" ht="22.5" customHeight="1">
+      <c r="F339" s="11"/>
+      <c r="G339" s="11"/>
+    </row>
+    <row r="340" ht="22.5" customHeight="1">
+      <c r="F340" s="11"/>
+      <c r="G340" s="11"/>
+    </row>
+    <row r="341" ht="22.5" customHeight="1">
+      <c r="F341" s="11"/>
+      <c r="G341" s="11"/>
+    </row>
+    <row r="342" ht="22.5" customHeight="1">
+      <c r="F342" s="11"/>
+      <c r="G342" s="11"/>
+    </row>
+    <row r="343" ht="22.5" customHeight="1">
+      <c r="F343" s="11"/>
+      <c r="G343" s="11"/>
+    </row>
+    <row r="344" ht="22.5" customHeight="1">
+      <c r="F344" s="11"/>
+      <c r="G344" s="11"/>
+    </row>
+    <row r="345" ht="22.5" customHeight="1">
+      <c r="F345" s="11"/>
+      <c r="G345" s="11"/>
+    </row>
+    <row r="346" ht="22.5" customHeight="1">
+      <c r="F346" s="11"/>
+      <c r="G346" s="11"/>
+    </row>
+    <row r="347" ht="22.5" customHeight="1">
+      <c r="F347" s="11"/>
+      <c r="G347" s="11"/>
+    </row>
+    <row r="348" ht="22.5" customHeight="1">
+      <c r="F348" s="11"/>
+      <c r="G348" s="11"/>
+    </row>
+    <row r="349" ht="22.5" customHeight="1">
+      <c r="F349" s="11"/>
+      <c r="G349" s="11"/>
+    </row>
+    <row r="350" ht="22.5" customHeight="1">
+      <c r="F350" s="11"/>
+      <c r="G350" s="11"/>
+    </row>
+    <row r="351" ht="22.5" customHeight="1">
+      <c r="F351" s="11"/>
+      <c r="G351" s="11"/>
+    </row>
+    <row r="352" ht="22.5" customHeight="1">
+      <c r="F352" s="11"/>
+      <c r="G352" s="11"/>
+    </row>
+    <row r="353" ht="22.5" customHeight="1">
+      <c r="F353" s="11"/>
+      <c r="G353" s="11"/>
+    </row>
+    <row r="354" ht="22.5" customHeight="1">
+      <c r="F354" s="11"/>
+      <c r="G354" s="11"/>
+    </row>
+    <row r="355" ht="22.5" customHeight="1">
+      <c r="F355" s="11"/>
+      <c r="G355" s="11"/>
+    </row>
+    <row r="356" ht="22.5" customHeight="1">
+      <c r="F356" s="11"/>
+      <c r="G356" s="11"/>
+    </row>
+    <row r="357" ht="22.5" customHeight="1">
+      <c r="F357" s="11"/>
+      <c r="G357" s="11"/>
+    </row>
+    <row r="358" ht="22.5" customHeight="1">
+      <c r="F358" s="11"/>
+      <c r="G358" s="11"/>
+    </row>
+    <row r="359" ht="22.5" customHeight="1">
+      <c r="F359" s="11"/>
+      <c r="G359" s="11"/>
+    </row>
+    <row r="360" ht="22.5" customHeight="1">
+      <c r="F360" s="11"/>
+      <c r="G360" s="11"/>
+    </row>
+    <row r="361" ht="22.5" customHeight="1">
+      <c r="F361" s="11"/>
+      <c r="G361" s="11"/>
+    </row>
+    <row r="362" ht="22.5" customHeight="1">
+      <c r="F362" s="11"/>
+      <c r="G362" s="11"/>
+    </row>
+    <row r="363" ht="22.5" customHeight="1">
+      <c r="F363" s="11"/>
+      <c r="G363" s="11"/>
+    </row>
+    <row r="364" ht="22.5" customHeight="1">
+      <c r="F364" s="11"/>
+      <c r="G364" s="11"/>
+    </row>
+    <row r="365" ht="22.5" customHeight="1">
+      <c r="F365" s="11"/>
+      <c r="G365" s="11"/>
+    </row>
+    <row r="366" ht="22.5" customHeight="1">
+      <c r="F366" s="11"/>
+      <c r="G366" s="11"/>
+    </row>
+    <row r="367" ht="22.5" customHeight="1">
+      <c r="F367" s="11"/>
+      <c r="G367" s="11"/>
+    </row>
+    <row r="368" ht="22.5" customHeight="1">
+      <c r="F368" s="11"/>
+      <c r="G368" s="11"/>
+    </row>
+    <row r="369" ht="22.5" customHeight="1">
+      <c r="F369" s="11"/>
+      <c r="G369" s="11"/>
+    </row>
+    <row r="370" ht="22.5" customHeight="1">
+      <c r="F370" s="11"/>
+      <c r="G370" s="11"/>
+    </row>
+    <row r="371" ht="22.5" customHeight="1">
+      <c r="F371" s="11"/>
+      <c r="G371" s="11"/>
+    </row>
+    <row r="372" ht="22.5" customHeight="1">
+      <c r="F372" s="11"/>
+      <c r="G372" s="11"/>
+    </row>
+    <row r="373" ht="22.5" customHeight="1">
+      <c r="F373" s="11"/>
+      <c r="G373" s="11"/>
+    </row>
+    <row r="374" ht="22.5" customHeight="1">
+      <c r="F374" s="11"/>
+      <c r="G374" s="11"/>
+    </row>
+    <row r="375" ht="22.5" customHeight="1">
+      <c r="F375" s="11"/>
+      <c r="G375" s="11"/>
+    </row>
+    <row r="376" ht="22.5" customHeight="1">
+      <c r="F376" s="11"/>
+      <c r="G376" s="11"/>
+    </row>
+    <row r="377" ht="22.5" customHeight="1">
+      <c r="F377" s="11"/>
+      <c r="G377" s="11"/>
+    </row>
+    <row r="378" ht="22.5" customHeight="1">
+      <c r="F378" s="11"/>
+      <c r="G378" s="11"/>
+    </row>
+    <row r="379" ht="22.5" customHeight="1">
+      <c r="F379" s="11"/>
+      <c r="G379" s="11"/>
+    </row>
+    <row r="380" ht="22.5" customHeight="1">
+      <c r="F380" s="11"/>
+      <c r="G380" s="11"/>
+    </row>
+    <row r="381" ht="22.5" customHeight="1">
+      <c r="F381" s="11"/>
+      <c r="G381" s="11"/>
+    </row>
+    <row r="382" ht="22.5" customHeight="1">
+      <c r="F382" s="11"/>
+      <c r="G382" s="11"/>
+    </row>
+    <row r="383" ht="22.5" customHeight="1">
+      <c r="F383" s="11"/>
+      <c r="G383" s="11"/>
+    </row>
+    <row r="384" ht="22.5" customHeight="1">
+      <c r="F384" s="11"/>
+      <c r="G384" s="11"/>
+    </row>
+    <row r="385" ht="22.5" customHeight="1">
+      <c r="F385" s="11"/>
+      <c r="G385" s="11"/>
+    </row>
+    <row r="386" ht="22.5" customHeight="1">
+      <c r="F386" s="11"/>
+      <c r="G386" s="11"/>
+    </row>
+    <row r="387" ht="22.5" customHeight="1">
+      <c r="F387" s="11"/>
+      <c r="G387" s="11"/>
+    </row>
+    <row r="388" ht="22.5" customHeight="1">
+      <c r="F388" s="11"/>
+      <c r="G388" s="11"/>
+    </row>
+    <row r="389" ht="22.5" customHeight="1">
+      <c r="F389" s="11"/>
+      <c r="G389" s="11"/>
+    </row>
+    <row r="390" ht="22.5" customHeight="1">
+      <c r="F390" s="11"/>
+      <c r="G390" s="11"/>
+    </row>
+    <row r="391" ht="22.5" customHeight="1">
+      <c r="F391" s="11"/>
+      <c r="G391" s="11"/>
+    </row>
+    <row r="392" ht="22.5" customHeight="1">
+      <c r="F392" s="11"/>
+      <c r="G392" s="11"/>
+    </row>
+    <row r="393" ht="22.5" customHeight="1">
+      <c r="F393" s="11"/>
+      <c r="G393" s="11"/>
+    </row>
+    <row r="394" ht="22.5" customHeight="1">
+      <c r="F394" s="11"/>
+      <c r="G394" s="11"/>
+    </row>
+    <row r="395" ht="22.5" customHeight="1">
+      <c r="F395" s="11"/>
+      <c r="G395" s="11"/>
+    </row>
+    <row r="396" ht="22.5" customHeight="1">
+      <c r="F396" s="11"/>
+      <c r="G396" s="11"/>
+    </row>
+    <row r="397" ht="22.5" customHeight="1">
+      <c r="F397" s="11"/>
+      <c r="G397" s="11"/>
+    </row>
+    <row r="398" ht="22.5" customHeight="1">
+      <c r="F398" s="11"/>
+      <c r="G398" s="11"/>
+    </row>
+    <row r="399" ht="22.5" customHeight="1">
+      <c r="F399" s="11"/>
+      <c r="G399" s="11"/>
+    </row>
+    <row r="400" ht="22.5" customHeight="1">
+      <c r="F400" s="11"/>
+      <c r="G400" s="11"/>
+    </row>
+    <row r="401" ht="22.5" customHeight="1">
+      <c r="F401" s="11"/>
+      <c r="G401" s="11"/>
+    </row>
+    <row r="402" ht="22.5" customHeight="1">
+      <c r="F402" s="11"/>
+      <c r="G402" s="11"/>
+    </row>
+    <row r="403" ht="22.5" customHeight="1">
+      <c r="F403" s="11"/>
+      <c r="G403" s="11"/>
+    </row>
+    <row r="404" ht="22.5" customHeight="1">
+      <c r="F404" s="11"/>
+      <c r="G404" s="11"/>
+    </row>
+    <row r="405" ht="22.5" customHeight="1">
+      <c r="F405" s="11"/>
+      <c r="G405" s="11"/>
+    </row>
+    <row r="406" ht="22.5" customHeight="1">
+      <c r="F406" s="11"/>
+      <c r="G406" s="11"/>
+    </row>
+    <row r="407" ht="22.5" customHeight="1">
+      <c r="F407" s="11"/>
+      <c r="G407" s="11"/>
+    </row>
+    <row r="408" ht="22.5" customHeight="1">
+      <c r="F408" s="11"/>
+      <c r="G408" s="11"/>
+    </row>
+    <row r="409" ht="22.5" customHeight="1">
+      <c r="F409" s="11"/>
+      <c r="G409" s="11"/>
+    </row>
+    <row r="410" ht="22.5" customHeight="1">
+      <c r="F410" s="11"/>
+      <c r="G410" s="11"/>
+    </row>
+    <row r="411" ht="22.5" customHeight="1">
+      <c r="F411" s="11"/>
+      <c r="G411" s="11"/>
+    </row>
+    <row r="412" ht="22.5" customHeight="1">
+      <c r="F412" s="11"/>
+      <c r="G412" s="11"/>
+    </row>
+    <row r="413" ht="22.5" customHeight="1">
+      <c r="F413" s="11"/>
+      <c r="G413" s="11"/>
+    </row>
+    <row r="414" ht="22.5" customHeight="1">
+      <c r="F414" s="11"/>
+      <c r="G414" s="11"/>
+    </row>
+    <row r="415" ht="22.5" customHeight="1">
+      <c r="F415" s="11"/>
+      <c r="G415" s="11"/>
+    </row>
+    <row r="416" ht="22.5" customHeight="1">
+      <c r="F416" s="11"/>
+      <c r="G416" s="11"/>
+    </row>
+    <row r="417" ht="22.5" customHeight="1">
+      <c r="F417" s="11"/>
+      <c r="G417" s="11"/>
+    </row>
+    <row r="418" ht="22.5" customHeight="1">
+      <c r="F418" s="11"/>
+      <c r="G418" s="11"/>
+    </row>
+    <row r="419" ht="22.5" customHeight="1">
+      <c r="F419" s="11"/>
+      <c r="G419" s="11"/>
+    </row>
+    <row r="420" ht="22.5" customHeight="1">
+      <c r="F420" s="11"/>
+      <c r="G420" s="11"/>
+    </row>
+    <row r="421" ht="22.5" customHeight="1">
+      <c r="F421" s="11"/>
+      <c r="G421" s="11"/>
+    </row>
+    <row r="422" ht="22.5" customHeight="1">
+      <c r="F422" s="11"/>
+      <c r="G422" s="11"/>
+    </row>
+    <row r="423" ht="22.5" customHeight="1">
+      <c r="F423" s="11"/>
+      <c r="G423" s="11"/>
+    </row>
+    <row r="424" ht="22.5" customHeight="1">
+      <c r="F424" s="11"/>
+      <c r="G424" s="11"/>
+    </row>
+    <row r="425" ht="22.5" customHeight="1">
+      <c r="F425" s="11"/>
+      <c r="G425" s="11"/>
+    </row>
+    <row r="426" ht="22.5" customHeight="1">
+      <c r="F426" s="11"/>
+      <c r="G426" s="11"/>
+    </row>
+    <row r="427" ht="22.5" customHeight="1">
+      <c r="F427" s="11"/>
+      <c r="G427" s="11"/>
+    </row>
+    <row r="428" ht="22.5" customHeight="1">
+      <c r="F428" s="11"/>
+      <c r="G428" s="11"/>
+    </row>
+    <row r="429" ht="22.5" customHeight="1">
+      <c r="F429" s="11"/>
+      <c r="G429" s="11"/>
+    </row>
+    <row r="430" ht="22.5" customHeight="1">
+      <c r="F430" s="11"/>
+      <c r="G430" s="11"/>
+    </row>
+    <row r="431" ht="22.5" customHeight="1">
+      <c r="F431" s="11"/>
+      <c r="G431" s="11"/>
+    </row>
+    <row r="432" ht="22.5" customHeight="1">
+      <c r="F432" s="11"/>
+      <c r="G432" s="11"/>
+    </row>
+    <row r="433" ht="22.5" customHeight="1">
+      <c r="F433" s="11"/>
+      <c r="G433" s="11"/>
+    </row>
+    <row r="434" ht="22.5" customHeight="1">
+      <c r="F434" s="11"/>
+      <c r="G434" s="11"/>
+    </row>
+    <row r="435" ht="22.5" customHeight="1">
+      <c r="F435" s="11"/>
+      <c r="G435" s="11"/>
+    </row>
+    <row r="436" ht="22.5" customHeight="1">
+      <c r="F436" s="11"/>
+      <c r="G436" s="11"/>
+    </row>
+    <row r="437" ht="22.5" customHeight="1">
+      <c r="F437" s="11"/>
+      <c r="G437" s="11"/>
+    </row>
+    <row r="438" ht="22.5" customHeight="1">
+      <c r="F438" s="11"/>
+      <c r="G438" s="11"/>
+    </row>
+    <row r="439" ht="22.5" customHeight="1">
+      <c r="F439" s="11"/>
+      <c r="G439" s="11"/>
+    </row>
+    <row r="440" ht="22.5" customHeight="1">
+      <c r="F440" s="11"/>
+      <c r="G440" s="11"/>
+    </row>
+    <row r="441" ht="22.5" customHeight="1">
+      <c r="F441" s="11"/>
+      <c r="G441" s="11"/>
+    </row>
+    <row r="442" ht="22.5" customHeight="1">
+      <c r="F442" s="11"/>
+      <c r="G442" s="11"/>
+    </row>
+    <row r="443" ht="22.5" customHeight="1">
+      <c r="F443" s="11"/>
+      <c r="G443" s="11"/>
+    </row>
+    <row r="444" ht="22.5" customHeight="1">
+      <c r="F444" s="11"/>
+      <c r="G444" s="11"/>
+    </row>
+    <row r="445" ht="22.5" customHeight="1">
+      <c r="F445" s="11"/>
+      <c r="G445" s="11"/>
+    </row>
+    <row r="446" ht="22.5" customHeight="1">
+      <c r="F446" s="11"/>
+      <c r="G446" s="11"/>
+    </row>
+    <row r="447" ht="22.5" customHeight="1">
+      <c r="F447" s="11"/>
+      <c r="G447" s="11"/>
+    </row>
+    <row r="448" ht="22.5" customHeight="1">
+      <c r="F448" s="11"/>
+      <c r="G448" s="11"/>
+    </row>
+    <row r="449" ht="22.5" customHeight="1">
+      <c r="F449" s="11"/>
+      <c r="G449" s="11"/>
+    </row>
+    <row r="450" ht="22.5" customHeight="1">
+      <c r="F450" s="11"/>
+      <c r="G450" s="11"/>
+    </row>
+    <row r="451" ht="22.5" customHeight="1">
+      <c r="F451" s="11"/>
+      <c r="G451" s="11"/>
+    </row>
+    <row r="452" ht="22.5" customHeight="1">
+      <c r="F452" s="11"/>
+      <c r="G452" s="11"/>
+    </row>
+    <row r="453" ht="22.5" customHeight="1">
+      <c r="F453" s="11"/>
+      <c r="G453" s="11"/>
+    </row>
+    <row r="454" ht="22.5" customHeight="1">
+      <c r="F454" s="11"/>
+      <c r="G454" s="11"/>
+    </row>
+    <row r="455" ht="22.5" customHeight="1">
+      <c r="F455" s="11"/>
+      <c r="G455" s="11"/>
+    </row>
+    <row r="456" ht="22.5" customHeight="1">
+      <c r="F456" s="11"/>
+      <c r="G456" s="11"/>
+    </row>
+    <row r="457" ht="22.5" customHeight="1">
+      <c r="F457" s="11"/>
+      <c r="G457" s="11"/>
+    </row>
+    <row r="458" ht="22.5" customHeight="1">
+      <c r="F458" s="11"/>
+      <c r="G458" s="11"/>
+    </row>
+    <row r="459" ht="22.5" customHeight="1">
+      <c r="F459" s="11"/>
+      <c r="G459" s="11"/>
+    </row>
+    <row r="460" ht="22.5" customHeight="1">
+      <c r="F460" s="11"/>
+      <c r="G460" s="11"/>
+    </row>
+    <row r="461" ht="22.5" customHeight="1">
+      <c r="F461" s="11"/>
+      <c r="G461" s="11"/>
+    </row>
+    <row r="462" ht="22.5" customHeight="1">
+      <c r="F462" s="11"/>
+      <c r="G462" s="11"/>
+    </row>
+    <row r="463" ht="22.5" customHeight="1">
+      <c r="F463" s="11"/>
+      <c r="G463" s="11"/>
+    </row>
+    <row r="464" ht="22.5" customHeight="1">
+      <c r="F464" s="11"/>
+      <c r="G464" s="11"/>
+    </row>
+    <row r="465" ht="22.5" customHeight="1">
+      <c r="F465" s="11"/>
+      <c r="G465" s="11"/>
+    </row>
+    <row r="466" ht="22.5" customHeight="1">
+      <c r="F466" s="11"/>
+      <c r="G466" s="11"/>
+    </row>
+    <row r="467" ht="22.5" customHeight="1">
+      <c r="F467" s="11"/>
+      <c r="G467" s="11"/>
+    </row>
+    <row r="468" ht="22.5" customHeight="1">
+      <c r="F468" s="11"/>
+      <c r="G468" s="11"/>
+    </row>
+    <row r="469" ht="22.5" customHeight="1">
+      <c r="F469" s="11"/>
+      <c r="G469" s="11"/>
+    </row>
+    <row r="470" ht="22.5" customHeight="1">
+      <c r="F470" s="11"/>
+      <c r="G470" s="11"/>
+    </row>
+    <row r="471" ht="22.5" customHeight="1">
+      <c r="F471" s="11"/>
+      <c r="G471" s="11"/>
+    </row>
+    <row r="472" ht="22.5" customHeight="1">
+      <c r="F472" s="11"/>
+      <c r="G472" s="11"/>
+    </row>
+    <row r="473" ht="22.5" customHeight="1">
+      <c r="F473" s="11"/>
+      <c r="G473" s="11"/>
+    </row>
+    <row r="474" ht="22.5" customHeight="1">
+      <c r="F474" s="11"/>
+      <c r="G474" s="11"/>
+    </row>
+    <row r="475" ht="22.5" customHeight="1">
+      <c r="F475" s="11"/>
+      <c r="G475" s="11"/>
+    </row>
+    <row r="476" ht="22.5" customHeight="1">
+      <c r="F476" s="11"/>
+      <c r="G476" s="11"/>
+    </row>
+    <row r="477" ht="22.5" customHeight="1">
+      <c r="F477" s="11"/>
+      <c r="G477" s="11"/>
+    </row>
+    <row r="478" ht="22.5" customHeight="1">
+      <c r="F478" s="11"/>
+      <c r="G478" s="11"/>
+    </row>
+    <row r="479" ht="22.5" customHeight="1">
+      <c r="F479" s="11"/>
+      <c r="G479" s="11"/>
+    </row>
+    <row r="480" ht="22.5" customHeight="1">
+      <c r="F480" s="11"/>
+      <c r="G480" s="11"/>
+    </row>
+    <row r="481" ht="22.5" customHeight="1">
+      <c r="F481" s="11"/>
+      <c r="G481" s="11"/>
+    </row>
+    <row r="482" ht="22.5" customHeight="1">
+      <c r="F482" s="11"/>
+      <c r="G482" s="11"/>
+    </row>
+    <row r="483" ht="22.5" customHeight="1">
+      <c r="F483" s="11"/>
+      <c r="G483" s="11"/>
+    </row>
+    <row r="484" ht="22.5" customHeight="1">
+      <c r="F484" s="11"/>
+      <c r="G484" s="11"/>
+    </row>
+    <row r="485" ht="22.5" customHeight="1">
+      <c r="F485" s="11"/>
+      <c r="G485" s="11"/>
+    </row>
+    <row r="486" ht="22.5" customHeight="1">
+      <c r="F486" s="11"/>
+      <c r="G486" s="11"/>
+    </row>
+    <row r="487" ht="22.5" customHeight="1">
+      <c r="F487" s="11"/>
+      <c r="G487" s="11"/>
+    </row>
+    <row r="488" ht="22.5" customHeight="1">
+      <c r="F488" s="11"/>
+      <c r="G488" s="11"/>
+    </row>
+    <row r="489" ht="22.5" customHeight="1">
+      <c r="F489" s="11"/>
+      <c r="G489" s="11"/>
+    </row>
+    <row r="490" ht="22.5" customHeight="1">
+      <c r="F490" s="11"/>
+      <c r="G490" s="11"/>
+    </row>
+    <row r="491" ht="22.5" customHeight="1">
+      <c r="F491" s="11"/>
+      <c r="G491" s="11"/>
+    </row>
+    <row r="492" ht="22.5" customHeight="1">
+      <c r="F492" s="11"/>
+      <c r="G492" s="11"/>
+    </row>
+    <row r="493" ht="22.5" customHeight="1">
+      <c r="F493" s="11"/>
+      <c r="G493" s="11"/>
+    </row>
+    <row r="494" ht="22.5" customHeight="1">
+      <c r="F494" s="11"/>
+      <c r="G494" s="11"/>
+    </row>
+    <row r="495" ht="22.5" customHeight="1">
+      <c r="F495" s="11"/>
+      <c r="G495" s="11"/>
+    </row>
+    <row r="496" ht="22.5" customHeight="1">
+      <c r="F496" s="11"/>
+      <c r="G496" s="11"/>
+    </row>
+    <row r="497" ht="22.5" customHeight="1">
+      <c r="F497" s="11"/>
+      <c r="G497" s="11"/>
+    </row>
+    <row r="498" ht="22.5" customHeight="1">
+      <c r="F498" s="11"/>
+      <c r="G498" s="11"/>
+    </row>
+    <row r="499" ht="22.5" customHeight="1">
+      <c r="F499" s="11"/>
+      <c r="G499" s="11"/>
+    </row>
+    <row r="500" ht="22.5" customHeight="1">
+      <c r="F500" s="11"/>
+      <c r="G500" s="11"/>
+    </row>
+    <row r="501" ht="22.5" customHeight="1">
+      <c r="F501" s="11"/>
+      <c r="G501" s="11"/>
+    </row>
+    <row r="502" ht="22.5" customHeight="1">
+      <c r="F502" s="11"/>
+      <c r="G502" s="11"/>
+    </row>
+    <row r="503" ht="22.5" customHeight="1">
+      <c r="F503" s="11"/>
+      <c r="G503" s="11"/>
+    </row>
+    <row r="504" ht="22.5" customHeight="1">
+      <c r="F504" s="11"/>
+      <c r="G504" s="11"/>
+    </row>
+    <row r="505" ht="22.5" customHeight="1">
+      <c r="F505" s="11"/>
+      <c r="G505" s="11"/>
+    </row>
+    <row r="506" ht="22.5" customHeight="1">
+      <c r="F506" s="11"/>
+      <c r="G506" s="11"/>
+    </row>
+    <row r="507" ht="22.5" customHeight="1">
+      <c r="F507" s="11"/>
+      <c r="G507" s="11"/>
+    </row>
+    <row r="508" ht="22.5" customHeight="1">
+      <c r="F508" s="11"/>
+      <c r="G508" s="11"/>
+    </row>
+    <row r="509" ht="22.5" customHeight="1">
+      <c r="F509" s="11"/>
+      <c r="G509" s="11"/>
+    </row>
+    <row r="510" ht="22.5" customHeight="1">
+      <c r="F510" s="11"/>
+      <c r="G510" s="11"/>
+    </row>
+    <row r="511" ht="22.5" customHeight="1">
+      <c r="F511" s="11"/>
+      <c r="G511" s="11"/>
+    </row>
+    <row r="512" ht="22.5" customHeight="1">
+      <c r="F512" s="11"/>
+      <c r="G512" s="11"/>
+    </row>
+    <row r="513" ht="22.5" customHeight="1">
+      <c r="F513" s="11"/>
+      <c r="G513" s="11"/>
+    </row>
+    <row r="514" ht="22.5" customHeight="1">
+      <c r="F514" s="11"/>
+      <c r="G514" s="11"/>
+    </row>
+    <row r="515" ht="22.5" customHeight="1">
+      <c r="F515" s="11"/>
+      <c r="G515" s="11"/>
+    </row>
+    <row r="516" ht="22.5" customHeight="1">
+      <c r="F516" s="11"/>
+      <c r="G516" s="11"/>
+    </row>
+    <row r="517" ht="22.5" customHeight="1">
+      <c r="F517" s="11"/>
+      <c r="G517" s="11"/>
+    </row>
+    <row r="518" ht="22.5" customHeight="1">
+      <c r="F518" s="11"/>
+      <c r="G518" s="11"/>
+    </row>
+    <row r="519" ht="22.5" customHeight="1">
+      <c r="F519" s="11"/>
+      <c r="G519" s="11"/>
+    </row>
+    <row r="520" ht="22.5" customHeight="1">
+      <c r="F520" s="11"/>
+      <c r="G520" s="11"/>
+    </row>
+    <row r="521" ht="22.5" customHeight="1">
+      <c r="F521" s="11"/>
+      <c r="G521" s="11"/>
+    </row>
+    <row r="522" ht="22.5" customHeight="1">
+      <c r="F522" s="11"/>
+      <c r="G522" s="11"/>
+    </row>
+    <row r="523" ht="22.5" customHeight="1">
+      <c r="F523" s="11"/>
+      <c r="G523" s="11"/>
+    </row>
+    <row r="524" ht="22.5" customHeight="1">
+      <c r="F524" s="11"/>
+      <c r="G524" s="11"/>
+    </row>
+    <row r="525" ht="22.5" customHeight="1">
+      <c r="F525" s="11"/>
+      <c r="G525" s="11"/>
+    </row>
+    <row r="526" ht="22.5" customHeight="1">
+      <c r="F526" s="11"/>
+      <c r="G526" s="11"/>
+    </row>
+    <row r="527" ht="22.5" customHeight="1">
+      <c r="F527" s="11"/>
+      <c r="G527" s="11"/>
+    </row>
+    <row r="528" ht="22.5" customHeight="1">
+      <c r="F528" s="11"/>
+      <c r="G528" s="11"/>
+    </row>
+    <row r="529" ht="22.5" customHeight="1">
+      <c r="F529" s="11"/>
+      <c r="G529" s="11"/>
+    </row>
+    <row r="530" ht="22.5" customHeight="1">
+      <c r="F530" s="11"/>
+      <c r="G530" s="11"/>
+    </row>
+    <row r="531" ht="22.5" customHeight="1">
+      <c r="F531" s="11"/>
+      <c r="G531" s="11"/>
+    </row>
+    <row r="532" ht="22.5" customHeight="1">
+      <c r="F532" s="11"/>
+      <c r="G532" s="11"/>
+    </row>
+    <row r="533" ht="22.5" customHeight="1">
+      <c r="F533" s="11"/>
+      <c r="G533" s="11"/>
+    </row>
+    <row r="534" ht="22.5" customHeight="1">
+      <c r="F534" s="11"/>
+      <c r="G534" s="11"/>
+    </row>
+    <row r="535" ht="22.5" customHeight="1">
+      <c r="F535" s="11"/>
+      <c r="G535" s="11"/>
+    </row>
+    <row r="536" ht="22.5" customHeight="1">
+      <c r="F536" s="11"/>
+      <c r="G536" s="11"/>
+    </row>
+    <row r="537" ht="22.5" customHeight="1">
+      <c r="F537" s="11"/>
+      <c r="G537" s="11"/>
+    </row>
+    <row r="538" ht="22.5" customHeight="1">
+      <c r="F538" s="11"/>
+      <c r="G538" s="11"/>
+    </row>
+    <row r="539" ht="22.5" customHeight="1">
+      <c r="F539" s="11"/>
+      <c r="G539" s="11"/>
+    </row>
+    <row r="540" ht="22.5" customHeight="1">
+      <c r="F540" s="11"/>
+      <c r="G540" s="11"/>
+    </row>
+    <row r="541" ht="22.5" customHeight="1">
+      <c r="F541" s="11"/>
+      <c r="G541" s="11"/>
+    </row>
+    <row r="542" ht="22.5" customHeight="1">
+      <c r="F542" s="11"/>
+      <c r="G542" s="11"/>
+    </row>
+    <row r="543" ht="22.5" customHeight="1">
+      <c r="F543" s="11"/>
+      <c r="G543" s="11"/>
+    </row>
+    <row r="544" ht="22.5" customHeight="1">
+      <c r="F544" s="11"/>
+      <c r="G544" s="11"/>
+    </row>
+    <row r="545" ht="22.5" customHeight="1">
+      <c r="F545" s="11"/>
+      <c r="G545" s="11"/>
+    </row>
+    <row r="546" ht="22.5" customHeight="1">
+      <c r="F546" s="11"/>
+      <c r="G546" s="11"/>
+    </row>
+    <row r="547" ht="22.5" customHeight="1">
+      <c r="F547" s="11"/>
+      <c r="G547" s="11"/>
+    </row>
+    <row r="548" ht="22.5" customHeight="1">
+      <c r="F548" s="11"/>
+      <c r="G548" s="11"/>
+    </row>
+    <row r="549" ht="22.5" customHeight="1">
+      <c r="F549" s="11"/>
+      <c r="G549" s="11"/>
+    </row>
+    <row r="550" ht="22.5" customHeight="1">
+      <c r="F550" s="11"/>
+      <c r="G550" s="11"/>
+    </row>
+    <row r="551" ht="22.5" customHeight="1">
+      <c r="F551" s="11"/>
+      <c r="G551" s="11"/>
+    </row>
+    <row r="552" ht="22.5" customHeight="1">
+      <c r="F552" s="11"/>
+      <c r="G552" s="11"/>
+    </row>
+    <row r="553" ht="22.5" customHeight="1">
+      <c r="F553" s="11"/>
+      <c r="G553" s="11"/>
+    </row>
+    <row r="554" ht="22.5" customHeight="1">
+      <c r="F554" s="11"/>
+      <c r="G554" s="11"/>
+    </row>
+    <row r="555" ht="22.5" customHeight="1">
+      <c r="F555" s="11"/>
+      <c r="G555" s="11"/>
+    </row>
+    <row r="556" ht="22.5" customHeight="1">
+      <c r="F556" s="11"/>
+      <c r="G556" s="11"/>
+    </row>
+    <row r="557" ht="22.5" customHeight="1">
+      <c r="F557" s="11"/>
+      <c r="G557" s="11"/>
+    </row>
+    <row r="558" ht="22.5" customHeight="1">
+      <c r="F558" s="11"/>
+      <c r="G558" s="11"/>
+    </row>
+    <row r="559" ht="22.5" customHeight="1">
+      <c r="F559" s="11"/>
+      <c r="G559" s="11"/>
+    </row>
+    <row r="560" ht="22.5" customHeight="1">
+      <c r="F560" s="11"/>
+      <c r="G560" s="11"/>
+    </row>
+    <row r="561" ht="22.5" customHeight="1">
+      <c r="F561" s="11"/>
+      <c r="G561" s="11"/>
+    </row>
+    <row r="562" ht="22.5" customHeight="1">
+      <c r="F562" s="11"/>
+      <c r="G562" s="11"/>
+    </row>
+    <row r="563" ht="22.5" customHeight="1">
+      <c r="F563" s="11"/>
+      <c r="G563" s="11"/>
+    </row>
+    <row r="564" ht="22.5" customHeight="1">
+      <c r="F564" s="11"/>
+      <c r="G564" s="11"/>
+    </row>
+    <row r="565" ht="22.5" customHeight="1">
+      <c r="F565" s="11"/>
+      <c r="G565" s="11"/>
+    </row>
+    <row r="566" ht="22.5" customHeight="1">
+      <c r="F566" s="11"/>
+      <c r="G566" s="11"/>
+    </row>
+    <row r="567" ht="22.5" customHeight="1">
+      <c r="F567" s="11"/>
+      <c r="G567" s="11"/>
+    </row>
+    <row r="568" ht="22.5" customHeight="1">
+      <c r="F568" s="11"/>
+      <c r="G568" s="11"/>
+    </row>
+    <row r="569" ht="22.5" customHeight="1">
+      <c r="F569" s="11"/>
+      <c r="G569" s="11"/>
+    </row>
+    <row r="570" ht="22.5" customHeight="1">
+      <c r="F570" s="11"/>
+      <c r="G570" s="11"/>
+    </row>
+    <row r="571" ht="22.5" customHeight="1">
+      <c r="F571" s="11"/>
+      <c r="G571" s="11"/>
+    </row>
+    <row r="572" ht="22.5" customHeight="1">
+      <c r="F572" s="11"/>
+      <c r="G572" s="11"/>
+    </row>
+    <row r="573" ht="22.5" customHeight="1">
+      <c r="F573" s="11"/>
+      <c r="G573" s="11"/>
+    </row>
+    <row r="574" ht="22.5" customHeight="1">
+      <c r="F574" s="11"/>
+      <c r="G574" s="11"/>
+    </row>
+    <row r="575" ht="22.5" customHeight="1">
+      <c r="F575" s="11"/>
+      <c r="G575" s="11"/>
+    </row>
+    <row r="576" ht="22.5" customHeight="1">
+      <c r="F576" s="11"/>
+      <c r="G576" s="11"/>
+    </row>
+    <row r="577" ht="22.5" customHeight="1">
+      <c r="F577" s="11"/>
+      <c r="G577" s="11"/>
+    </row>
+    <row r="578" ht="22.5" customHeight="1">
+      <c r="F578" s="11"/>
+      <c r="G578" s="11"/>
+    </row>
+    <row r="579" ht="22.5" customHeight="1">
+      <c r="F579" s="11"/>
+      <c r="G579" s="11"/>
+    </row>
+    <row r="580" ht="22.5" customHeight="1">
+      <c r="F580" s="11"/>
+      <c r="G580" s="11"/>
+    </row>
+    <row r="581" ht="22.5" customHeight="1">
+      <c r="F581" s="11"/>
+      <c r="G581" s="11"/>
+    </row>
+    <row r="582" ht="22.5" customHeight="1">
+      <c r="F582" s="11"/>
+      <c r="G582" s="11"/>
+    </row>
+    <row r="583" ht="22.5" customHeight="1">
+      <c r="F583" s="11"/>
+      <c r="G583" s="11"/>
+    </row>
+    <row r="584" ht="22.5" customHeight="1">
+      <c r="F584" s="11"/>
+      <c r="G584" s="11"/>
+    </row>
+    <row r="585" ht="22.5" customHeight="1">
+      <c r="F585" s="11"/>
+      <c r="G585" s="11"/>
+    </row>
+    <row r="586" ht="22.5" customHeight="1">
+      <c r="F586" s="11"/>
+      <c r="G586" s="11"/>
+    </row>
+    <row r="587" ht="22.5" customHeight="1">
+      <c r="F587" s="11"/>
+      <c r="G587" s="11"/>
+    </row>
+    <row r="588" ht="22.5" customHeight="1">
+      <c r="F588" s="11"/>
+      <c r="G588" s="11"/>
+    </row>
+    <row r="589" ht="22.5" customHeight="1">
+      <c r="F589" s="11"/>
+      <c r="G589" s="11"/>
+    </row>
+    <row r="590" ht="22.5" customHeight="1">
+      <c r="F590" s="11"/>
+      <c r="G590" s="11"/>
+    </row>
+    <row r="591" ht="22.5" customHeight="1">
+      <c r="F591" s="11"/>
+      <c r="G591" s="11"/>
+    </row>
+    <row r="592" ht="22.5" customHeight="1">
+      <c r="F592" s="11"/>
+      <c r="G592" s="11"/>
+    </row>
+    <row r="593" ht="22.5" customHeight="1">
+      <c r="F593" s="11"/>
+      <c r="G593" s="11"/>
+    </row>
+    <row r="594" ht="22.5" customHeight="1">
+      <c r="F594" s="11"/>
+      <c r="G594" s="11"/>
+    </row>
+    <row r="595" ht="22.5" customHeight="1">
+      <c r="F595" s="11"/>
+      <c r="G595" s="11"/>
+    </row>
+    <row r="596" ht="22.5" customHeight="1">
+      <c r="F596" s="11"/>
+      <c r="G596" s="11"/>
+    </row>
+    <row r="597" ht="22.5" customHeight="1">
+      <c r="F597" s="11"/>
+      <c r="G597" s="11"/>
+    </row>
+    <row r="598" ht="22.5" customHeight="1">
+      <c r="F598" s="11"/>
+      <c r="G598" s="11"/>
+    </row>
+    <row r="599" ht="22.5" customHeight="1">
+      <c r="F599" s="11"/>
+      <c r="G599" s="11"/>
+    </row>
+    <row r="600" ht="22.5" customHeight="1">
+      <c r="F600" s="11"/>
+      <c r="G600" s="11"/>
+    </row>
+    <row r="601" ht="22.5" customHeight="1">
+      <c r="F601" s="11"/>
+      <c r="G601" s="11"/>
+    </row>
+    <row r="602" ht="22.5" customHeight="1">
+      <c r="F602" s="11"/>
+      <c r="G602" s="11"/>
+    </row>
+    <row r="603" ht="22.5" customHeight="1">
+      <c r="F603" s="11"/>
+      <c r="G603" s="11"/>
+    </row>
+    <row r="604" ht="22.5" customHeight="1">
+      <c r="F604" s="11"/>
+      <c r="G604" s="11"/>
+    </row>
+    <row r="605" ht="22.5" customHeight="1">
+      <c r="F605" s="11"/>
+      <c r="G605" s="11"/>
+    </row>
+    <row r="606" ht="22.5" customHeight="1">
+      <c r="F606" s="11"/>
+      <c r="G606" s="11"/>
+    </row>
+    <row r="607" ht="22.5" customHeight="1">
+      <c r="F607" s="11"/>
+      <c r="G607" s="11"/>
+    </row>
+    <row r="608" ht="22.5" customHeight="1">
+      <c r="F608" s="11"/>
+      <c r="G608" s="11"/>
+    </row>
+    <row r="609" ht="22.5" customHeight="1">
+      <c r="F609" s="11"/>
+      <c r="G609" s="11"/>
+    </row>
+    <row r="610" ht="22.5" customHeight="1">
+      <c r="F610" s="11"/>
+      <c r="G610" s="11"/>
+    </row>
+    <row r="611" ht="22.5" customHeight="1">
+      <c r="F611" s="11"/>
+      <c r="G611" s="11"/>
+    </row>
+    <row r="612" ht="22.5" customHeight="1">
+      <c r="F612" s="11"/>
+      <c r="G612" s="11"/>
+    </row>
+    <row r="613" ht="22.5" customHeight="1">
+      <c r="F613" s="11"/>
+      <c r="G613" s="11"/>
+    </row>
+    <row r="614" ht="22.5" customHeight="1">
+      <c r="F614" s="11"/>
+      <c r="G614" s="11"/>
+    </row>
+    <row r="615" ht="22.5" customHeight="1">
+      <c r="F615" s="11"/>
+      <c r="G615" s="11"/>
+    </row>
+    <row r="616" ht="22.5" customHeight="1">
+      <c r="F616" s="11"/>
+      <c r="G616" s="11"/>
+    </row>
+    <row r="617" ht="22.5" customHeight="1">
+      <c r="F617" s="11"/>
+      <c r="G617" s="11"/>
+    </row>
+    <row r="618" ht="22.5" customHeight="1">
+      <c r="F618" s="11"/>
+      <c r="G618" s="11"/>
+    </row>
+    <row r="619" ht="22.5" customHeight="1">
+      <c r="F619" s="11"/>
+      <c r="G619" s="11"/>
+    </row>
+    <row r="620" ht="22.5" customHeight="1">
+      <c r="F620" s="11"/>
+      <c r="G620" s="11"/>
+    </row>
+    <row r="621" ht="22.5" customHeight="1">
+      <c r="F621" s="11"/>
+      <c r="G621" s="11"/>
+    </row>
+    <row r="622" ht="22.5" customHeight="1">
+      <c r="F622" s="11"/>
+      <c r="G622" s="11"/>
+    </row>
+    <row r="623" ht="22.5" customHeight="1">
+      <c r="F623" s="11"/>
+      <c r="G623" s="11"/>
+    </row>
+    <row r="624" ht="22.5" customHeight="1">
+      <c r="F624" s="11"/>
+      <c r="G624" s="11"/>
+    </row>
+    <row r="625" ht="22.5" customHeight="1">
+      <c r="F625" s="11"/>
+      <c r="G625" s="11"/>
+    </row>
+    <row r="626" ht="22.5" customHeight="1">
+      <c r="F626" s="11"/>
+      <c r="G626" s="11"/>
+    </row>
+    <row r="627" ht="22.5" customHeight="1">
+      <c r="F627" s="11"/>
+      <c r="G627" s="11"/>
+    </row>
+    <row r="628" ht="22.5" customHeight="1">
+      <c r="F628" s="11"/>
+      <c r="G628" s="11"/>
+    </row>
+    <row r="629" ht="22.5" customHeight="1">
+      <c r="F629" s="11"/>
+      <c r="G629" s="11"/>
+    </row>
+    <row r="630" ht="22.5" customHeight="1">
+      <c r="F630" s="11"/>
+      <c r="G630" s="11"/>
+    </row>
+    <row r="631" ht="22.5" customHeight="1">
+      <c r="F631" s="11"/>
+      <c r="G631" s="11"/>
+    </row>
+    <row r="632" ht="22.5" customHeight="1">
+      <c r="F632" s="11"/>
+      <c r="G632" s="11"/>
+    </row>
+    <row r="633" ht="22.5" customHeight="1">
+      <c r="F633" s="11"/>
+      <c r="G633" s="11"/>
+    </row>
+    <row r="634" ht="22.5" customHeight="1">
+      <c r="F634" s="11"/>
+      <c r="G634" s="11"/>
+    </row>
+    <row r="635" ht="22.5" customHeight="1">
+      <c r="F635" s="11"/>
+      <c r="G635" s="11"/>
+    </row>
+    <row r="636" ht="22.5" customHeight="1">
+      <c r="F636" s="11"/>
+      <c r="G636" s="11"/>
+    </row>
+    <row r="637" ht="22.5" customHeight="1">
+      <c r="F637" s="11"/>
+      <c r="G637" s="11"/>
+    </row>
+    <row r="638" ht="22.5" customHeight="1">
+      <c r="F638" s="11"/>
+      <c r="G638" s="11"/>
+    </row>
+    <row r="639" ht="22.5" customHeight="1">
+      <c r="F639" s="11"/>
+      <c r="G639" s="11"/>
+    </row>
+    <row r="640" ht="22.5" customHeight="1">
+      <c r="F640" s="11"/>
+      <c r="G640" s="11"/>
+    </row>
+    <row r="641" ht="22.5" customHeight="1">
+      <c r="F641" s="11"/>
+      <c r="G641" s="11"/>
+    </row>
+    <row r="642" ht="22.5" customHeight="1">
+      <c r="F642" s="11"/>
+      <c r="G642" s="11"/>
+    </row>
+    <row r="643" ht="22.5" customHeight="1">
+      <c r="F643" s="11"/>
+      <c r="G643" s="11"/>
+    </row>
+    <row r="644" ht="22.5" customHeight="1">
+      <c r="F644" s="11"/>
+      <c r="G644" s="11"/>
+    </row>
+    <row r="645" ht="22.5" customHeight="1">
+      <c r="F645" s="11"/>
+      <c r="G645" s="11"/>
+    </row>
+    <row r="646" ht="22.5" customHeight="1">
+      <c r="F646" s="11"/>
+      <c r="G646" s="11"/>
+    </row>
+    <row r="647" ht="22.5" customHeight="1">
+      <c r="F647" s="11"/>
+      <c r="G647" s="11"/>
+    </row>
+    <row r="648" ht="22.5" customHeight="1">
+      <c r="F648" s="11"/>
+      <c r="G648" s="11"/>
+    </row>
+    <row r="649" ht="22.5" customHeight="1">
+      <c r="F649" s="11"/>
+      <c r="G649" s="11"/>
+    </row>
+    <row r="650" ht="22.5" customHeight="1">
+      <c r="F650" s="11"/>
+      <c r="G650" s="11"/>
+    </row>
+    <row r="651" ht="22.5" customHeight="1">
+      <c r="F651" s="11"/>
+      <c r="G651" s="11"/>
+    </row>
+    <row r="652" ht="22.5" customHeight="1">
+      <c r="F652" s="11"/>
+      <c r="G652" s="11"/>
+    </row>
+    <row r="653" ht="22.5" customHeight="1">
+      <c r="F653" s="11"/>
+      <c r="G653" s="11"/>
+    </row>
+    <row r="654" ht="22.5" customHeight="1">
+      <c r="F654" s="11"/>
+      <c r="G654" s="11"/>
+    </row>
+    <row r="655" ht="22.5" customHeight="1">
+      <c r="F655" s="11"/>
+      <c r="G655" s="11"/>
+    </row>
+    <row r="656" ht="22.5" customHeight="1">
+      <c r="F656" s="11"/>
+      <c r="G656" s="11"/>
+    </row>
+    <row r="657" ht="22.5" customHeight="1">
+      <c r="F657" s="11"/>
+      <c r="G657" s="11"/>
+    </row>
+    <row r="658" ht="22.5" customHeight="1">
+      <c r="F658" s="11"/>
+      <c r="G658" s="11"/>
+    </row>
+    <row r="659" ht="22.5" customHeight="1">
+      <c r="F659" s="11"/>
+      <c r="G659" s="11"/>
+    </row>
+    <row r="660" ht="22.5" customHeight="1">
+      <c r="F660" s="11"/>
+      <c r="G660" s="11"/>
+    </row>
+    <row r="661" ht="22.5" customHeight="1">
+      <c r="F661" s="11"/>
+      <c r="G661" s="11"/>
+    </row>
+    <row r="662" ht="22.5" customHeight="1">
+      <c r="F662" s="11"/>
+      <c r="G662" s="11"/>
+    </row>
+    <row r="663" ht="22.5" customHeight="1">
+      <c r="F663" s="11"/>
+      <c r="G663" s="11"/>
+    </row>
+    <row r="664" ht="22.5" customHeight="1">
+      <c r="F664" s="11"/>
+      <c r="G664" s="11"/>
+    </row>
+    <row r="665" ht="22.5" customHeight="1">
+      <c r="F665" s="11"/>
+      <c r="G665" s="11"/>
+    </row>
+    <row r="666" ht="22.5" customHeight="1">
+      <c r="F666" s="11"/>
+      <c r="G666" s="11"/>
+    </row>
+    <row r="667" ht="22.5" customHeight="1">
+      <c r="F667" s="11"/>
+      <c r="G667" s="11"/>
+    </row>
+    <row r="668" ht="22.5" customHeight="1">
+      <c r="F668" s="11"/>
+      <c r="G668" s="11"/>
+    </row>
+    <row r="669" ht="22.5" customHeight="1">
+      <c r="F669" s="11"/>
+      <c r="G669" s="11"/>
+    </row>
+    <row r="670" ht="22.5" customHeight="1">
+      <c r="F670" s="11"/>
+      <c r="G670" s="11"/>
+    </row>
+    <row r="671" ht="22.5" customHeight="1">
+      <c r="F671" s="11"/>
+      <c r="G671" s="11"/>
+    </row>
+    <row r="672" ht="22.5" customHeight="1">
+      <c r="F672" s="11"/>
+      <c r="G672" s="11"/>
+    </row>
+    <row r="673" ht="22.5" customHeight="1">
+      <c r="F673" s="11"/>
+      <c r="G673" s="11"/>
+    </row>
+    <row r="674" ht="22.5" customHeight="1">
+      <c r="F674" s="11"/>
+      <c r="G674" s="11"/>
+    </row>
+    <row r="675" ht="22.5" customHeight="1">
+      <c r="F675" s="11"/>
+      <c r="G675" s="11"/>
+    </row>
+    <row r="676" ht="22.5" customHeight="1">
+      <c r="F676" s="11"/>
+      <c r="G676" s="11"/>
+    </row>
+    <row r="677" ht="22.5" customHeight="1">
+      <c r="F677" s="11"/>
+      <c r="G677" s="11"/>
+    </row>
+    <row r="678" ht="22.5" customHeight="1">
+      <c r="F678" s="11"/>
+      <c r="G678" s="11"/>
+    </row>
+    <row r="679" ht="22.5" customHeight="1">
+      <c r="F679" s="11"/>
+      <c r="G679" s="11"/>
+    </row>
+    <row r="680" ht="22.5" customHeight="1">
+      <c r="F680" s="11"/>
+      <c r="G680" s="11"/>
+    </row>
+    <row r="681" ht="22.5" customHeight="1">
+      <c r="F681" s="11"/>
+      <c r="G681" s="11"/>
+    </row>
+    <row r="682" ht="22.5" customHeight="1">
+      <c r="F682" s="11"/>
+      <c r="G682" s="11"/>
+    </row>
+    <row r="683" ht="22.5" customHeight="1">
+      <c r="F683" s="11"/>
+      <c r="G683" s="11"/>
+    </row>
+    <row r="684" ht="22.5" customHeight="1">
+      <c r="F684" s="11"/>
+      <c r="G684" s="11"/>
+    </row>
+    <row r="685" ht="22.5" customHeight="1">
+      <c r="F685" s="11"/>
+      <c r="G685" s="11"/>
+    </row>
+    <row r="686" ht="22.5" customHeight="1">
+      <c r="F686" s="11"/>
+      <c r="G686" s="11"/>
+    </row>
+    <row r="687" ht="22.5" customHeight="1">
+      <c r="F687" s="11"/>
+      <c r="G687" s="11"/>
+    </row>
+    <row r="688" ht="22.5" customHeight="1">
+      <c r="F688" s="11"/>
+      <c r="G688" s="11"/>
+    </row>
+    <row r="689" ht="22.5" customHeight="1">
+      <c r="F689" s="11"/>
+      <c r="G689" s="11"/>
+    </row>
+    <row r="690" ht="22.5" customHeight="1">
+      <c r="F690" s="11"/>
+      <c r="G690" s="11"/>
+    </row>
+    <row r="691" ht="22.5" customHeight="1">
+      <c r="F691" s="11"/>
+      <c r="G691" s="11"/>
+    </row>
+    <row r="692" ht="22.5" customHeight="1">
+      <c r="F692" s="11"/>
+      <c r="G692" s="11"/>
+    </row>
+    <row r="693" ht="22.5" customHeight="1">
+      <c r="F693" s="11"/>
+      <c r="G693" s="11"/>
+    </row>
+    <row r="694" ht="22.5" customHeight="1">
+      <c r="F694" s="11"/>
+      <c r="G694" s="11"/>
+    </row>
+    <row r="695" ht="22.5" customHeight="1">
+      <c r="F695" s="11"/>
+      <c r="G695" s="11"/>
+    </row>
+    <row r="696" ht="22.5" customHeight="1">
+      <c r="F696" s="11"/>
+      <c r="G696" s="11"/>
+    </row>
+    <row r="697" ht="22.5" customHeight="1">
+      <c r="F697" s="11"/>
+      <c r="G697" s="11"/>
+    </row>
+    <row r="698" ht="22.5" customHeight="1">
+      <c r="F698" s="11"/>
+      <c r="G698" s="11"/>
+    </row>
+    <row r="699" ht="22.5" customHeight="1">
+      <c r="F699" s="11"/>
+      <c r="G699" s="11"/>
+    </row>
+    <row r="700" ht="22.5" customHeight="1">
+      <c r="F700" s="11"/>
+      <c r="G700" s="11"/>
+    </row>
+    <row r="701" ht="22.5" customHeight="1">
+      <c r="F701" s="11"/>
+      <c r="G701" s="11"/>
+    </row>
+    <row r="702" ht="22.5" customHeight="1">
+      <c r="F702" s="11"/>
+      <c r="G702" s="11"/>
+    </row>
+    <row r="703" ht="22.5" customHeight="1">
+      <c r="F703" s="11"/>
+      <c r="G703" s="11"/>
+    </row>
+    <row r="704" ht="22.5" customHeight="1">
+      <c r="F704" s="11"/>
+      <c r="G704" s="11"/>
+    </row>
+    <row r="705" ht="22.5" customHeight="1">
+      <c r="F705" s="11"/>
+      <c r="G705" s="11"/>
+    </row>
+    <row r="706" ht="22.5" customHeight="1">
+      <c r="F706" s="11"/>
+      <c r="G706" s="11"/>
+    </row>
+    <row r="707" ht="22.5" customHeight="1">
+      <c r="F707" s="11"/>
+      <c r="G707" s="11"/>
+    </row>
+    <row r="708" ht="22.5" customHeight="1">
+      <c r="F708" s="11"/>
+      <c r="G708" s="11"/>
+    </row>
+    <row r="709" ht="22.5" customHeight="1">
+      <c r="F709" s="11"/>
+      <c r="G709" s="11"/>
+    </row>
+    <row r="710" ht="22.5" customHeight="1">
+      <c r="F710" s="11"/>
+      <c r="G710" s="11"/>
+    </row>
+    <row r="711" ht="22.5" customHeight="1">
+      <c r="F711" s="11"/>
+      <c r="G711" s="11"/>
+    </row>
+    <row r="712" ht="22.5" customHeight="1">
+      <c r="F712" s="11"/>
+      <c r="G712" s="11"/>
+    </row>
+    <row r="713" ht="22.5" customHeight="1">
+      <c r="F713" s="11"/>
+      <c r="G713" s="11"/>
+    </row>
+    <row r="714" ht="22.5" customHeight="1">
+      <c r="F714" s="11"/>
+      <c r="G714" s="11"/>
+    </row>
+    <row r="715" ht="22.5" customHeight="1">
+      <c r="F715" s="11"/>
+      <c r="G715" s="11"/>
+    </row>
+    <row r="716" ht="22.5" customHeight="1">
+      <c r="F716" s="11"/>
+      <c r="G716" s="11"/>
+    </row>
+    <row r="717" ht="22.5" customHeight="1">
+      <c r="F717" s="11"/>
+      <c r="G717" s="11"/>
+    </row>
+    <row r="718" ht="22.5" customHeight="1">
+      <c r="F718" s="11"/>
+      <c r="G718" s="11"/>
+    </row>
+    <row r="719" ht="22.5" customHeight="1">
+      <c r="F719" s="11"/>
+      <c r="G719" s="11"/>
+    </row>
+    <row r="720" ht="22.5" customHeight="1">
+      <c r="F720" s="11"/>
+      <c r="G720" s="11"/>
+    </row>
+    <row r="721" ht="22.5" customHeight="1">
+      <c r="F721" s="11"/>
+      <c r="G721" s="11"/>
+    </row>
+    <row r="722" ht="22.5" customHeight="1">
+      <c r="F722" s="11"/>
+      <c r="G722" s="11"/>
+    </row>
+    <row r="723" ht="22.5" customHeight="1">
+      <c r="F723" s="11"/>
+      <c r="G723" s="11"/>
+    </row>
+    <row r="724" ht="22.5" customHeight="1">
+      <c r="F724" s="11"/>
+      <c r="G724" s="11"/>
+    </row>
+    <row r="725" ht="22.5" customHeight="1">
+      <c r="F725" s="11"/>
+      <c r="G725" s="11"/>
+    </row>
+    <row r="726" ht="22.5" customHeight="1">
+      <c r="F726" s="11"/>
+      <c r="G726" s="11"/>
+    </row>
+    <row r="727" ht="22.5" customHeight="1">
+      <c r="F727" s="11"/>
+      <c r="G727" s="11"/>
+    </row>
+    <row r="728" ht="22.5" customHeight="1">
+      <c r="F728" s="11"/>
+      <c r="G728" s="11"/>
+    </row>
+    <row r="729" ht="22.5" customHeight="1">
+      <c r="F729" s="11"/>
+      <c r="G729" s="11"/>
+    </row>
+    <row r="730" ht="22.5" customHeight="1">
+      <c r="F730" s="11"/>
+      <c r="G730" s="11"/>
+    </row>
+    <row r="731" ht="22.5" customHeight="1">
+      <c r="F731" s="11"/>
+      <c r="G731" s="11"/>
+    </row>
+    <row r="732" ht="22.5" customHeight="1">
+      <c r="F732" s="11"/>
+      <c r="G732" s="11"/>
+    </row>
+    <row r="733" ht="22.5" customHeight="1">
+      <c r="F733" s="11"/>
+      <c r="G733" s="11"/>
+    </row>
+    <row r="734" ht="22.5" customHeight="1">
+      <c r="F734" s="11"/>
+      <c r="G734" s="11"/>
+    </row>
+    <row r="735" ht="22.5" customHeight="1">
+      <c r="F735" s="11"/>
+      <c r="G735" s="11"/>
+    </row>
+    <row r="736" ht="22.5" customHeight="1">
+      <c r="F736" s="11"/>
+      <c r="G736" s="11"/>
+    </row>
+    <row r="737" ht="22.5" customHeight="1">
+      <c r="F737" s="11"/>
+      <c r="G737" s="11"/>
+    </row>
+    <row r="738" ht="22.5" customHeight="1">
+      <c r="F738" s="11"/>
+      <c r="G738" s="11"/>
+    </row>
+    <row r="739" ht="22.5" customHeight="1">
+      <c r="F739" s="11"/>
+      <c r="G739" s="11"/>
+    </row>
+    <row r="740" ht="22.5" customHeight="1">
+      <c r="F740" s="11"/>
+      <c r="G740" s="11"/>
+    </row>
+    <row r="741" ht="22.5" customHeight="1">
+      <c r="F741" s="11"/>
+      <c r="G741" s="11"/>
+    </row>
+    <row r="742" ht="22.5" customHeight="1">
+      <c r="F742" s="11"/>
+      <c r="G742" s="11"/>
+    </row>
+    <row r="743" ht="22.5" customHeight="1">
+      <c r="F743" s="11"/>
+      <c r="G743" s="11"/>
+    </row>
+    <row r="744" ht="22.5" customHeight="1">
+      <c r="F744" s="11"/>
+      <c r="G744" s="11"/>
+    </row>
+    <row r="745" ht="22.5" customHeight="1">
+      <c r="F745" s="11"/>
+      <c r="G745" s="11"/>
+    </row>
+    <row r="746" ht="22.5" customHeight="1">
+      <c r="F746" s="11"/>
+      <c r="G746" s="11"/>
+    </row>
+    <row r="747" ht="22.5" customHeight="1">
+      <c r="F747" s="11"/>
+      <c r="G747" s="11"/>
+    </row>
+    <row r="748" ht="22.5" customHeight="1">
+      <c r="F748" s="11"/>
+      <c r="G748" s="11"/>
+    </row>
+    <row r="749" ht="22.5" customHeight="1">
+      <c r="F749" s="11"/>
+      <c r="G749" s="11"/>
+    </row>
+    <row r="750" ht="22.5" customHeight="1">
+      <c r="F750" s="11"/>
+      <c r="G750" s="11"/>
+    </row>
+    <row r="751" ht="22.5" customHeight="1">
+      <c r="F751" s="11"/>
+      <c r="G751" s="11"/>
+    </row>
+    <row r="752" ht="22.5" customHeight="1">
+      <c r="F752" s="11"/>
+      <c r="G752" s="11"/>
+    </row>
+    <row r="753" ht="22.5" customHeight="1">
+      <c r="F753" s="11"/>
+      <c r="G753" s="11"/>
+    </row>
+    <row r="754" ht="22.5" customHeight="1">
+      <c r="F754" s="11"/>
+      <c r="G754" s="11"/>
+    </row>
+    <row r="755" ht="22.5" customHeight="1">
+      <c r="F755" s="11"/>
+      <c r="G755" s="11"/>
+    </row>
+    <row r="756" ht="22.5" customHeight="1">
+      <c r="F756" s="11"/>
+      <c r="G756" s="11"/>
+    </row>
+    <row r="757" ht="22.5" customHeight="1">
+      <c r="F757" s="11"/>
+      <c r="G757" s="11"/>
+    </row>
+    <row r="758" ht="22.5" customHeight="1">
+      <c r="F758" s="11"/>
+      <c r="G758" s="11"/>
+    </row>
+    <row r="759" ht="22.5" customHeight="1">
+      <c r="F759" s="11"/>
+      <c r="G759" s="11"/>
+    </row>
+    <row r="760" ht="22.5" customHeight="1">
+      <c r="F760" s="11"/>
+      <c r="G760" s="11"/>
+    </row>
+    <row r="761" ht="22.5" customHeight="1">
+      <c r="F761" s="11"/>
+      <c r="G761" s="11"/>
+    </row>
+    <row r="762" ht="22.5" customHeight="1">
+      <c r="F762" s="11"/>
+      <c r="G762" s="11"/>
+    </row>
+    <row r="763" ht="22.5" customHeight="1">
+      <c r="F763" s="11"/>
+      <c r="G763" s="11"/>
+    </row>
+    <row r="764" ht="22.5" customHeight="1">
+      <c r="F764" s="11"/>
+      <c r="G764" s="11"/>
+    </row>
+    <row r="765" ht="22.5" customHeight="1">
+      <c r="F765" s="11"/>
+      <c r="G765" s="11"/>
+    </row>
+    <row r="766" ht="22.5" customHeight="1">
+      <c r="F766" s="11"/>
+      <c r="G766" s="11"/>
+    </row>
+    <row r="767" ht="22.5" customHeight="1">
+      <c r="F767" s="11"/>
+      <c r="G767" s="11"/>
+    </row>
+    <row r="768" ht="22.5" customHeight="1">
+      <c r="F768" s="11"/>
+      <c r="G768" s="11"/>
+    </row>
+    <row r="769" ht="22.5" customHeight="1">
+      <c r="F769" s="11"/>
+      <c r="G769" s="11"/>
+    </row>
+    <row r="770" ht="22.5" customHeight="1">
+      <c r="F770" s="11"/>
+      <c r="G770" s="11"/>
+    </row>
+    <row r="771" ht="22.5" customHeight="1">
+      <c r="F771" s="11"/>
+      <c r="G771" s="11"/>
+    </row>
+    <row r="772" ht="22.5" customHeight="1">
+      <c r="F772" s="11"/>
+      <c r="G772" s="11"/>
+    </row>
+    <row r="773" ht="22.5" customHeight="1">
+      <c r="F773" s="11"/>
+      <c r="G773" s="11"/>
+    </row>
+    <row r="774" ht="22.5" customHeight="1">
+      <c r="F774" s="11"/>
+      <c r="G774" s="11"/>
+    </row>
+    <row r="775" ht="22.5" customHeight="1">
+      <c r="F775" s="11"/>
+      <c r="G775" s="11"/>
+    </row>
+    <row r="776" ht="22.5" customHeight="1">
+      <c r="F776" s="11"/>
+      <c r="G776" s="11"/>
+    </row>
+    <row r="777" ht="22.5" customHeight="1">
+      <c r="F777" s="11"/>
+      <c r="G777" s="11"/>
+    </row>
+    <row r="778" ht="22.5" customHeight="1">
+      <c r="F778" s="11"/>
+      <c r="G778" s="11"/>
+    </row>
+    <row r="779" ht="22.5" customHeight="1">
+      <c r="F779" s="11"/>
+      <c r="G779" s="11"/>
+    </row>
+    <row r="780" ht="22.5" customHeight="1">
+      <c r="F780" s="11"/>
+      <c r="G780" s="11"/>
+    </row>
+    <row r="781" ht="22.5" customHeight="1">
+      <c r="F781" s="11"/>
+      <c r="G781" s="11"/>
+    </row>
+    <row r="782" ht="22.5" customHeight="1">
+      <c r="F782" s="11"/>
+      <c r="G782" s="11"/>
+    </row>
+    <row r="783" ht="22.5" customHeight="1">
+      <c r="F783" s="11"/>
+      <c r="G783" s="11"/>
+    </row>
+    <row r="784" ht="22.5" customHeight="1">
+      <c r="F784" s="11"/>
+      <c r="G784" s="11"/>
+    </row>
+    <row r="785" ht="22.5" customHeight="1">
+      <c r="F785" s="11"/>
+      <c r="G785" s="11"/>
+    </row>
+    <row r="786" ht="22.5" customHeight="1">
+      <c r="F786" s="11"/>
+      <c r="G786" s="11"/>
+    </row>
+    <row r="787" ht="22.5" customHeight="1">
+      <c r="F787" s="11"/>
+      <c r="G787" s="11"/>
+    </row>
+    <row r="788" ht="22.5" customHeight="1">
+      <c r="F788" s="11"/>
+      <c r="G788" s="11"/>
+    </row>
+    <row r="789" ht="22.5" customHeight="1">
+      <c r="F789" s="11"/>
+      <c r="G789" s="11"/>
+    </row>
+    <row r="790" ht="22.5" customHeight="1">
+      <c r="F790" s="11"/>
+      <c r="G790" s="11"/>
+    </row>
+    <row r="791" ht="22.5" customHeight="1">
+      <c r="F791" s="11"/>
+      <c r="G791" s="11"/>
+    </row>
+    <row r="792" ht="22.5" customHeight="1">
+      <c r="F792" s="11"/>
+      <c r="G792" s="11"/>
+    </row>
+    <row r="793" ht="22.5" customHeight="1">
+      <c r="F793" s="11"/>
+      <c r="G793" s="11"/>
+    </row>
+    <row r="794" ht="22.5" customHeight="1">
+      <c r="F794" s="11"/>
+      <c r="G794" s="11"/>
+    </row>
+    <row r="795" ht="22.5" customHeight="1">
+      <c r="F795" s="11"/>
+      <c r="G795" s="11"/>
+    </row>
+    <row r="796" ht="22.5" customHeight="1">
+      <c r="F796" s="11"/>
+      <c r="G796" s="11"/>
+    </row>
+    <row r="797" ht="22.5" customHeight="1">
+      <c r="F797" s="11"/>
+      <c r="G797" s="11"/>
+    </row>
+    <row r="798" ht="22.5" customHeight="1">
+      <c r="F798" s="11"/>
+      <c r="G798" s="11"/>
+    </row>
+    <row r="799" ht="22.5" customHeight="1">
+      <c r="F799" s="11"/>
+      <c r="G799" s="11"/>
+    </row>
+    <row r="800" ht="22.5" customHeight="1">
+      <c r="F800" s="11"/>
+      <c r="G800" s="11"/>
+    </row>
+    <row r="801" ht="22.5" customHeight="1">
+      <c r="F801" s="11"/>
+      <c r="G801" s="11"/>
+    </row>
+    <row r="802" ht="22.5" customHeight="1">
+      <c r="F802" s="11"/>
+      <c r="G802" s="11"/>
+    </row>
+    <row r="803" ht="22.5" customHeight="1">
+      <c r="F803" s="11"/>
+      <c r="G803" s="11"/>
+    </row>
+    <row r="804" ht="22.5" customHeight="1">
+      <c r="F804" s="11"/>
+      <c r="G804" s="11"/>
+    </row>
+    <row r="805" ht="22.5" customHeight="1">
+      <c r="F805" s="11"/>
+      <c r="G805" s="11"/>
+    </row>
+    <row r="806" ht="22.5" customHeight="1">
+      <c r="F806" s="11"/>
+      <c r="G806" s="11"/>
+    </row>
+    <row r="807" ht="22.5" customHeight="1">
+      <c r="F807" s="11"/>
+      <c r="G807" s="11"/>
+    </row>
+    <row r="808" ht="22.5" customHeight="1">
+      <c r="F808" s="11"/>
+      <c r="G808" s="11"/>
+    </row>
+    <row r="809" ht="22.5" customHeight="1">
+      <c r="F809" s="11"/>
+      <c r="G809" s="11"/>
+    </row>
+    <row r="810" ht="22.5" customHeight="1">
+      <c r="F810" s="11"/>
+      <c r="G810" s="11"/>
+    </row>
+    <row r="811" ht="22.5" customHeight="1">
+      <c r="F811" s="11"/>
+      <c r="G811" s="11"/>
+    </row>
+    <row r="812" ht="22.5" customHeight="1">
+      <c r="F812" s="11"/>
+      <c r="G812" s="11"/>
+    </row>
+    <row r="813" ht="22.5" customHeight="1">
+      <c r="F813" s="11"/>
+      <c r="G813" s="11"/>
+    </row>
+    <row r="814" ht="22.5" customHeight="1">
+      <c r="F814" s="11"/>
+      <c r="G814" s="11"/>
+    </row>
+    <row r="815" ht="22.5" customHeight="1">
+      <c r="F815" s="11"/>
+      <c r="G815" s="11"/>
+    </row>
+    <row r="816" ht="22.5" customHeight="1">
+      <c r="F816" s="11"/>
+      <c r="G816" s="11"/>
+    </row>
+    <row r="817" ht="22.5" customHeight="1">
+      <c r="F817" s="11"/>
+      <c r="G817" s="11"/>
+    </row>
+    <row r="818" ht="22.5" customHeight="1">
+      <c r="F818" s="11"/>
+      <c r="G818" s="11"/>
+    </row>
+    <row r="819" ht="22.5" customHeight="1">
+      <c r="F819" s="11"/>
+      <c r="G819" s="11"/>
+    </row>
+    <row r="820" ht="22.5" customHeight="1">
+      <c r="F820" s="11"/>
+      <c r="G820" s="11"/>
+    </row>
+    <row r="821" ht="22.5" customHeight="1">
+      <c r="F821" s="11"/>
+      <c r="G821" s="11"/>
+    </row>
+    <row r="822" ht="22.5" customHeight="1">
+      <c r="F822" s="11"/>
+      <c r="G822" s="11"/>
+    </row>
+    <row r="823" ht="22.5" customHeight="1">
+      <c r="F823" s="11"/>
+      <c r="G823" s="11"/>
+    </row>
+    <row r="824" ht="22.5" customHeight="1">
+      <c r="F824" s="11"/>
+      <c r="G824" s="11"/>
+    </row>
+    <row r="825" ht="22.5" customHeight="1">
+      <c r="F825" s="11"/>
+      <c r="G825" s="11"/>
+    </row>
+    <row r="826" ht="22.5" customHeight="1">
+      <c r="F826" s="11"/>
+      <c r="G826" s="11"/>
+    </row>
+    <row r="827" ht="22.5" customHeight="1">
+      <c r="F827" s="11"/>
+      <c r="G827" s="11"/>
+    </row>
+    <row r="828" ht="22.5" customHeight="1">
+      <c r="F828" s="11"/>
+      <c r="G828" s="11"/>
+    </row>
+    <row r="829" ht="22.5" customHeight="1">
+      <c r="F829" s="11"/>
+      <c r="G829" s="11"/>
+    </row>
+    <row r="830" ht="22.5" customHeight="1">
+      <c r="F830" s="11"/>
+      <c r="G830" s="11"/>
+    </row>
+    <row r="831" ht="22.5" customHeight="1">
+      <c r="F831" s="11"/>
+      <c r="G831" s="11"/>
+    </row>
+    <row r="832" ht="22.5" customHeight="1">
+      <c r="F832" s="11"/>
+      <c r="G832" s="11"/>
+    </row>
+    <row r="833" ht="22.5" customHeight="1">
+      <c r="F833" s="11"/>
+      <c r="G833" s="11"/>
+    </row>
+    <row r="834" ht="22.5" customHeight="1">
+      <c r="F834" s="11"/>
+      <c r="G834" s="11"/>
+    </row>
+    <row r="835" ht="22.5" customHeight="1">
+      <c r="F835" s="11"/>
+      <c r="G835" s="11"/>
+    </row>
+    <row r="836" ht="22.5" customHeight="1">
+      <c r="F836" s="11"/>
+      <c r="G836" s="11"/>
+    </row>
+    <row r="837" ht="22.5" customHeight="1">
+      <c r="F837" s="11"/>
+      <c r="G837" s="11"/>
+    </row>
+    <row r="838" ht="22.5" customHeight="1">
+      <c r="F838" s="11"/>
+      <c r="G838" s="11"/>
+    </row>
+    <row r="839" ht="22.5" customHeight="1">
+      <c r="F839" s="11"/>
+      <c r="G839" s="11"/>
+    </row>
+    <row r="840" ht="22.5" customHeight="1">
+      <c r="F840" s="11"/>
+      <c r="G840" s="11"/>
+    </row>
+    <row r="841" ht="22.5" customHeight="1">
+      <c r="F841" s="11"/>
+      <c r="G841" s="11"/>
+    </row>
+    <row r="842" ht="22.5" customHeight="1">
+      <c r="F842" s="11"/>
+      <c r="G842" s="11"/>
+    </row>
+    <row r="843" ht="22.5" customHeight="1">
+      <c r="F843" s="11"/>
+      <c r="G843" s="11"/>
+    </row>
+    <row r="844" ht="22.5" customHeight="1">
+      <c r="F844" s="11"/>
+      <c r="G844" s="11"/>
+    </row>
+    <row r="845" ht="22.5" customHeight="1">
+      <c r="F845" s="11"/>
+      <c r="G845" s="11"/>
+    </row>
+    <row r="846" ht="22.5" customHeight="1">
+      <c r="F846" s="11"/>
+      <c r="G846" s="11"/>
+    </row>
+    <row r="847" ht="22.5" customHeight="1">
+      <c r="F847" s="11"/>
+      <c r="G847" s="11"/>
+    </row>
+    <row r="848" ht="22.5" customHeight="1">
+      <c r="F848" s="11"/>
+      <c r="G848" s="11"/>
+    </row>
+    <row r="849" ht="22.5" customHeight="1">
+      <c r="F849" s="11"/>
+      <c r="G849" s="11"/>
+    </row>
+    <row r="850" ht="22.5" customHeight="1">
+      <c r="F850" s="11"/>
+      <c r="G850" s="11"/>
+    </row>
+    <row r="851" ht="22.5" customHeight="1">
+      <c r="F851" s="11"/>
+      <c r="G851" s="11"/>
+    </row>
+    <row r="852" ht="22.5" customHeight="1">
+      <c r="F852" s="11"/>
+      <c r="G852" s="11"/>
+    </row>
+    <row r="853" ht="22.5" customHeight="1">
+      <c r="F853" s="11"/>
+      <c r="G853" s="11"/>
+    </row>
+    <row r="854" ht="22.5" customHeight="1">
+      <c r="F854" s="11"/>
+      <c r="G854" s="11"/>
+    </row>
+    <row r="855" ht="22.5" customHeight="1">
+      <c r="F855" s="11"/>
+      <c r="G855" s="11"/>
+    </row>
+    <row r="856" ht="22.5" customHeight="1">
+      <c r="F856" s="11"/>
+      <c r="G856" s="11"/>
+    </row>
+    <row r="857" ht="22.5" customHeight="1">
+      <c r="F857" s="11"/>
+      <c r="G857" s="11"/>
+    </row>
+    <row r="858" ht="22.5" customHeight="1">
+      <c r="F858" s="11"/>
+      <c r="G858" s="11"/>
+    </row>
+    <row r="859" ht="22.5" customHeight="1">
+      <c r="F859" s="11"/>
+      <c r="G859" s="11"/>
+    </row>
+    <row r="860" ht="22.5" customHeight="1">
+      <c r="F860" s="11"/>
+      <c r="G860" s="11"/>
+    </row>
+    <row r="861" ht="22.5" customHeight="1">
+      <c r="F861" s="11"/>
+      <c r="G861" s="11"/>
+    </row>
+    <row r="862" ht="22.5" customHeight="1">
+      <c r="F862" s="11"/>
+      <c r="G862" s="11"/>
+    </row>
+    <row r="863" ht="22.5" customHeight="1">
+      <c r="F863" s="11"/>
+      <c r="G863" s="11"/>
+    </row>
+    <row r="864" ht="22.5" customHeight="1">
+      <c r="F864" s="11"/>
+      <c r="G864" s="11"/>
+    </row>
+    <row r="865" ht="22.5" customHeight="1">
+      <c r="F865" s="11"/>
+      <c r="G865" s="11"/>
+    </row>
+    <row r="866" ht="22.5" customHeight="1">
+      <c r="F866" s="11"/>
+      <c r="G866" s="11"/>
+    </row>
+    <row r="867" ht="22.5" customHeight="1">
+      <c r="F867" s="11"/>
+      <c r="G867" s="11"/>
+    </row>
+    <row r="868" ht="22.5" customHeight="1">
+      <c r="F868" s="11"/>
+      <c r="G868" s="11"/>
+    </row>
+    <row r="869" ht="22.5" customHeight="1">
+      <c r="F869" s="11"/>
+      <c r="G869" s="11"/>
+    </row>
+    <row r="870" ht="22.5" customHeight="1">
+      <c r="F870" s="11"/>
+      <c r="G870" s="11"/>
+    </row>
+    <row r="871" ht="22.5" customHeight="1">
+      <c r="F871" s="11"/>
+      <c r="G871" s="11"/>
+    </row>
+    <row r="872" ht="22.5" customHeight="1">
+      <c r="F872" s="11"/>
+      <c r="G872" s="11"/>
+    </row>
+    <row r="873" ht="22.5" customHeight="1">
+      <c r="F873" s="11"/>
+      <c r="G873" s="11"/>
+    </row>
+    <row r="874" ht="22.5" customHeight="1">
+      <c r="F874" s="11"/>
+      <c r="G874" s="11"/>
+    </row>
+    <row r="875" ht="22.5" customHeight="1">
+      <c r="F875" s="11"/>
+      <c r="G875" s="11"/>
+    </row>
+    <row r="876" ht="22.5" customHeight="1">
+      <c r="F876" s="11"/>
+      <c r="G876" s="11"/>
+    </row>
+    <row r="877" ht="22.5" customHeight="1">
+      <c r="F877" s="11"/>
+      <c r="G877" s="11"/>
+    </row>
+    <row r="878" ht="22.5" customHeight="1">
+      <c r="F878" s="11"/>
+      <c r="G878" s="11"/>
+    </row>
+    <row r="879" ht="22.5" customHeight="1">
+      <c r="F879" s="11"/>
+      <c r="G879" s="11"/>
+    </row>
+    <row r="880" ht="22.5" customHeight="1">
+      <c r="F880" s="11"/>
+      <c r="G880" s="11"/>
+    </row>
+    <row r="881" ht="22.5" customHeight="1">
+      <c r="F881" s="11"/>
+      <c r="G881" s="11"/>
+    </row>
+    <row r="882" ht="22.5" customHeight="1">
+      <c r="F882" s="11"/>
+      <c r="G882" s="11"/>
+    </row>
+    <row r="883" ht="22.5" customHeight="1">
+      <c r="F883" s="11"/>
+      <c r="G883" s="11"/>
+    </row>
+    <row r="884" ht="22.5" customHeight="1">
+      <c r="F884" s="11"/>
+      <c r="G884" s="11"/>
+    </row>
+    <row r="885" ht="22.5" customHeight="1">
+      <c r="F885" s="11"/>
+      <c r="G885" s="11"/>
+    </row>
+    <row r="886" ht="22.5" customHeight="1">
+      <c r="F886" s="11"/>
+      <c r="G886" s="11"/>
+    </row>
+    <row r="887" ht="22.5" customHeight="1">
+      <c r="F887" s="11"/>
+      <c r="G887" s="11"/>
+    </row>
+    <row r="888" ht="22.5" customHeight="1">
+      <c r="F888" s="11"/>
+      <c r="G888" s="11"/>
+    </row>
+    <row r="889" ht="22.5" customHeight="1">
+      <c r="F889" s="11"/>
+      <c r="G889" s="11"/>
+    </row>
+    <row r="890" ht="22.5" customHeight="1">
+      <c r="F890" s="11"/>
+      <c r="G890" s="11"/>
+    </row>
+    <row r="891" ht="22.5" customHeight="1">
+      <c r="F891" s="11"/>
+      <c r="G891" s="11"/>
+    </row>
+    <row r="892" ht="22.5" customHeight="1">
+      <c r="F892" s="11"/>
+      <c r="G892" s="11"/>
+    </row>
+    <row r="893" ht="22.5" customHeight="1">
+      <c r="F893" s="11"/>
+      <c r="G893" s="11"/>
+    </row>
+    <row r="894" ht="22.5" customHeight="1">
+      <c r="F894" s="11"/>
+      <c r="G894" s="11"/>
+    </row>
+    <row r="895" ht="22.5" customHeight="1">
+      <c r="F895" s="11"/>
+      <c r="G895" s="11"/>
+    </row>
+    <row r="896" ht="22.5" customHeight="1">
+      <c r="F896" s="11"/>
+      <c r="G896" s="11"/>
+    </row>
+    <row r="897" ht="22.5" customHeight="1">
+      <c r="F897" s="11"/>
+      <c r="G897" s="11"/>
+    </row>
+    <row r="898" ht="22.5" customHeight="1">
+      <c r="F898" s="11"/>
+      <c r="G898" s="11"/>
+    </row>
+    <row r="899" ht="22.5" customHeight="1">
+      <c r="F899" s="11"/>
+      <c r="G899" s="11"/>
+    </row>
+    <row r="900" ht="22.5" customHeight="1">
+      <c r="F900" s="11"/>
+      <c r="G900" s="11"/>
+    </row>
+    <row r="901" ht="22.5" customHeight="1">
+      <c r="F901" s="11"/>
+      <c r="G901" s="11"/>
+    </row>
+    <row r="902" ht="22.5" customHeight="1">
+      <c r="F902" s="11"/>
+      <c r="G902" s="11"/>
+    </row>
+    <row r="903" ht="22.5" customHeight="1">
+      <c r="F903" s="11"/>
+      <c r="G903" s="11"/>
+    </row>
+    <row r="904" ht="22.5" customHeight="1">
+      <c r="F904" s="11"/>
+      <c r="G904" s="11"/>
+    </row>
+    <row r="905" ht="22.5" customHeight="1">
+      <c r="F905" s="11"/>
+      <c r="G905" s="11"/>
+    </row>
+    <row r="906" ht="22.5" customHeight="1">
+      <c r="F906" s="11"/>
+      <c r="G906" s="11"/>
+    </row>
+    <row r="907" ht="22.5" customHeight="1">
+      <c r="F907" s="11"/>
+      <c r="G907" s="11"/>
+    </row>
+    <row r="908" ht="22.5" customHeight="1">
+      <c r="F908" s="11"/>
+      <c r="G908" s="11"/>
+    </row>
+    <row r="909" ht="22.5" customHeight="1">
+      <c r="F909" s="11"/>
+      <c r="G909" s="11"/>
+    </row>
+    <row r="910" ht="22.5" customHeight="1">
+      <c r="F910" s="11"/>
+      <c r="G910" s="11"/>
+    </row>
+    <row r="911" ht="22.5" customHeight="1">
+      <c r="F911" s="11"/>
+      <c r="G911" s="11"/>
+    </row>
+    <row r="912" ht="22.5" customHeight="1">
+      <c r="F912" s="11"/>
+      <c r="G912" s="11"/>
+    </row>
+    <row r="913" ht="22.5" customHeight="1">
+      <c r="F913" s="11"/>
+      <c r="G913" s="11"/>
+    </row>
+    <row r="914" ht="22.5" customHeight="1">
+      <c r="F914" s="11"/>
+      <c r="G914" s="11"/>
+    </row>
+    <row r="915" ht="22.5" customHeight="1">
+      <c r="F915" s="11"/>
+      <c r="G915" s="11"/>
+    </row>
+    <row r="916" ht="22.5" customHeight="1">
+      <c r="F916" s="11"/>
+      <c r="G916" s="11"/>
+    </row>
+    <row r="917" ht="22.5" customHeight="1">
+      <c r="F917" s="11"/>
+      <c r="G917" s="11"/>
+    </row>
+    <row r="918" ht="22.5" customHeight="1">
+      <c r="F918" s="11"/>
+      <c r="G918" s="11"/>
+    </row>
+    <row r="919" ht="22.5" customHeight="1">
+      <c r="F919" s="11"/>
+      <c r="G919" s="11"/>
+    </row>
+    <row r="920" ht="22.5" customHeight="1">
+      <c r="F920" s="11"/>
+      <c r="G920" s="11"/>
+    </row>
+    <row r="921" ht="22.5" customHeight="1">
+      <c r="F921" s="11"/>
+      <c r="G921" s="11"/>
+    </row>
+    <row r="922" ht="22.5" customHeight="1">
+      <c r="F922" s="11"/>
+      <c r="G922" s="11"/>
+    </row>
+    <row r="923" ht="22.5" customHeight="1">
+      <c r="F923" s="11"/>
+      <c r="G923" s="11"/>
+    </row>
+    <row r="924" ht="22.5" customHeight="1">
+      <c r="F924" s="11"/>
+      <c r="G924" s="11"/>
+    </row>
+    <row r="925" ht="22.5" customHeight="1">
+      <c r="F925" s="11"/>
+      <c r="G925" s="11"/>
+    </row>
+    <row r="926" ht="22.5" customHeight="1">
+      <c r="F926" s="11"/>
+      <c r="G926" s="11"/>
+    </row>
+    <row r="927" ht="22.5" customHeight="1">
+      <c r="F927" s="11"/>
+      <c r="G927" s="11"/>
+    </row>
+    <row r="928" ht="22.5" customHeight="1">
+      <c r="F928" s="11"/>
+      <c r="G928" s="11"/>
+    </row>
+    <row r="929" ht="22.5" customHeight="1">
+      <c r="F929" s="11"/>
+      <c r="G929" s="11"/>
+    </row>
+    <row r="930" ht="22.5" customHeight="1">
+      <c r="F930" s="11"/>
+      <c r="G930" s="11"/>
+    </row>
+    <row r="931" ht="22.5" customHeight="1">
+      <c r="F931" s="11"/>
+      <c r="G931" s="11"/>
+    </row>
+    <row r="932" ht="22.5" customHeight="1">
+      <c r="F932" s="11"/>
+      <c r="G932" s="11"/>
+    </row>
+    <row r="933" ht="22.5" customHeight="1">
+      <c r="F933" s="11"/>
+      <c r="G933" s="11"/>
+    </row>
+    <row r="934" ht="22.5" customHeight="1">
+      <c r="F934" s="11"/>
+      <c r="G934" s="11"/>
+    </row>
+    <row r="935" ht="22.5" customHeight="1">
+      <c r="F935" s="11"/>
+      <c r="G935" s="11"/>
+    </row>
+    <row r="936" ht="22.5" customHeight="1">
+      <c r="F936" s="11"/>
+      <c r="G936" s="11"/>
+    </row>
+    <row r="937" ht="22.5" customHeight="1">
+      <c r="F937" s="11"/>
+      <c r="G937" s="11"/>
+    </row>
+    <row r="938" ht="22.5" customHeight="1">
+      <c r="F938" s="11"/>
+      <c r="G938" s="11"/>
+    </row>
+    <row r="939" ht="22.5" customHeight="1">
+      <c r="F939" s="11"/>
+      <c r="G939" s="11"/>
+    </row>
+    <row r="940" ht="22.5" customHeight="1">
+      <c r="F940" s="11"/>
+      <c r="G940" s="11"/>
+    </row>
+    <row r="941" ht="22.5" customHeight="1">
+      <c r="F941" s="11"/>
+      <c r="G941" s="11"/>
+    </row>
+    <row r="942" ht="22.5" customHeight="1">
+      <c r="F942" s="11"/>
+      <c r="G942" s="11"/>
+    </row>
+    <row r="943" ht="22.5" customHeight="1">
+      <c r="F943" s="11"/>
+      <c r="G943" s="11"/>
+    </row>
+    <row r="944" ht="22.5" customHeight="1">
+      <c r="F944" s="11"/>
+      <c r="G944" s="11"/>
+    </row>
+    <row r="945" ht="22.5" customHeight="1">
+      <c r="F945" s="11"/>
+      <c r="G945" s="11"/>
+    </row>
+    <row r="946" ht="22.5" customHeight="1">
+      <c r="F946" s="11"/>
+      <c r="G946" s="11"/>
+    </row>
+    <row r="947" ht="22.5" customHeight="1">
+      <c r="F947" s="11"/>
+      <c r="G947" s="11"/>
+    </row>
+    <row r="948" ht="22.5" customHeight="1">
+      <c r="F948" s="11"/>
+      <c r="G948" s="11"/>
+    </row>
+    <row r="949" ht="22.5" customHeight="1">
+      <c r="F949" s="11"/>
+      <c r="G949" s="11"/>
+    </row>
+    <row r="950" ht="22.5" customHeight="1">
+      <c r="F950" s="11"/>
+      <c r="G950" s="11"/>
+    </row>
+    <row r="951" ht="22.5" customHeight="1">
+      <c r="F951" s="11"/>
+      <c r="G951" s="11"/>
+    </row>
+    <row r="952" ht="22.5" customHeight="1">
+      <c r="F952" s="11"/>
+      <c r="G952" s="11"/>
+    </row>
+    <row r="953" ht="22.5" customHeight="1">
+      <c r="F953" s="11"/>
+      <c r="G953" s="11"/>
+    </row>
+    <row r="954" ht="22.5" customHeight="1">
+      <c r="F954" s="11"/>
+      <c r="G954" s="11"/>
+    </row>
+    <row r="955" ht="22.5" customHeight="1">
+      <c r="F955" s="11"/>
+      <c r="G955" s="11"/>
+    </row>
+    <row r="956" ht="22.5" customHeight="1">
+      <c r="F956" s="11"/>
+      <c r="G956" s="11"/>
+    </row>
+    <row r="957" ht="22.5" customHeight="1">
+      <c r="F957" s="11"/>
+      <c r="G957" s="11"/>
+    </row>
+    <row r="958" ht="22.5" customHeight="1">
+      <c r="F958" s="11"/>
+      <c r="G958" s="11"/>
+    </row>
+    <row r="959" ht="22.5" customHeight="1">
+      <c r="F959" s="11"/>
+      <c r="G959" s="11"/>
+    </row>
+    <row r="960" ht="22.5" customHeight="1">
+      <c r="F960" s="11"/>
+      <c r="G960" s="11"/>
+    </row>
+    <row r="961" ht="22.5" customHeight="1">
+      <c r="F961" s="11"/>
+      <c r="G961" s="11"/>
+    </row>
+    <row r="962" ht="22.5" customHeight="1">
+      <c r="F962" s="11"/>
+      <c r="G962" s="11"/>
+    </row>
+    <row r="963" ht="22.5" customHeight="1">
+      <c r="F963" s="11"/>
+      <c r="G963" s="11"/>
+    </row>
+    <row r="964" ht="22.5" customHeight="1">
+      <c r="F964" s="11"/>
+      <c r="G964" s="11"/>
+    </row>
+    <row r="965" ht="22.5" customHeight="1">
+      <c r="F965" s="11"/>
+      <c r="G965" s="11"/>
+    </row>
+    <row r="966" ht="22.5" customHeight="1">
+      <c r="F966" s="11"/>
+      <c r="G966" s="11"/>
+    </row>
+    <row r="967" ht="22.5" customHeight="1">
+      <c r="F967" s="11"/>
+      <c r="G967" s="11"/>
+    </row>
+    <row r="968" ht="22.5" customHeight="1">
+      <c r="F968" s="11"/>
+      <c r="G968" s="11"/>
+    </row>
+    <row r="969" ht="22.5" customHeight="1">
+      <c r="F969" s="11"/>
+      <c r="G969" s="11"/>
+    </row>
+    <row r="970" ht="22.5" customHeight="1">
+      <c r="F970" s="11"/>
+      <c r="G970" s="11"/>
+    </row>
+    <row r="971" ht="22.5" customHeight="1">
+      <c r="F971" s="11"/>
+      <c r="G971" s="11"/>
+    </row>
+    <row r="972" ht="22.5" customHeight="1">
+      <c r="F972" s="11"/>
+      <c r="G972" s="11"/>
+    </row>
+    <row r="973" ht="22.5" customHeight="1">
+      <c r="F973" s="11"/>
+      <c r="G973" s="11"/>
+    </row>
+    <row r="974" ht="22.5" customHeight="1">
+      <c r="F974" s="11"/>
+      <c r="G974" s="11"/>
+    </row>
+    <row r="975" ht="22.5" customHeight="1">
+      <c r="F975" s="11"/>
+      <c r="G975" s="11"/>
+    </row>
+    <row r="976" ht="22.5" customHeight="1">
+      <c r="F976" s="11"/>
+      <c r="G976" s="11"/>
+    </row>
+    <row r="977" ht="22.5" customHeight="1">
+      <c r="F977" s="11"/>
+      <c r="G977" s="11"/>
+    </row>
+    <row r="978" ht="22.5" customHeight="1">
+      <c r="F978" s="11"/>
+      <c r="G978" s="11"/>
+    </row>
+    <row r="979" ht="22.5" customHeight="1">
+      <c r="F979" s="11"/>
+      <c r="G979" s="11"/>
+    </row>
+    <row r="980" ht="22.5" customHeight="1">
+      <c r="F980" s="11"/>
+      <c r="G980" s="11"/>
+    </row>
+    <row r="981" ht="22.5" customHeight="1">
+      <c r="F981" s="11"/>
+      <c r="G981" s="11"/>
+    </row>
+    <row r="982" ht="22.5" customHeight="1">
+      <c r="F982" s="11"/>
+      <c r="G982" s="11"/>
+    </row>
+    <row r="983" ht="22.5" customHeight="1">
+      <c r="F983" s="11"/>
+      <c r="G983" s="11"/>
+    </row>
+    <row r="984" ht="22.5" customHeight="1">
+      <c r="F984" s="11"/>
+      <c r="G984" s="11"/>
+    </row>
+    <row r="985" ht="22.5" customHeight="1">
+      <c r="F985" s="11"/>
+      <c r="G985" s="11"/>
+    </row>
+    <row r="986" ht="22.5" customHeight="1">
+      <c r="F986" s="11"/>
+      <c r="G986" s="11"/>
+    </row>
+    <row r="987" ht="22.5" customHeight="1">
+      <c r="F987" s="11"/>
+      <c r="G987" s="11"/>
+    </row>
+    <row r="988" ht="22.5" customHeight="1">
+      <c r="F988" s="11"/>
+      <c r="G988" s="11"/>
+    </row>
+    <row r="989" ht="22.5" customHeight="1">
+      <c r="F989" s="11"/>
+      <c r="G989" s="11"/>
+    </row>
+    <row r="990" ht="22.5" customHeight="1">
+      <c r="F990" s="11"/>
+      <c r="G990" s="11"/>
+    </row>
+    <row r="991" ht="22.5" customHeight="1">
+      <c r="F991" s="11"/>
+      <c r="G991" s="11"/>
+    </row>
+    <row r="992" ht="22.5" customHeight="1">
+      <c r="F992" s="11"/>
+      <c r="G992" s="11"/>
+    </row>
+    <row r="993" ht="22.5" customHeight="1">
+      <c r="F993" s="11"/>
+      <c r="G993" s="11"/>
+    </row>
+    <row r="994" ht="22.5" customHeight="1">
+      <c r="F994" s="11"/>
+      <c r="G994" s="11"/>
+    </row>
+    <row r="995" ht="22.5" customHeight="1">
+      <c r="F995" s="11"/>
+      <c r="G995" s="11"/>
+    </row>
+    <row r="996" ht="22.5" customHeight="1">
+      <c r="F996" s="11"/>
+      <c r="G996" s="11"/>
+    </row>
+    <row r="997" ht="22.5" customHeight="1">
+      <c r="F997" s="11"/>
+      <c r="G997" s="11"/>
+    </row>
+    <row r="998" ht="22.5" customHeight="1">
+      <c r="F998" s="11"/>
+      <c r="G998" s="11"/>
+    </row>
+    <row r="999" ht="22.5" customHeight="1">
+      <c r="F999" s="11"/>
+      <c r="G999" s="11"/>
+    </row>
+    <row r="1000" ht="22.5" customHeight="1">
+      <c r="F1000" s="11"/>
+      <c r="G1000" s="11"/>
+    </row>
+    <row r="1001" ht="22.5" customHeight="1">
+      <c r="F1001" s="11"/>
+      <c r="G1001" s="11"/>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
   <tableParts count="1">

--- a/Demographic analysis sites.xlsx
+++ b/Demographic analysis sites.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Brandon Nguyen\Documents\Independent study\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3410420-E67B-454A-8E4E-AB546EE7828A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29FC958C-F9B1-4866-BEA8-95808DACEC3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1531" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1531" uniqueCount="147">
   <si>
     <t>Site</t>
   </si>
@@ -462,6 +462,9 @@
   </si>
   <si>
     <t>Nesje and Dahl 2001</t>
+  </si>
+  <si>
+    <t>8.2k</t>
   </si>
 </sst>
 </file>
@@ -10389,9 +10392,7 @@
       <c r="F14" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>118</v>
-      </c>
+      <c r="G14" s="2"/>
     </row>
     <row r="15" spans="1:7" ht="22.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
@@ -10630,8 +10631,8 @@
       <c r="E25" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="F25" s="2">
-        <v>8.1999999999999993</v>
+      <c r="F25" s="2" t="s">
+        <v>146</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>118</v>
